--- a/artfynd/A 55525-2025 artfynd.xlsx
+++ b/artfynd/A 55525-2025 artfynd.xlsx
@@ -1412,7 +1412,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133888831</v>
+        <v>133888836</v>
       </c>
       <c r="B9" t="n">
         <v>99070</v>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>706466</v>
+        <v>706505</v>
       </c>
       <c r="R9" t="n">
-        <v>7426731</v>
+        <v>7426733</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1483,11 +1483,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>9 blommor</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1514,7 +1509,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133888836</v>
+        <v>133888831</v>
       </c>
       <c r="B10" t="n">
         <v>99070</v>
@@ -1549,10 +1544,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>706505</v>
+        <v>706466</v>
       </c>
       <c r="R10" t="n">
-        <v>7426733</v>
+        <v>7426731</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1585,6 +1580,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>9 blommor</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1611,32 +1611,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133888827</v>
+        <v>133888837</v>
       </c>
       <c r="B11" t="n">
-        <v>57162</v>
+        <v>99070</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>233</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>706811</v>
+        <v>706498</v>
       </c>
       <c r="R11" t="n">
-        <v>7426646</v>
+        <v>7426729</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1708,32 +1708,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133888837</v>
+        <v>133888827</v>
       </c>
       <c r="B12" t="n">
-        <v>99070</v>
+        <v>57162</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>233</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>706498</v>
+        <v>706811</v>
       </c>
       <c r="R12" t="n">
-        <v>7426729</v>
+        <v>7426646</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1907,7 +1907,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133888833</v>
+        <v>133888835</v>
       </c>
       <c r="B14" t="n">
         <v>99070</v>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>706441</v>
+        <v>706462</v>
       </c>
       <c r="R14" t="n">
-        <v>7426721</v>
+        <v>7426725</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -1978,6 +1978,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>5 blommor</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2004,7 +2009,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133888835</v>
+        <v>133888833</v>
       </c>
       <c r="B15" t="n">
         <v>99070</v>
@@ -2039,10 +2044,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>706462</v>
+        <v>706441</v>
       </c>
       <c r="R15" t="n">
-        <v>7426725</v>
+        <v>7426721</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2075,11 +2080,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>5 blommor</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2305,7 +2305,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134102397</v>
+        <v>134102294</v>
       </c>
       <c r="B18" t="n">
         <v>79426</v>
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>706868</v>
+        <v>706878</v>
       </c>
       <c r="R18" t="n">
-        <v>7426681</v>
+        <v>7426778</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2402,7 +2402,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134102294</v>
+        <v>134102397</v>
       </c>
       <c r="B19" t="n">
         <v>79426</v>
@@ -2437,10 +2437,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>706878</v>
+        <v>706868</v>
       </c>
       <c r="R19" t="n">
-        <v>7426778</v>
+        <v>7426681</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2790,7 +2790,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134102293</v>
+        <v>134102313</v>
       </c>
       <c r="B23" t="n">
         <v>79426</v>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>706890</v>
+        <v>706912</v>
       </c>
       <c r="R23" t="n">
-        <v>7426773</v>
+        <v>7426790</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -2887,7 +2887,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134102313</v>
+        <v>134102293</v>
       </c>
       <c r="B24" t="n">
         <v>79426</v>
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>706912</v>
+        <v>706890</v>
       </c>
       <c r="R24" t="n">
-        <v>7426790</v>
+        <v>7426773</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -3183,7 +3183,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134102298</v>
+        <v>134102296</v>
       </c>
       <c r="B27" t="n">
         <v>79426</v>
@@ -3218,10 +3218,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>706810</v>
+        <v>706851</v>
       </c>
       <c r="R27" t="n">
-        <v>7426802</v>
+        <v>7426782</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3280,7 +3280,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134102296</v>
+        <v>134102298</v>
       </c>
       <c r="B28" t="n">
         <v>79426</v>
@@ -3315,10 +3315,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>706851</v>
+        <v>706810</v>
       </c>
       <c r="R28" t="n">
-        <v>7426782</v>
+        <v>7426802</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -3377,7 +3377,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134102305</v>
+        <v>134102323</v>
       </c>
       <c r="B29" t="n">
         <v>79426</v>
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>706852</v>
+        <v>706967</v>
       </c>
       <c r="R29" t="n">
-        <v>7426799</v>
+        <v>7426729</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3442,12 +3442,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3474,7 +3474,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134102323</v>
+        <v>134102305</v>
       </c>
       <c r="B30" t="n">
         <v>79426</v>
@@ -3509,10 +3509,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>706967</v>
+        <v>706852</v>
       </c>
       <c r="R30" t="n">
-        <v>7426729</v>
+        <v>7426799</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3539,12 +3539,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3765,7 +3765,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134102297</v>
+        <v>134102291</v>
       </c>
       <c r="B33" t="n">
         <v>79426</v>
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>706834</v>
+        <v>706899</v>
       </c>
       <c r="R33" t="n">
-        <v>7426787</v>
+        <v>7426771</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -3862,7 +3862,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134102291</v>
+        <v>134102297</v>
       </c>
       <c r="B34" t="n">
         <v>79426</v>
@@ -3897,10 +3897,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>706899</v>
+        <v>706834</v>
       </c>
       <c r="R34" t="n">
-        <v>7426771</v>
+        <v>7426787</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -3959,7 +3959,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134102304</v>
+        <v>134102299</v>
       </c>
       <c r="B35" t="n">
         <v>79426</v>
@@ -3994,10 +3994,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>706855</v>
+        <v>706809</v>
       </c>
       <c r="R35" t="n">
-        <v>7426811</v>
+        <v>7426819</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -4056,7 +4056,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134102299</v>
+        <v>134102304</v>
       </c>
       <c r="B36" t="n">
         <v>79426</v>
@@ -4091,10 +4091,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>706809</v>
+        <v>706855</v>
       </c>
       <c r="R36" t="n">
-        <v>7426819</v>
+        <v>7426811</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4638,10 +4638,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134102311</v>
+        <v>134102331</v>
       </c>
       <c r="B42" t="n">
-        <v>79426</v>
+        <v>99070</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4649,21 +4649,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>637</v>
+        <v>233</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4673,10 +4673,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>706893</v>
+        <v>706920</v>
       </c>
       <c r="R42" t="n">
-        <v>7426806</v>
+        <v>7426776</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -4709,6 +4709,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>5 blommor</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4735,10 +4740,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134102331</v>
+        <v>134102302</v>
       </c>
       <c r="B43" t="n">
-        <v>99070</v>
+        <v>79426</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4746,21 +4751,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>233</v>
+        <v>637</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4770,10 +4775,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>706920</v>
+        <v>706816</v>
       </c>
       <c r="R43" t="n">
-        <v>7426776</v>
+        <v>7426823</v>
       </c>
       <c r="S43" t="n">
         <v>3</v>
@@ -4806,11 +4811,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>5 blommor</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4837,7 +4837,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134102302</v>
+        <v>134102311</v>
       </c>
       <c r="B44" t="n">
         <v>79426</v>
@@ -4872,10 +4872,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>706816</v>
+        <v>706893</v>
       </c>
       <c r="R44" t="n">
-        <v>7426823</v>
+        <v>7426806</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -5322,32 +5322,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134102334</v>
+        <v>134102395</v>
       </c>
       <c r="B49" t="n">
-        <v>79438</v>
+        <v>79426</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>864</v>
+        <v>637</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5357,10 +5357,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>706856</v>
+        <v>706915</v>
       </c>
       <c r="R49" t="n">
-        <v>7426791</v>
+        <v>7426639</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -5419,7 +5419,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134102395</v>
+        <v>134102289</v>
       </c>
       <c r="B50" t="n">
         <v>79426</v>
@@ -5454,10 +5454,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>706915</v>
+        <v>706941</v>
       </c>
       <c r="R50" t="n">
-        <v>7426639</v>
+        <v>7426720</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -5516,32 +5516,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134102292</v>
+        <v>134102334</v>
       </c>
       <c r="B51" t="n">
-        <v>79426</v>
+        <v>79438</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>637</v>
+        <v>864</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5551,10 +5551,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>706891</v>
+        <v>706856</v>
       </c>
       <c r="R51" t="n">
-        <v>7426771</v>
+        <v>7426791</v>
       </c>
       <c r="S51" t="n">
         <v>3</v>
@@ -5613,7 +5613,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134102289</v>
+        <v>134102292</v>
       </c>
       <c r="B52" t="n">
         <v>79426</v>
@@ -5648,10 +5648,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>706941</v>
+        <v>706891</v>
       </c>
       <c r="R52" t="n">
-        <v>7426720</v>
+        <v>7426771</v>
       </c>
       <c r="S52" t="n">
         <v>3</v>
@@ -5710,7 +5710,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134102312</v>
+        <v>134102314</v>
       </c>
       <c r="B53" t="n">
         <v>79426</v>
@@ -5745,10 +5745,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>706909</v>
+        <v>706925</v>
       </c>
       <c r="R53" t="n">
-        <v>7426793</v>
+        <v>7426791</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -5904,7 +5904,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134102320</v>
+        <v>134102394</v>
       </c>
       <c r="B55" t="n">
         <v>79426</v>
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>706960</v>
+        <v>706913</v>
       </c>
       <c r="R55" t="n">
-        <v>7426760</v>
+        <v>7426627</v>
       </c>
       <c r="S55" t="n">
         <v>3</v>
@@ -6001,7 +6001,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134102314</v>
+        <v>134102312</v>
       </c>
       <c r="B56" t="n">
         <v>79426</v>
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>706925</v>
+        <v>706909</v>
       </c>
       <c r="R56" t="n">
-        <v>7426791</v>
+        <v>7426793</v>
       </c>
       <c r="S56" t="n">
         <v>3</v>
@@ -6098,7 +6098,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134102394</v>
+        <v>134102320</v>
       </c>
       <c r="B57" t="n">
         <v>79426</v>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>706913</v>
+        <v>706960</v>
       </c>
       <c r="R57" t="n">
-        <v>7426627</v>
+        <v>7426760</v>
       </c>
       <c r="S57" t="n">
         <v>3</v>
@@ -6486,32 +6486,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134272886</v>
+        <v>134272878</v>
       </c>
       <c r="B61" t="n">
-        <v>79116</v>
+        <v>58839</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>208249</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6521,10 +6521,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>706845</v>
+        <v>706913</v>
       </c>
       <c r="R61" t="n">
-        <v>7426764</v>
+        <v>7426789</v>
       </c>
       <c r="S61" t="n">
         <v>3</v>
@@ -6680,32 +6680,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>134272878</v>
+        <v>134272886</v>
       </c>
       <c r="B63" t="n">
-        <v>58839</v>
+        <v>79116</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>208249</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6715,10 +6715,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>706913</v>
+        <v>706845</v>
       </c>
       <c r="R63" t="n">
-        <v>7426789</v>
+        <v>7426764</v>
       </c>
       <c r="S63" t="n">
         <v>3</v>
@@ -7558,32 +7558,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134272750</v>
+        <v>134272879</v>
       </c>
       <c r="B72" t="n">
-        <v>99070</v>
+        <v>58839</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>233</v>
+        <v>208249</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7593,10 +7593,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>706247</v>
+        <v>706948</v>
       </c>
       <c r="R72" t="n">
-        <v>7426954</v>
+        <v>7426772</v>
       </c>
       <c r="S72" t="n">
         <v>3</v>
@@ -7629,11 +7629,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>4 blommor</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7660,32 +7655,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134272879</v>
+        <v>134272750</v>
       </c>
       <c r="B73" t="n">
-        <v>58839</v>
+        <v>99070</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>208249</v>
+        <v>233</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7695,10 +7690,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>706948</v>
+        <v>706247</v>
       </c>
       <c r="R73" t="n">
-        <v>7426772</v>
+        <v>7426954</v>
       </c>
       <c r="S73" t="n">
         <v>3</v>
@@ -7731,6 +7726,11 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>4 blommor</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7757,10 +7757,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134272755</v>
+        <v>134272885</v>
       </c>
       <c r="B74" t="n">
-        <v>79025</v>
+        <v>79116</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7768,21 +7768,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7792,10 +7792,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>706573</v>
+        <v>706844</v>
       </c>
       <c r="R74" t="n">
-        <v>7426540</v>
+        <v>7426764</v>
       </c>
       <c r="S74" t="n">
         <v>3</v>
@@ -7854,10 +7854,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>134272885</v>
+        <v>134272755</v>
       </c>
       <c r="B75" t="n">
-        <v>79116</v>
+        <v>79025</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7865,21 +7865,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7889,10 +7889,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>706844</v>
+        <v>706573</v>
       </c>
       <c r="R75" t="n">
-        <v>7426764</v>
+        <v>7426540</v>
       </c>
       <c r="S75" t="n">
         <v>3</v>

--- a/artfynd/A 55525-2025 artfynd.xlsx
+++ b/artfynd/A 55525-2025 artfynd.xlsx
@@ -920,7 +920,7 @@
         <v>133888834</v>
       </c>
       <c r="B4" t="n">
-        <v>99070</v>
+        <v>99077</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>133888838</v>
       </c>
       <c r="B5" t="n">
-        <v>99070</v>
+        <v>99077</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>133888840</v>
       </c>
       <c r="B6" t="n">
-        <v>93257</v>
+        <v>93264</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>133888830</v>
       </c>
       <c r="B7" t="n">
-        <v>99070</v>
+        <v>99077</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>133888832</v>
       </c>
       <c r="B8" t="n">
-        <v>99070</v>
+        <v>99077</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1412,10 +1412,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133888836</v>
+        <v>133888831</v>
       </c>
       <c r="B9" t="n">
-        <v>99070</v>
+        <v>99077</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1447,10 +1447,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>706505</v>
+        <v>706466</v>
       </c>
       <c r="R9" t="n">
-        <v>7426733</v>
+        <v>7426731</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1483,6 +1483,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>9 blommor</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1509,10 +1514,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133888831</v>
+        <v>133888836</v>
       </c>
       <c r="B10" t="n">
-        <v>99070</v>
+        <v>99077</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,10 +1549,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>706466</v>
+        <v>706505</v>
       </c>
       <c r="R10" t="n">
-        <v>7426731</v>
+        <v>7426733</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1580,11 +1585,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>9 blommor</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1611,32 +1611,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133888837</v>
+        <v>133888827</v>
       </c>
       <c r="B11" t="n">
-        <v>99070</v>
+        <v>57162</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>233</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>706498</v>
+        <v>706811</v>
       </c>
       <c r="R11" t="n">
-        <v>7426729</v>
+        <v>7426646</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1708,32 +1708,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133888827</v>
+        <v>133888837</v>
       </c>
       <c r="B12" t="n">
-        <v>57162</v>
+        <v>99077</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>233</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>706811</v>
+        <v>706498</v>
       </c>
       <c r="R12" t="n">
-        <v>7426646</v>
+        <v>7426729</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1808,7 +1808,7 @@
         <v>133888829</v>
       </c>
       <c r="B13" t="n">
-        <v>99070</v>
+        <v>99077</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1907,10 +1907,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133888835</v>
+        <v>133888833</v>
       </c>
       <c r="B14" t="n">
-        <v>99070</v>
+        <v>99077</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1942,10 +1942,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>706462</v>
+        <v>706441</v>
       </c>
       <c r="R14" t="n">
-        <v>7426725</v>
+        <v>7426721</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -1978,11 +1978,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>5 blommor</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2009,10 +2004,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133888833</v>
+        <v>133888835</v>
       </c>
       <c r="B15" t="n">
-        <v>99070</v>
+        <v>99077</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2044,10 +2039,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>706441</v>
+        <v>706462</v>
       </c>
       <c r="R15" t="n">
-        <v>7426721</v>
+        <v>7426725</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2080,6 +2075,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>5 blommor</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2109,7 +2109,7 @@
         <v>133888839</v>
       </c>
       <c r="B16" t="n">
-        <v>99070</v>
+        <v>99077</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>134102290</v>
       </c>
       <c r="B17" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2305,10 +2305,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134102294</v>
+        <v>134102397</v>
       </c>
       <c r="B18" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>706878</v>
+        <v>706868</v>
       </c>
       <c r="R18" t="n">
-        <v>7426778</v>
+        <v>7426681</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2402,10 +2402,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134102397</v>
+        <v>134102294</v>
       </c>
       <c r="B19" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2437,10 +2437,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>706868</v>
+        <v>706878</v>
       </c>
       <c r="R19" t="n">
-        <v>7426681</v>
+        <v>7426778</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2502,7 +2502,7 @@
         <v>134102309</v>
       </c>
       <c r="B20" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
         <v>134102321</v>
       </c>
       <c r="B21" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>134102307</v>
       </c>
       <c r="B22" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2790,10 +2790,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134102313</v>
+        <v>134102293</v>
       </c>
       <c r="B23" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2825,10 +2825,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>706912</v>
+        <v>706890</v>
       </c>
       <c r="R23" t="n">
-        <v>7426790</v>
+        <v>7426773</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -2887,10 +2887,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134102293</v>
+        <v>134102313</v>
       </c>
       <c r="B24" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2922,10 +2922,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>706890</v>
+        <v>706912</v>
       </c>
       <c r="R24" t="n">
-        <v>7426773</v>
+        <v>7426790</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -2987,7 +2987,7 @@
         <v>134102329</v>
       </c>
       <c r="B25" t="n">
-        <v>99070</v>
+        <v>99077</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         <v>134102319</v>
       </c>
       <c r="B26" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3183,10 +3183,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134102296</v>
+        <v>134102298</v>
       </c>
       <c r="B27" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3218,10 +3218,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>706851</v>
+        <v>706810</v>
       </c>
       <c r="R27" t="n">
-        <v>7426782</v>
+        <v>7426802</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3280,10 +3280,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134102298</v>
+        <v>134102296</v>
       </c>
       <c r="B28" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3315,10 +3315,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>706810</v>
+        <v>706851</v>
       </c>
       <c r="R28" t="n">
-        <v>7426802</v>
+        <v>7426782</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -3377,10 +3377,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134102323</v>
+        <v>134102305</v>
       </c>
       <c r="B29" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>706967</v>
+        <v>706852</v>
       </c>
       <c r="R29" t="n">
-        <v>7426729</v>
+        <v>7426799</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3442,12 +3442,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3474,10 +3474,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134102305</v>
+        <v>134102323</v>
       </c>
       <c r="B30" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3509,10 +3509,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>706852</v>
+        <v>706967</v>
       </c>
       <c r="R30" t="n">
-        <v>7426799</v>
+        <v>7426729</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3539,12 +3539,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3574,7 +3574,7 @@
         <v>134102318</v>
       </c>
       <c r="B31" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>134102317</v>
       </c>
       <c r="B32" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3765,10 +3765,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134102291</v>
+        <v>134102297</v>
       </c>
       <c r="B33" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3800,10 +3800,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>706899</v>
+        <v>706834</v>
       </c>
       <c r="R33" t="n">
-        <v>7426771</v>
+        <v>7426787</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -3862,10 +3862,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134102297</v>
+        <v>134102291</v>
       </c>
       <c r="B34" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3897,10 +3897,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>706834</v>
+        <v>706899</v>
       </c>
       <c r="R34" t="n">
-        <v>7426787</v>
+        <v>7426771</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -3959,10 +3959,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134102299</v>
+        <v>134102304</v>
       </c>
       <c r="B35" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3994,10 +3994,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>706809</v>
+        <v>706855</v>
       </c>
       <c r="R35" t="n">
-        <v>7426819</v>
+        <v>7426811</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -4056,10 +4056,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134102304</v>
+        <v>134102299</v>
       </c>
       <c r="B36" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4091,10 +4091,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>706855</v>
+        <v>706809</v>
       </c>
       <c r="R36" t="n">
-        <v>7426811</v>
+        <v>7426819</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4156,7 +4156,7 @@
         <v>134102322</v>
       </c>
       <c r="B37" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4253,7 +4253,7 @@
         <v>134102315</v>
       </c>
       <c r="B38" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4350,7 +4350,7 @@
         <v>134102295</v>
       </c>
       <c r="B39" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>134102288</v>
       </c>
       <c r="B40" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4544,7 +4544,7 @@
         <v>134102310</v>
       </c>
       <c r="B41" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4638,10 +4638,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134102331</v>
+        <v>134102311</v>
       </c>
       <c r="B42" t="n">
-        <v>99070</v>
+        <v>79433</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4649,21 +4649,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>233</v>
+        <v>637</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4673,10 +4673,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>706920</v>
+        <v>706893</v>
       </c>
       <c r="R42" t="n">
-        <v>7426776</v>
+        <v>7426806</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -4709,11 +4709,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>5 blommor</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4740,10 +4735,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134102302</v>
+        <v>134102331</v>
       </c>
       <c r="B43" t="n">
-        <v>79426</v>
+        <v>99077</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4751,21 +4746,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>637</v>
+        <v>233</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4775,10 +4770,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>706816</v>
+        <v>706920</v>
       </c>
       <c r="R43" t="n">
-        <v>7426823</v>
+        <v>7426776</v>
       </c>
       <c r="S43" t="n">
         <v>3</v>
@@ -4811,6 +4806,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>5 blommor</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4837,10 +4837,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134102311</v>
+        <v>134102302</v>
       </c>
       <c r="B44" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4872,10 +4872,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>706893</v>
+        <v>706816</v>
       </c>
       <c r="R44" t="n">
-        <v>7426806</v>
+        <v>7426823</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -4937,7 +4937,7 @@
         <v>134102306</v>
       </c>
       <c r="B45" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>134102332</v>
       </c>
       <c r="B47" t="n">
-        <v>79438</v>
+        <v>79445</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>134102303</v>
       </c>
       <c r="B48" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5322,32 +5322,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134102395</v>
+        <v>134102334</v>
       </c>
       <c r="B49" t="n">
-        <v>79426</v>
+        <v>79445</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>637</v>
+        <v>864</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5357,10 +5357,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>706915</v>
+        <v>706856</v>
       </c>
       <c r="R49" t="n">
-        <v>7426639</v>
+        <v>7426791</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -5419,10 +5419,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134102289</v>
+        <v>134102395</v>
       </c>
       <c r="B50" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5454,10 +5454,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>706941</v>
+        <v>706915</v>
       </c>
       <c r="R50" t="n">
-        <v>7426720</v>
+        <v>7426639</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -5516,32 +5516,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134102334</v>
+        <v>134102292</v>
       </c>
       <c r="B51" t="n">
-        <v>79438</v>
+        <v>79433</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>864</v>
+        <v>637</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5551,10 +5551,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>706856</v>
+        <v>706891</v>
       </c>
       <c r="R51" t="n">
-        <v>7426791</v>
+        <v>7426771</v>
       </c>
       <c r="S51" t="n">
         <v>3</v>
@@ -5613,10 +5613,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134102292</v>
+        <v>134102289</v>
       </c>
       <c r="B52" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5648,10 +5648,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>706891</v>
+        <v>706941</v>
       </c>
       <c r="R52" t="n">
-        <v>7426771</v>
+        <v>7426720</v>
       </c>
       <c r="S52" t="n">
         <v>3</v>
@@ -5710,10 +5710,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134102314</v>
+        <v>134102394</v>
       </c>
       <c r="B53" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5745,10 +5745,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>706925</v>
+        <v>706913</v>
       </c>
       <c r="R53" t="n">
-        <v>7426791</v>
+        <v>7426627</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -5810,7 +5810,7 @@
         <v>134102396</v>
       </c>
       <c r="B54" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5904,10 +5904,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134102394</v>
+        <v>134102320</v>
       </c>
       <c r="B55" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5939,10 +5939,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>706913</v>
+        <v>706960</v>
       </c>
       <c r="R55" t="n">
-        <v>7426627</v>
+        <v>7426760</v>
       </c>
       <c r="S55" t="n">
         <v>3</v>
@@ -6001,10 +6001,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134102312</v>
+        <v>134102314</v>
       </c>
       <c r="B56" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6036,10 +6036,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>706909</v>
+        <v>706925</v>
       </c>
       <c r="R56" t="n">
-        <v>7426793</v>
+        <v>7426791</v>
       </c>
       <c r="S56" t="n">
         <v>3</v>
@@ -6098,10 +6098,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134102320</v>
+        <v>134102312</v>
       </c>
       <c r="B57" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6133,10 +6133,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>706960</v>
+        <v>706909</v>
       </c>
       <c r="R57" t="n">
-        <v>7426760</v>
+        <v>7426793</v>
       </c>
       <c r="S57" t="n">
         <v>3</v>
@@ -6198,7 +6198,7 @@
         <v>134102316</v>
       </c>
       <c r="B58" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6295,7 +6295,7 @@
         <v>134102335</v>
       </c>
       <c r="B59" t="n">
-        <v>83208</v>
+        <v>83215</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6486,32 +6486,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134272878</v>
+        <v>134272886</v>
       </c>
       <c r="B61" t="n">
-        <v>58839</v>
+        <v>79123</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>208249</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6521,10 +6521,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>706913</v>
+        <v>706845</v>
       </c>
       <c r="R61" t="n">
-        <v>7426789</v>
+        <v>7426764</v>
       </c>
       <c r="S61" t="n">
         <v>3</v>
@@ -6586,7 +6586,7 @@
         <v>134272745</v>
       </c>
       <c r="B62" t="n">
-        <v>79885</v>
+        <v>79892</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6680,32 +6680,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>134272886</v>
+        <v>134272878</v>
       </c>
       <c r="B63" t="n">
-        <v>79116</v>
+        <v>58839</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6446</v>
+        <v>208249</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6715,10 +6715,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>706845</v>
+        <v>706913</v>
       </c>
       <c r="R63" t="n">
-        <v>7426764</v>
+        <v>7426789</v>
       </c>
       <c r="S63" t="n">
         <v>3</v>
@@ -6780,7 +6780,7 @@
         <v>134272877</v>
       </c>
       <c r="B64" t="n">
-        <v>79949</v>
+        <v>79956</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6974,7 +6974,7 @@
         <v>134272883</v>
       </c>
       <c r="B66" t="n">
-        <v>101362</v>
+        <v>101369</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>134272751</v>
       </c>
       <c r="B67" t="n">
-        <v>99070</v>
+        <v>99077</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7173,7 +7173,7 @@
         <v>134272754</v>
       </c>
       <c r="B68" t="n">
-        <v>79025</v>
+        <v>79032</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7270,7 +7270,7 @@
         <v>134272749</v>
       </c>
       <c r="B69" t="n">
-        <v>79426</v>
+        <v>79433</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7367,7 +7367,7 @@
         <v>134272741</v>
       </c>
       <c r="B70" t="n">
-        <v>106295</v>
+        <v>106302</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7464,7 +7464,7 @@
         <v>134272744</v>
       </c>
       <c r="B71" t="n">
-        <v>79885</v>
+        <v>79892</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7558,32 +7558,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134272879</v>
+        <v>134272750</v>
       </c>
       <c r="B72" t="n">
-        <v>58839</v>
+        <v>99077</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>208249</v>
+        <v>233</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7593,10 +7593,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>706948</v>
+        <v>706247</v>
       </c>
       <c r="R72" t="n">
-        <v>7426772</v>
+        <v>7426954</v>
       </c>
       <c r="S72" t="n">
         <v>3</v>
@@ -7629,6 +7629,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>4 blommor</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7655,32 +7660,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134272750</v>
+        <v>134272879</v>
       </c>
       <c r="B73" t="n">
-        <v>99070</v>
+        <v>58839</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>233</v>
+        <v>208249</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7690,10 +7695,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>706247</v>
+        <v>706948</v>
       </c>
       <c r="R73" t="n">
-        <v>7426954</v>
+        <v>7426772</v>
       </c>
       <c r="S73" t="n">
         <v>3</v>
@@ -7726,11 +7731,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>4 blommor</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7757,10 +7757,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134272885</v>
+        <v>134272755</v>
       </c>
       <c r="B74" t="n">
-        <v>79116</v>
+        <v>79032</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7768,21 +7768,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6446</v>
+        <v>353</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7792,10 +7792,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>706844</v>
+        <v>706573</v>
       </c>
       <c r="R74" t="n">
-        <v>7426764</v>
+        <v>7426540</v>
       </c>
       <c r="S74" t="n">
         <v>3</v>
@@ -7854,10 +7854,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>134272755</v>
+        <v>134272885</v>
       </c>
       <c r="B75" t="n">
-        <v>79025</v>
+        <v>79123</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7865,21 +7865,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>353</v>
+        <v>6446</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7889,10 +7889,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>706573</v>
+        <v>706844</v>
       </c>
       <c r="R75" t="n">
-        <v>7426540</v>
+        <v>7426764</v>
       </c>
       <c r="S75" t="n">
         <v>3</v>
@@ -7954,7 +7954,7 @@
         <v>134272881</v>
       </c>
       <c r="B76" t="n">
-        <v>101362</v>
+        <v>101369</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>134272876</v>
       </c>
       <c r="B77" t="n">
-        <v>106295</v>
+        <v>106302</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>134272884</v>
       </c>
       <c r="B78" t="n">
-        <v>79116</v>
+        <v>79123</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8242,32 +8242,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>134272753</v>
+        <v>134272882</v>
       </c>
       <c r="B79" t="n">
-        <v>79116</v>
+        <v>101369</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>1365</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8277,10 +8277,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>706836</v>
+        <v>706944</v>
       </c>
       <c r="R79" t="n">
-        <v>7426766</v>
+        <v>7426775</v>
       </c>
       <c r="S79" t="n">
         <v>3</v>
@@ -8339,32 +8339,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>134272882</v>
+        <v>134272753</v>
       </c>
       <c r="B80" t="n">
-        <v>101362</v>
+        <v>79123</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>1365</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8374,10 +8374,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>706944</v>
+        <v>706836</v>
       </c>
       <c r="R80" t="n">
-        <v>7426775</v>
+        <v>7426766</v>
       </c>
       <c r="S80" t="n">
         <v>3</v>
@@ -8439,7 +8439,7 @@
         <v>134272752</v>
       </c>
       <c r="B81" t="n">
-        <v>79117</v>
+        <v>79124</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>

--- a/artfynd/A 55525-2025 artfynd.xlsx
+++ b/artfynd/A 55525-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY81"/>
+  <dimension ref="A1:AY95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90907438</v>
+        <v>133888829</v>
       </c>
       <c r="B2" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99084</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4362</v>
+        <v>233</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Agas, Lu lm</t>
+          <t>Ågåsgielas, Lu lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>706953.1675574451</v>
+        <v>706484</v>
       </c>
       <c r="R2" t="n">
-        <v>7426549.111910723</v>
+        <v>7426734</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-09-22</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-09-22</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2 blommor</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,78 +761,64 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>Olle Finnström</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Charles Campbell</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Charles Campbell</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Statens Fastighetsverk - NVB - Greensway</t>
-        </is>
-      </c>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>90907437</v>
+        <v>133888830</v>
       </c>
       <c r="B3" t="n">
-        <v>89557</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99084</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1588</v>
+        <v>233</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Agas, Lu lm</t>
+          <t>Ågåsgielas, Lu lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>706938.1047705793</v>
+        <v>706475</v>
       </c>
       <c r="R3" t="n">
-        <v>7426555.066284467</v>
+        <v>7426727</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,22 +842,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2019-09-22</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2019-09-22</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>5 blommor</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,35 +863,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>Olle Finnström</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Charles Campbell</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Via Charles Campbell</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Statens Fastighetsverk - NVB - Greensway</t>
-        </is>
-      </c>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133888834</v>
+        <v>133888831</v>
       </c>
       <c r="B4" t="n">
-        <v>99077</v>
+        <v>99084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>706459</v>
+        <v>706466</v>
       </c>
       <c r="R4" t="n">
-        <v>7426728</v>
+        <v>7426731</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -988,6 +950,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>9 blommor</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133888838</v>
+        <v>133888832</v>
       </c>
       <c r="B5" t="n">
-        <v>99077</v>
+        <v>99084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1049,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>706493</v>
+        <v>706457</v>
       </c>
       <c r="R5" t="n">
-        <v>7426724</v>
+        <v>7426725</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1085,6 +1052,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>3 blommor</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,32 +1083,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133888840</v>
+        <v>133888833</v>
       </c>
       <c r="B6" t="n">
-        <v>93264</v>
+        <v>99084</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>233</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1146,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>706935</v>
+        <v>706441</v>
       </c>
       <c r="R6" t="n">
-        <v>7426534</v>
+        <v>7426721</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1208,10 +1180,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133888830</v>
+        <v>133888834</v>
       </c>
       <c r="B7" t="n">
-        <v>99077</v>
+        <v>99084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1243,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>706475</v>
+        <v>706459</v>
       </c>
       <c r="R7" t="n">
-        <v>7426727</v>
+        <v>7426728</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1279,11 +1251,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>5 blommor</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1310,10 +1277,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133888832</v>
+        <v>133888835</v>
       </c>
       <c r="B8" t="n">
-        <v>99077</v>
+        <v>99084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1345,7 +1312,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>706457</v>
+        <v>706462</v>
       </c>
       <c r="R8" t="n">
         <v>7426725</v>
@@ -1385,7 +1352,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>3 blommor</t>
+          <t>5 blommor</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1412,10 +1379,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133888831</v>
+        <v>133888836</v>
       </c>
       <c r="B9" t="n">
-        <v>99077</v>
+        <v>99084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1447,10 +1414,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>706466</v>
+        <v>706505</v>
       </c>
       <c r="R9" t="n">
-        <v>7426731</v>
+        <v>7426733</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1483,11 +1450,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>9 blommor</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1514,10 +1476,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133888836</v>
+        <v>133888837</v>
       </c>
       <c r="B10" t="n">
-        <v>99077</v>
+        <v>99084</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1549,10 +1511,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>706505</v>
+        <v>706498</v>
       </c>
       <c r="R10" t="n">
-        <v>7426733</v>
+        <v>7426729</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1611,32 +1573,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133888827</v>
+        <v>133888838</v>
       </c>
       <c r="B11" t="n">
-        <v>57162</v>
+        <v>99084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>233</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1646,10 +1608,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>706811</v>
+        <v>706493</v>
       </c>
       <c r="R11" t="n">
-        <v>7426646</v>
+        <v>7426724</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1708,10 +1670,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133888837</v>
+        <v>133888839</v>
       </c>
       <c r="B12" t="n">
-        <v>99077</v>
+        <v>99084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1743,10 +1705,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>706498</v>
+        <v>706491</v>
       </c>
       <c r="R12" t="n">
-        <v>7426729</v>
+        <v>7426731</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1779,6 +1741,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Två blommor</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1805,10 +1772,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133888829</v>
+        <v>134102329</v>
       </c>
       <c r="B13" t="n">
-        <v>99077</v>
+        <v>99084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1840,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>706484</v>
+        <v>706942</v>
       </c>
       <c r="R13" t="n">
-        <v>7426734</v>
+        <v>7426762</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -1870,17 +1837,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>2 blommor</t>
+          <t>En blomma</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1907,10 +1874,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133888833</v>
+        <v>134102330</v>
       </c>
       <c r="B14" t="n">
-        <v>99077</v>
+        <v>99084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1942,10 +1909,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>706441</v>
+        <v>706920</v>
       </c>
       <c r="R14" t="n">
-        <v>7426721</v>
+        <v>7426776</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -1972,12 +1939,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2004,10 +1971,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133888835</v>
+        <v>134272750</v>
       </c>
       <c r="B15" t="n">
-        <v>99077</v>
+        <v>99084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2039,10 +2006,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>706462</v>
+        <v>706247</v>
       </c>
       <c r="R15" t="n">
-        <v>7426725</v>
+        <v>7426954</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2069,17 +2036,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>5 blommor</t>
+          <t>4 blommor</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2106,10 +2073,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133888839</v>
+        <v>134272751</v>
       </c>
       <c r="B16" t="n">
-        <v>99077</v>
+        <v>99084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2141,10 +2108,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>706491</v>
+        <v>706204</v>
       </c>
       <c r="R16" t="n">
-        <v>7426731</v>
+        <v>7426971</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2171,17 +2138,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Två blommor</t>
+          <t>1 blommande</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2208,32 +2175,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134102290</v>
+        <v>134272754</v>
       </c>
       <c r="B17" t="n">
-        <v>79433</v>
+        <v>79039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>637</v>
+        <v>353</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2243,10 +2210,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>706918</v>
+        <v>706491</v>
       </c>
       <c r="R17" t="n">
-        <v>7426756</v>
+        <v>7426611</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2273,12 +2240,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2305,32 +2272,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134102397</v>
+        <v>134272755</v>
       </c>
       <c r="B18" t="n">
-        <v>79433</v>
+        <v>79039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>637</v>
+        <v>353</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2340,10 +2307,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>706868</v>
+        <v>706573</v>
       </c>
       <c r="R18" t="n">
-        <v>7426681</v>
+        <v>7426540</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2370,12 +2337,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2402,10 +2369,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134102294</v>
+        <v>134102288</v>
       </c>
       <c r="B19" t="n">
-        <v>79433</v>
+        <v>79440</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2437,10 +2404,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>706878</v>
+        <v>706968</v>
       </c>
       <c r="R19" t="n">
-        <v>7426778</v>
+        <v>7426698</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2499,10 +2466,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134102309</v>
+        <v>134102289</v>
       </c>
       <c r="B20" t="n">
-        <v>79433</v>
+        <v>79440</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2534,10 +2501,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>706885</v>
+        <v>706941</v>
       </c>
       <c r="R20" t="n">
-        <v>7426802</v>
+        <v>7426720</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2596,10 +2563,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134102321</v>
+        <v>134102290</v>
       </c>
       <c r="B21" t="n">
-        <v>79433</v>
+        <v>79440</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2631,10 +2598,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>706970</v>
+        <v>706918</v>
       </c>
       <c r="R21" t="n">
-        <v>7426748</v>
+        <v>7426756</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2693,10 +2660,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134102307</v>
+        <v>134102291</v>
       </c>
       <c r="B22" t="n">
-        <v>79433</v>
+        <v>79440</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2728,10 +2695,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>706875</v>
+        <v>706899</v>
       </c>
       <c r="R22" t="n">
-        <v>7426805</v>
+        <v>7426771</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -2790,10 +2757,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134102293</v>
+        <v>134102292</v>
       </c>
       <c r="B23" t="n">
-        <v>79433</v>
+        <v>79440</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2825,10 +2792,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>706890</v>
+        <v>706891</v>
       </c>
       <c r="R23" t="n">
-        <v>7426773</v>
+        <v>7426771</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -2887,10 +2854,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134102313</v>
+        <v>134102293</v>
       </c>
       <c r="B24" t="n">
-        <v>79433</v>
+        <v>79440</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2922,10 +2889,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>706912</v>
+        <v>706890</v>
       </c>
       <c r="R24" t="n">
-        <v>7426790</v>
+        <v>7426773</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -2984,10 +2951,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134102329</v>
+        <v>134102294</v>
       </c>
       <c r="B25" t="n">
-        <v>99077</v>
+        <v>79440</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2995,21 +2962,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>233</v>
+        <v>637</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3019,10 +2986,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>706942</v>
+        <v>706878</v>
       </c>
       <c r="R25" t="n">
-        <v>7426762</v>
+        <v>7426778</v>
       </c>
       <c r="S25" t="n">
         <v>3</v>
@@ -3055,11 +3022,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>En blomma</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3086,10 +3048,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134102319</v>
+        <v>134102295</v>
       </c>
       <c r="B26" t="n">
-        <v>79433</v>
+        <v>79440</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3121,10 +3083,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>706952</v>
+        <v>706859</v>
       </c>
       <c r="R26" t="n">
-        <v>7426764</v>
+        <v>7426782</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3183,10 +3145,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134102298</v>
+        <v>134102296</v>
       </c>
       <c r="B27" t="n">
-        <v>79433</v>
+        <v>79440</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3218,10 +3180,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>706810</v>
+        <v>706851</v>
       </c>
       <c r="R27" t="n">
-        <v>7426802</v>
+        <v>7426782</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3280,10 +3242,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134102296</v>
+        <v>134102297</v>
       </c>
       <c r="B28" t="n">
-        <v>79433</v>
+        <v>79440</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3315,10 +3277,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>706851</v>
+        <v>706834</v>
       </c>
       <c r="R28" t="n">
-        <v>7426782</v>
+        <v>7426787</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -3377,10 +3339,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134102305</v>
+        <v>134102298</v>
       </c>
       <c r="B29" t="n">
-        <v>79433</v>
+        <v>79440</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3412,10 +3374,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>706852</v>
+        <v>706810</v>
       </c>
       <c r="R29" t="n">
-        <v>7426799</v>
+        <v>7426802</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3474,10 +3436,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134102323</v>
+        <v>134102299</v>
       </c>
       <c r="B30" t="n">
-        <v>79433</v>
+        <v>79440</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3509,10 +3471,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>706967</v>
+        <v>706809</v>
       </c>
       <c r="R30" t="n">
-        <v>7426729</v>
+        <v>7426819</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3539,12 +3501,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3571,10 +3533,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134102318</v>
+        <v>134102300</v>
       </c>
       <c r="B31" t="n">
-        <v>79433</v>
+        <v>79440</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3606,10 +3568,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>706944</v>
+        <v>706796</v>
       </c>
       <c r="R31" t="n">
-        <v>7426769</v>
+        <v>7426839</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -3668,10 +3630,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134102317</v>
+        <v>134102301</v>
       </c>
       <c r="B32" t="n">
-        <v>79433</v>
+        <v>79440</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3703,10 +3665,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>706934</v>
+        <v>706805</v>
       </c>
       <c r="R32" t="n">
-        <v>7426777</v>
+        <v>7426845</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
@@ -3765,10 +3727,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134102297</v>
+        <v>134102302</v>
       </c>
       <c r="B33" t="n">
-        <v>79433</v>
+        <v>79440</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3800,10 +3762,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>706834</v>
+        <v>706816</v>
       </c>
       <c r="R33" t="n">
-        <v>7426787</v>
+        <v>7426823</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -3862,10 +3824,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134102291</v>
+        <v>134102303</v>
       </c>
       <c r="B34" t="n">
-        <v>79433</v>
+        <v>79440</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3897,10 +3859,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>706899</v>
+        <v>706841</v>
       </c>
       <c r="R34" t="n">
-        <v>7426771</v>
+        <v>7426814</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -3962,7 +3924,7 @@
         <v>134102304</v>
       </c>
       <c r="B35" t="n">
-        <v>79433</v>
+        <v>79440</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4056,10 +4018,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134102299</v>
+        <v>134102305</v>
       </c>
       <c r="B36" t="n">
-        <v>79433</v>
+        <v>79440</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4091,10 +4053,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>706809</v>
+        <v>706852</v>
       </c>
       <c r="R36" t="n">
-        <v>7426819</v>
+        <v>7426799</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4153,10 +4115,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134102322</v>
+        <v>134102306</v>
       </c>
       <c r="B37" t="n">
-        <v>79433</v>
+        <v>79440</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4188,10 +4150,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>706963</v>
+        <v>706863</v>
       </c>
       <c r="R37" t="n">
-        <v>7426740</v>
+        <v>7426795</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4218,12 +4180,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4250,10 +4212,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134102315</v>
+        <v>134102307</v>
       </c>
       <c r="B38" t="n">
-        <v>79433</v>
+        <v>79440</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4285,10 +4247,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>706920</v>
+        <v>706875</v>
       </c>
       <c r="R38" t="n">
-        <v>7426784</v>
+        <v>7426805</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4347,10 +4309,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134102295</v>
+        <v>134102309</v>
       </c>
       <c r="B39" t="n">
-        <v>79433</v>
+        <v>79440</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4382,10 +4344,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>706859</v>
+        <v>706885</v>
       </c>
       <c r="R39" t="n">
-        <v>7426782</v>
+        <v>7426802</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4444,10 +4406,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134102288</v>
+        <v>134102310</v>
       </c>
       <c r="B40" t="n">
-        <v>79433</v>
+        <v>79440</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4479,10 +4441,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>706968</v>
+        <v>706887</v>
       </c>
       <c r="R40" t="n">
-        <v>7426698</v>
+        <v>7426800</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -4541,10 +4503,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134102310</v>
+        <v>134102311</v>
       </c>
       <c r="B41" t="n">
-        <v>79433</v>
+        <v>79440</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4576,10 +4538,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>706887</v>
+        <v>706893</v>
       </c>
       <c r="R41" t="n">
-        <v>7426800</v>
+        <v>7426806</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
@@ -4638,10 +4600,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134102311</v>
+        <v>134102312</v>
       </c>
       <c r="B42" t="n">
-        <v>79433</v>
+        <v>79440</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4673,10 +4635,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>706893</v>
+        <v>706909</v>
       </c>
       <c r="R42" t="n">
-        <v>7426806</v>
+        <v>7426793</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -4735,10 +4697,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134102331</v>
+        <v>134102313</v>
       </c>
       <c r="B43" t="n">
-        <v>99077</v>
+        <v>79440</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4746,21 +4708,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>233</v>
+        <v>637</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4770,10 +4732,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>706920</v>
+        <v>706912</v>
       </c>
       <c r="R43" t="n">
-        <v>7426776</v>
+        <v>7426790</v>
       </c>
       <c r="S43" t="n">
         <v>3</v>
@@ -4806,11 +4768,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>5 blommor</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4837,10 +4794,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134102302</v>
+        <v>134102314</v>
       </c>
       <c r="B44" t="n">
-        <v>79433</v>
+        <v>79440</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4872,10 +4829,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>706816</v>
+        <v>706925</v>
       </c>
       <c r="R44" t="n">
-        <v>7426823</v>
+        <v>7426791</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -4934,10 +4891,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134102306</v>
+        <v>134102315</v>
       </c>
       <c r="B45" t="n">
-        <v>79433</v>
+        <v>79440</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4969,10 +4926,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>706863</v>
+        <v>706920</v>
       </c>
       <c r="R45" t="n">
-        <v>7426795</v>
+        <v>7426784</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -5031,32 +4988,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134102284</v>
+        <v>134102316</v>
       </c>
       <c r="B46" t="n">
-        <v>57975</v>
+        <v>79440</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>637</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5066,10 +5023,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>706890</v>
+        <v>706925</v>
       </c>
       <c r="R46" t="n">
-        <v>7426773</v>
+        <v>7426793</v>
       </c>
       <c r="S46" t="n">
         <v>3</v>
@@ -5128,32 +5085,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134102332</v>
+        <v>134102317</v>
       </c>
       <c r="B47" t="n">
-        <v>79445</v>
+        <v>79440</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>864</v>
+        <v>637</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5163,10 +5120,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>706805</v>
+        <v>706934</v>
       </c>
       <c r="R47" t="n">
-        <v>7426821</v>
+        <v>7426777</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
@@ -5225,10 +5182,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134102303</v>
+        <v>134102318</v>
       </c>
       <c r="B48" t="n">
-        <v>79433</v>
+        <v>79440</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5260,10 +5217,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>706841</v>
+        <v>706944</v>
       </c>
       <c r="R48" t="n">
-        <v>7426814</v>
+        <v>7426769</v>
       </c>
       <c r="S48" t="n">
         <v>3</v>
@@ -5322,32 +5279,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134102334</v>
+        <v>134102319</v>
       </c>
       <c r="B49" t="n">
-        <v>79445</v>
+        <v>79440</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>864</v>
+        <v>637</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5357,10 +5314,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>706856</v>
+        <v>706952</v>
       </c>
       <c r="R49" t="n">
-        <v>7426791</v>
+        <v>7426764</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -5419,10 +5376,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134102395</v>
+        <v>134102320</v>
       </c>
       <c r="B50" t="n">
-        <v>79433</v>
+        <v>79440</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5454,10 +5411,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>706915</v>
+        <v>706960</v>
       </c>
       <c r="R50" t="n">
-        <v>7426639</v>
+        <v>7426760</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -5516,10 +5473,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134102292</v>
+        <v>134102321</v>
       </c>
       <c r="B51" t="n">
-        <v>79433</v>
+        <v>79440</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5551,10 +5508,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>706891</v>
+        <v>706970</v>
       </c>
       <c r="R51" t="n">
-        <v>7426771</v>
+        <v>7426748</v>
       </c>
       <c r="S51" t="n">
         <v>3</v>
@@ -5613,10 +5570,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134102289</v>
+        <v>134102322</v>
       </c>
       <c r="B52" t="n">
-        <v>79433</v>
+        <v>79440</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5648,10 +5605,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>706941</v>
+        <v>706963</v>
       </c>
       <c r="R52" t="n">
-        <v>7426720</v>
+        <v>7426740</v>
       </c>
       <c r="S52" t="n">
         <v>3</v>
@@ -5678,12 +5635,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5710,10 +5667,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134102394</v>
+        <v>134102323</v>
       </c>
       <c r="B53" t="n">
-        <v>79433</v>
+        <v>79440</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5745,10 +5702,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>706913</v>
+        <v>706967</v>
       </c>
       <c r="R53" t="n">
-        <v>7426627</v>
+        <v>7426729</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -5775,12 +5732,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5807,10 +5764,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134102396</v>
+        <v>134102324</v>
       </c>
       <c r="B54" t="n">
-        <v>79433</v>
+        <v>79440</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5842,10 +5799,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>706917</v>
+        <v>706968</v>
       </c>
       <c r="R54" t="n">
-        <v>7426646</v>
+        <v>7426683</v>
       </c>
       <c r="S54" t="n">
         <v>3</v>
@@ -5872,12 +5829,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -5904,10 +5861,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134102320</v>
+        <v>134102325</v>
       </c>
       <c r="B55" t="n">
-        <v>79433</v>
+        <v>79440</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5939,10 +5896,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>706960</v>
+        <v>706955</v>
       </c>
       <c r="R55" t="n">
-        <v>7426760</v>
+        <v>7426674</v>
       </c>
       <c r="S55" t="n">
         <v>3</v>
@@ -5969,12 +5926,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6001,10 +5958,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134102314</v>
+        <v>134102326</v>
       </c>
       <c r="B56" t="n">
-        <v>79433</v>
+        <v>79440</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6036,10 +5993,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>706925</v>
+        <v>706941</v>
       </c>
       <c r="R56" t="n">
-        <v>7426791</v>
+        <v>7426672</v>
       </c>
       <c r="S56" t="n">
         <v>3</v>
@@ -6066,12 +6023,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6098,10 +6055,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134102312</v>
+        <v>134102327</v>
       </c>
       <c r="B57" t="n">
-        <v>79433</v>
+        <v>79440</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6133,10 +6090,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>706909</v>
+        <v>706944</v>
       </c>
       <c r="R57" t="n">
-        <v>7426793</v>
+        <v>7426692</v>
       </c>
       <c r="S57" t="n">
         <v>3</v>
@@ -6163,12 +6120,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6195,10 +6152,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134102316</v>
+        <v>134102328</v>
       </c>
       <c r="B58" t="n">
-        <v>79433</v>
+        <v>79440</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6230,10 +6187,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>706925</v>
+        <v>706937</v>
       </c>
       <c r="R58" t="n">
-        <v>7426793</v>
+        <v>7426690</v>
       </c>
       <c r="S58" t="n">
         <v>3</v>
@@ -6260,12 +6217,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6292,32 +6249,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134102335</v>
+        <v>134102394</v>
       </c>
       <c r="B59" t="n">
-        <v>83215</v>
+        <v>79440</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1312</v>
+        <v>637</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6327,10 +6284,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>706856</v>
+        <v>706913</v>
       </c>
       <c r="R59" t="n">
-        <v>7426794</v>
+        <v>7426627</v>
       </c>
       <c r="S59" t="n">
         <v>3</v>
@@ -6389,32 +6346,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134102285</v>
+        <v>134102395</v>
       </c>
       <c r="B60" t="n">
-        <v>57975</v>
+        <v>79440</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>637</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6424,10 +6381,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>706809</v>
+        <v>706915</v>
       </c>
       <c r="R60" t="n">
-        <v>7426804</v>
+        <v>7426639</v>
       </c>
       <c r="S60" t="n">
         <v>3</v>
@@ -6486,32 +6443,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134272886</v>
+        <v>134102396</v>
       </c>
       <c r="B61" t="n">
-        <v>79123</v>
+        <v>79440</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6446</v>
+        <v>637</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6521,10 +6478,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>706845</v>
+        <v>706917</v>
       </c>
       <c r="R61" t="n">
-        <v>7426764</v>
+        <v>7426646</v>
       </c>
       <c r="S61" t="n">
         <v>3</v>
@@ -6551,12 +6508,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6583,32 +6540,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134272745</v>
+        <v>134102397</v>
       </c>
       <c r="B62" t="n">
-        <v>79892</v>
+        <v>79440</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229830</v>
+        <v>637</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Späd brosklav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Ramalina dilacerata</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6618,10 +6575,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>706278</v>
+        <v>706868</v>
       </c>
       <c r="R62" t="n">
-        <v>7426914</v>
+        <v>7426681</v>
       </c>
       <c r="S62" t="n">
         <v>3</v>
@@ -6648,12 +6605,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6680,32 +6637,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>134272878</v>
+        <v>134272749</v>
       </c>
       <c r="B63" t="n">
-        <v>58839</v>
+        <v>79440</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>208249</v>
+        <v>637</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6715,10 +6672,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>706913</v>
+        <v>706238</v>
       </c>
       <c r="R63" t="n">
-        <v>7426789</v>
+        <v>7426848</v>
       </c>
       <c r="S63" t="n">
         <v>3</v>
@@ -6777,10 +6734,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>134272877</v>
+        <v>134102332</v>
       </c>
       <c r="B64" t="n">
-        <v>79956</v>
+        <v>79452</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6788,21 +6745,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229821</v>
+        <v>864</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6812,10 +6769,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>706475</v>
+        <v>706805</v>
       </c>
       <c r="R64" t="n">
-        <v>7426738</v>
+        <v>7426821</v>
       </c>
       <c r="S64" t="n">
         <v>3</v>
@@ -6842,12 +6799,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6874,32 +6831,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>134272742</v>
+        <v>134102333</v>
       </c>
       <c r="B65" t="n">
-        <v>58839</v>
+        <v>79452</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>208249</v>
+        <v>864</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6909,10 +6866,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>706447</v>
+        <v>706797</v>
       </c>
       <c r="R65" t="n">
-        <v>7426815</v>
+        <v>7426837</v>
       </c>
       <c r="S65" t="n">
         <v>3</v>
@@ -6939,12 +6896,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6971,32 +6928,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>134272883</v>
+        <v>134102334</v>
       </c>
       <c r="B66" t="n">
-        <v>101369</v>
+        <v>79452</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1365</v>
+        <v>864</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7006,10 +6963,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>706961</v>
+        <v>706856</v>
       </c>
       <c r="R66" t="n">
-        <v>7426774</v>
+        <v>7426791</v>
       </c>
       <c r="S66" t="n">
         <v>3</v>
@@ -7036,12 +6993,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7068,32 +7025,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>134272751</v>
+        <v>134272887</v>
       </c>
       <c r="B67" t="n">
-        <v>99077</v>
+        <v>79452</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>233</v>
+        <v>864</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7103,10 +7060,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>706204</v>
+        <v>706763</v>
       </c>
       <c r="R67" t="n">
-        <v>7426971</v>
+        <v>7426802</v>
       </c>
       <c r="S67" t="n">
         <v>3</v>
@@ -7139,11 +7096,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>1 blommande</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7170,10 +7122,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>134272754</v>
+        <v>134102335</v>
       </c>
       <c r="B68" t="n">
-        <v>79032</v>
+        <v>83222</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7181,21 +7133,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>353</v>
+        <v>1312</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7205,10 +7157,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>706491</v>
+        <v>706856</v>
       </c>
       <c r="R68" t="n">
-        <v>7426611</v>
+        <v>7426794</v>
       </c>
       <c r="S68" t="n">
         <v>3</v>
@@ -7235,12 +7187,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7267,32 +7219,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134272749</v>
+        <v>134102336</v>
       </c>
       <c r="B69" t="n">
-        <v>79433</v>
+        <v>83222</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>637</v>
+        <v>1312</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7302,10 +7254,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>706238</v>
+        <v>706796</v>
       </c>
       <c r="R69" t="n">
-        <v>7426848</v>
+        <v>7426839</v>
       </c>
       <c r="S69" t="n">
         <v>3</v>
@@ -7332,12 +7284,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7364,10 +7316,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134272741</v>
+        <v>134272881</v>
       </c>
       <c r="B70" t="n">
-        <v>106302</v>
+        <v>101376</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7375,21 +7327,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>221725</v>
+        <v>1365</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7399,10 +7351,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>706510</v>
+        <v>706837</v>
       </c>
       <c r="R70" t="n">
-        <v>7426625</v>
+        <v>7426798</v>
       </c>
       <c r="S70" t="n">
         <v>3</v>
@@ -7461,10 +7413,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>134272744</v>
+        <v>134272882</v>
       </c>
       <c r="B71" t="n">
-        <v>79892</v>
+        <v>101376</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7472,21 +7424,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229830</v>
+        <v>1365</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Späd brosklav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Ramalina dilacerata</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7496,10 +7448,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>706239</v>
+        <v>706944</v>
       </c>
       <c r="R71" t="n">
-        <v>7426846</v>
+        <v>7426775</v>
       </c>
       <c r="S71" t="n">
         <v>3</v>
@@ -7558,32 +7510,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134272750</v>
+        <v>134272883</v>
       </c>
       <c r="B72" t="n">
-        <v>99077</v>
+        <v>101376</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>233</v>
+        <v>1365</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7593,10 +7545,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>706247</v>
+        <v>706961</v>
       </c>
       <c r="R72" t="n">
-        <v>7426954</v>
+        <v>7426774</v>
       </c>
       <c r="S72" t="n">
         <v>3</v>
@@ -7629,11 +7581,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>4 blommor</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7660,48 +7607,48 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134272879</v>
+        <v>90907437</v>
       </c>
       <c r="B73" t="n">
-        <v>58839</v>
+        <v>92097</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>208249</v>
+        <v>1588</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Ågåsgielas, Lu lm</t>
+          <t>Agas, Lu lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>706948</v>
+        <v>706938</v>
       </c>
       <c r="R73" t="n">
-        <v>7426772</v>
+        <v>7426555</v>
       </c>
       <c r="S73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -7725,12 +7672,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2019-09-22</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2019-09-22</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -7741,26 +7688,35 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AS73" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Charles Campbell</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr"/>
+          <t>Via Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr">
+        <is>
+          <t>Statens Fastighetsverk - NVB - Greensway</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134272755</v>
+        <v>90907438</v>
       </c>
       <c r="B74" t="n">
-        <v>79032</v>
+        <v>93191</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7768,37 +7724,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>353</v>
+        <v>4362</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Ågåsgielas, Lu lm</t>
+          <t>Agas, Lu lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>706573</v>
+        <v>706953</v>
       </c>
       <c r="R74" t="n">
-        <v>7426540</v>
+        <v>7426549</v>
       </c>
       <c r="S74" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -7822,12 +7778,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2019-09-22</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2019-09-22</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -7838,26 +7794,35 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AS74" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Charles Campbell</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr"/>
+          <t>Via Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr">
+        <is>
+          <t>Statens Fastighetsverk - NVB - Greensway</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>134272885</v>
+        <v>133888840</v>
       </c>
       <c r="B75" t="n">
-        <v>79123</v>
+        <v>93271</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7865,21 +7830,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7889,10 +7854,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>706844</v>
+        <v>706935</v>
       </c>
       <c r="R75" t="n">
-        <v>7426764</v>
+        <v>7426534</v>
       </c>
       <c r="S75" t="n">
         <v>3</v>
@@ -7919,12 +7884,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -7951,32 +7916,32 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134272881</v>
+        <v>134272753</v>
       </c>
       <c r="B76" t="n">
-        <v>101369</v>
+        <v>79130</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1365</v>
+        <v>6446</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7986,10 +7951,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>706837</v>
+        <v>706836</v>
       </c>
       <c r="R76" t="n">
-        <v>7426798</v>
+        <v>7426766</v>
       </c>
       <c r="S76" t="n">
         <v>3</v>
@@ -8048,32 +8013,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>134272876</v>
+        <v>134272884</v>
       </c>
       <c r="B77" t="n">
-        <v>106302</v>
+        <v>79130</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221725</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8083,10 +8048,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>706861</v>
+        <v>706477</v>
       </c>
       <c r="R77" t="n">
-        <v>7426790</v>
+        <v>7426743</v>
       </c>
       <c r="S77" t="n">
         <v>3</v>
@@ -8145,10 +8110,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>134272884</v>
+        <v>134272885</v>
       </c>
       <c r="B78" t="n">
-        <v>79123</v>
+        <v>79130</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8180,10 +8145,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>706477</v>
+        <v>706844</v>
       </c>
       <c r="R78" t="n">
-        <v>7426743</v>
+        <v>7426764</v>
       </c>
       <c r="S78" t="n">
         <v>3</v>
@@ -8242,32 +8207,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>134272882</v>
+        <v>134272886</v>
       </c>
       <c r="B79" t="n">
-        <v>101369</v>
+        <v>79130</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1365</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8277,10 +8242,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>706944</v>
+        <v>706845</v>
       </c>
       <c r="R79" t="n">
-        <v>7426775</v>
+        <v>7426764</v>
       </c>
       <c r="S79" t="n">
         <v>3</v>
@@ -8339,10 +8304,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>134272753</v>
+        <v>134102284</v>
       </c>
       <c r="B80" t="n">
-        <v>79123</v>
+        <v>57975</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8350,21 +8315,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8374,10 +8339,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>706836</v>
+        <v>706890</v>
       </c>
       <c r="R80" t="n">
-        <v>7426766</v>
+        <v>7426773</v>
       </c>
       <c r="S80" t="n">
         <v>3</v>
@@ -8404,12 +8369,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8436,10 +8401,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>134272752</v>
+        <v>134102285</v>
       </c>
       <c r="B81" t="n">
-        <v>79124</v>
+        <v>57975</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8447,21 +8412,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8471,10 +8436,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>706597</v>
+        <v>706809</v>
       </c>
       <c r="R81" t="n">
-        <v>7426486</v>
+        <v>7426804</v>
       </c>
       <c r="S81" t="n">
         <v>3</v>
@@ -8501,12 +8466,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8530,6 +8495,1374 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>134102286</v>
+      </c>
+      <c r="B82" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>706976</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7426669</v>
+      </c>
+      <c r="S82" t="n">
+        <v>3</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>133888827</v>
+      </c>
+      <c r="B83" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>706811</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7426646</v>
+      </c>
+      <c r="S83" t="n">
+        <v>3</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>134102287</v>
+      </c>
+      <c r="B84" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>706951</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7426689</v>
+      </c>
+      <c r="S84" t="n">
+        <v>3</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>134272743</v>
+      </c>
+      <c r="B85" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>706576</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7426767</v>
+      </c>
+      <c r="S85" t="n">
+        <v>3</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Otroligt mycket spillning på stenkulle</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>134272742</v>
+      </c>
+      <c r="B86" t="n">
+        <v>58839</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>706447</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7426815</v>
+      </c>
+      <c r="S86" t="n">
+        <v>3</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>134272878</v>
+      </c>
+      <c r="B87" t="n">
+        <v>58839</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>706913</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7426789</v>
+      </c>
+      <c r="S87" t="n">
+        <v>3</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>134272879</v>
+      </c>
+      <c r="B88" t="n">
+        <v>58839</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>706948</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7426772</v>
+      </c>
+      <c r="S88" t="n">
+        <v>3</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>134272741</v>
+      </c>
+      <c r="B89" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>706510</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7426625</v>
+      </c>
+      <c r="S89" t="n">
+        <v>3</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>134272876</v>
+      </c>
+      <c r="B90" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>706861</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7426790</v>
+      </c>
+      <c r="S90" t="n">
+        <v>3</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>133888828</v>
+      </c>
+      <c r="B91" t="n">
+        <v>104707</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>706508</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7426811</v>
+      </c>
+      <c r="S91" t="n">
+        <v>3</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>134272752</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>706597</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7426486</v>
+      </c>
+      <c r="S92" t="n">
+        <v>3</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>134272877</v>
+      </c>
+      <c r="B93" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>706475</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7426738</v>
+      </c>
+      <c r="S93" t="n">
+        <v>3</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>134272744</v>
+      </c>
+      <c r="B94" t="n">
+        <v>79899</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>229830</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Späd brosklav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Ramalina dilacerata</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>706239</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7426846</v>
+      </c>
+      <c r="S94" t="n">
+        <v>3</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>134272745</v>
+      </c>
+      <c r="B95" t="n">
+        <v>79899</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>229830</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Späd brosklav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Ramalina dilacerata</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>706278</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7426914</v>
+      </c>
+      <c r="S95" t="n">
+        <v>3</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 55525-2025 artfynd.xlsx
+++ b/artfynd/A 55525-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY95"/>
+  <dimension ref="A1:AZ95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133888829</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133888830</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133888831</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133888832</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133888833</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133888834</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1376,6 +1411,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133888835</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1473,6 +1513,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133888836</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1570,6 +1615,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133888837</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1667,6 +1717,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133888838</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1769,6 +1824,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133888839</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1871,6 +1931,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102329</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1968,6 +2033,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102330</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2070,6 +2140,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272750</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2172,6 +2247,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272751</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2269,6 +2349,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272754</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2366,6 +2451,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272755</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2463,6 +2553,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102288</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2560,6 +2655,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102289</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2657,6 +2757,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102290</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2754,6 +2859,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102291</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2851,6 +2961,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102292</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2948,6 +3063,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102293</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3045,6 +3165,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102294</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3142,6 +3267,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102295</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3239,6 +3369,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102296</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3336,6 +3471,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102297</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3433,6 +3573,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102298</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3530,6 +3675,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102299</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3627,6 +3777,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102300</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3724,6 +3879,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102301</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3821,6 +3981,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102302</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3918,6 +4083,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102303</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4015,6 +4185,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102304</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4112,6 +4287,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102305</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4209,6 +4389,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102306</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4306,6 +4491,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102307</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4403,6 +4593,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102309</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4500,6 +4695,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102310</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4597,6 +4797,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102311</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4694,6 +4899,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102312</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4791,6 +5001,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102313</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4888,6 +5103,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102314</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4985,6 +5205,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102315</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5082,6 +5307,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102316</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5179,6 +5409,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102317</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5276,6 +5511,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102318</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5373,6 +5613,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102319</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5470,6 +5715,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102320</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5567,6 +5817,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102321</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5664,6 +5919,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102322</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5761,6 +6021,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102323</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5858,6 +6123,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102324</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5955,6 +6225,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102325</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6052,6 +6327,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102326</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6149,6 +6429,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102327</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6246,6 +6531,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102328</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6343,6 +6633,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102394</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6440,6 +6735,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102395</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6537,6 +6837,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102396</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6634,6 +6939,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102397</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6731,6 +7041,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272749</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6828,6 +7143,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102332</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6925,6 +7245,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102333</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7022,6 +7347,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102334</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7119,6 +7449,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272887</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7216,6 +7551,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102335</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7313,6 +7653,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102336</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7410,6 +7755,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272881</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7507,6 +7857,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272882</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7604,6 +7959,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272883</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7710,6 +8070,11 @@
           <t>Statens Fastighetsverk - NVB - Greensway</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90907437</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7816,6 +8181,11 @@
           <t>Statens Fastighetsverk - NVB - Greensway</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90907438</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7913,6 +8283,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133888840</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8010,6 +8385,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272753</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8107,6 +8487,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272884</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8204,6 +8589,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272885</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8301,6 +8691,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272886</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8398,6 +8793,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102284</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8495,6 +8895,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102285</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8592,6 +8997,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102286</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8689,6 +9099,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133888827</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8791,6 +9206,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102287</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8893,6 +9313,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272743</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -8990,6 +9415,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272742</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9087,6 +9517,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272878</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9184,6 +9619,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272879</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9281,6 +9721,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272741</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9378,6 +9823,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272876</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9475,6 +9925,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133888828</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9572,6 +10027,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272752</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9669,6 +10129,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272877</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9766,6 +10231,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272744</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -9863,8 +10333,109 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272745</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 55525-2025 artfynd.xlsx
+++ b/artfynd/A 55525-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ95"/>
+  <dimension ref="A1:AZ116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,32 +680,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133888829</v>
+        <v>136114146</v>
       </c>
       <c r="B2" t="n">
-        <v>99084</v>
+        <v>97530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>233</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>706484</v>
+        <v>706766</v>
       </c>
       <c r="R2" t="n">
-        <v>7426734</v>
+        <v>7426712</v>
       </c>
       <c r="S2" t="n">
         <v>3</v>
@@ -745,17 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>2 blommor</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,16 +776,16 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133888829</t>
+          <t>https://artportalen.se/Sighting/136114146</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133888830</v>
+        <v>136114163</v>
       </c>
       <c r="B3" t="n">
-        <v>99084</v>
+        <v>92310</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>233</v>
+        <v>65</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>706475</v>
+        <v>706914</v>
       </c>
       <c r="R3" t="n">
-        <v>7426727</v>
+        <v>7426504</v>
       </c>
       <c r="S3" t="n">
         <v>3</v>
@@ -852,17 +847,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>5 blommor</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,16 +878,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133888830</t>
+          <t>https://artportalen.se/Sighting/136114163</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133888831</v>
+        <v>136114165</v>
       </c>
       <c r="B4" t="n">
-        <v>99084</v>
+        <v>92310</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>233</v>
+        <v>65</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>706466</v>
+        <v>707006</v>
       </c>
       <c r="R4" t="n">
-        <v>7426731</v>
+        <v>7426525</v>
       </c>
       <c r="S4" t="n">
         <v>3</v>
@@ -959,17 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>9 blommor</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -995,13 +980,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133888831</t>
+          <t>https://artportalen.se/Sighting/136114165</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133888832</v>
+        <v>133888829</v>
       </c>
       <c r="B5" t="n">
         <v>99084</v>
@@ -1036,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>706457</v>
+        <v>706484</v>
       </c>
       <c r="R5" t="n">
-        <v>7426725</v>
+        <v>7426734</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1076,7 +1061,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>3 blommor</t>
+          <t>2 blommor</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1102,13 +1087,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133888832</t>
+          <t>https://artportalen.se/Sighting/133888829</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133888833</v>
+        <v>133888830</v>
       </c>
       <c r="B6" t="n">
         <v>99084</v>
@@ -1143,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>706441</v>
+        <v>706475</v>
       </c>
       <c r="R6" t="n">
-        <v>7426721</v>
+        <v>7426727</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1181,6 +1166,11 @@
           <t>2026-05-25</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>5 blommor</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1204,13 +1194,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133888833</t>
+          <t>https://artportalen.se/Sighting/133888830</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133888834</v>
+        <v>133888831</v>
       </c>
       <c r="B7" t="n">
         <v>99084</v>
@@ -1245,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>706459</v>
+        <v>706466</v>
       </c>
       <c r="R7" t="n">
-        <v>7426728</v>
+        <v>7426731</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1283,6 +1273,11 @@
           <t>2026-05-25</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>9 blommor</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1306,13 +1301,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133888834</t>
+          <t>https://artportalen.se/Sighting/133888831</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133888835</v>
+        <v>133888832</v>
       </c>
       <c r="B8" t="n">
         <v>99084</v>
@@ -1347,7 +1342,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>706462</v>
+        <v>706457</v>
       </c>
       <c r="R8" t="n">
         <v>7426725</v>
@@ -1387,7 +1382,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>5 blommor</t>
+          <t>3 blommor</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1413,13 +1408,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133888835</t>
+          <t>https://artportalen.se/Sighting/133888832</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133888836</v>
+        <v>133888833</v>
       </c>
       <c r="B9" t="n">
         <v>99084</v>
@@ -1454,10 +1449,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>706505</v>
+        <v>706441</v>
       </c>
       <c r="R9" t="n">
-        <v>7426733</v>
+        <v>7426721</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1515,13 +1510,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133888836</t>
+          <t>https://artportalen.se/Sighting/133888833</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133888837</v>
+        <v>133888834</v>
       </c>
       <c r="B10" t="n">
         <v>99084</v>
@@ -1556,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>706498</v>
+        <v>706459</v>
       </c>
       <c r="R10" t="n">
-        <v>7426729</v>
+        <v>7426728</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1617,13 +1612,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133888837</t>
+          <t>https://artportalen.se/Sighting/133888834</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133888838</v>
+        <v>133888835</v>
       </c>
       <c r="B11" t="n">
         <v>99084</v>
@@ -1658,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>706493</v>
+        <v>706462</v>
       </c>
       <c r="R11" t="n">
-        <v>7426724</v>
+        <v>7426725</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1696,6 +1691,11 @@
           <t>2026-05-25</t>
         </is>
       </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>5 blommor</t>
+        </is>
+      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1719,13 +1719,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133888838</t>
+          <t>https://artportalen.se/Sighting/133888835</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133888839</v>
+        <v>133888836</v>
       </c>
       <c r="B12" t="n">
         <v>99084</v>
@@ -1760,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>706491</v>
+        <v>706505</v>
       </c>
       <c r="R12" t="n">
-        <v>7426731</v>
+        <v>7426733</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1798,11 +1798,6 @@
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Två blommor</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1826,13 +1821,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133888839</t>
+          <t>https://artportalen.se/Sighting/133888836</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134102329</v>
+        <v>133888837</v>
       </c>
       <c r="B13" t="n">
         <v>99084</v>
@@ -1867,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>706942</v>
+        <v>706498</v>
       </c>
       <c r="R13" t="n">
-        <v>7426762</v>
+        <v>7426729</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -1897,17 +1892,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>En blomma</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1933,13 +1923,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102329</t>
+          <t>https://artportalen.se/Sighting/133888837</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134102330</v>
+        <v>133888838</v>
       </c>
       <c r="B14" t="n">
         <v>99084</v>
@@ -1974,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>706920</v>
+        <v>706493</v>
       </c>
       <c r="R14" t="n">
-        <v>7426776</v>
+        <v>7426724</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -2004,12 +1994,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2035,13 +2025,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102330</t>
+          <t>https://artportalen.se/Sighting/133888838</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134272750</v>
+        <v>133888839</v>
       </c>
       <c r="B15" t="n">
         <v>99084</v>
@@ -2076,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>706247</v>
+        <v>706491</v>
       </c>
       <c r="R15" t="n">
-        <v>7426954</v>
+        <v>7426731</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
@@ -2106,17 +2096,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>4 blommor</t>
+          <t>Två blommor</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2142,13 +2132,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272750</t>
+          <t>https://artportalen.se/Sighting/133888839</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134272751</v>
+        <v>134102329</v>
       </c>
       <c r="B16" t="n">
         <v>99084</v>
@@ -2183,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>706204</v>
+        <v>706942</v>
       </c>
       <c r="R16" t="n">
-        <v>7426971</v>
+        <v>7426762</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2213,17 +2203,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>1 blommande</t>
+          <t>En blomma</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2249,38 +2239,38 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272751</t>
+          <t>https://artportalen.se/Sighting/134102329</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134272754</v>
+        <v>134102330</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>99084</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>353</v>
+        <v>233</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2290,10 +2280,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>706491</v>
+        <v>706920</v>
       </c>
       <c r="R17" t="n">
-        <v>7426611</v>
+        <v>7426776</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2320,12 +2310,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2351,38 +2341,38 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272754</t>
+          <t>https://artportalen.se/Sighting/134102330</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134272755</v>
+        <v>134272750</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>99084</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>353</v>
+        <v>233</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2392,10 +2382,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>706573</v>
+        <v>706247</v>
       </c>
       <c r="R18" t="n">
-        <v>7426540</v>
+        <v>7426954</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2430,6 +2420,11 @@
           <t>2026-06-09</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>4 blommor</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2453,16 +2448,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272755</t>
+          <t>https://artportalen.se/Sighting/134272750</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134102288</v>
+        <v>134272751</v>
       </c>
       <c r="B19" t="n">
-        <v>79440</v>
+        <v>99084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2470,21 +2465,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>637</v>
+        <v>233</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2494,10 +2489,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>706968</v>
+        <v>706204</v>
       </c>
       <c r="R19" t="n">
-        <v>7426698</v>
+        <v>7426971</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2524,12 +2519,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>1 blommande</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2555,38 +2555,38 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102288</t>
+          <t>https://artportalen.se/Sighting/134272751</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134102289</v>
+        <v>134272754</v>
       </c>
       <c r="B20" t="n">
-        <v>79440</v>
+        <v>79039</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>637</v>
+        <v>353</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2596,10 +2596,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>706941</v>
+        <v>706491</v>
       </c>
       <c r="R20" t="n">
-        <v>7426720</v>
+        <v>7426611</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2626,12 +2626,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2657,38 +2657,38 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102289</t>
+          <t>https://artportalen.se/Sighting/134272754</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134102290</v>
+        <v>134272755</v>
       </c>
       <c r="B21" t="n">
-        <v>79440</v>
+        <v>79039</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>637</v>
+        <v>353</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2698,10 +2698,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>706918</v>
+        <v>706573</v>
       </c>
       <c r="R21" t="n">
-        <v>7426756</v>
+        <v>7426540</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2728,12 +2728,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2759,38 +2759,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102290</t>
+          <t>https://artportalen.se/Sighting/134272755</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134102291</v>
+        <v>136114167</v>
       </c>
       <c r="B22" t="n">
-        <v>79440</v>
+        <v>79109</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>637</v>
+        <v>353</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2800,10 +2800,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>706899</v>
+        <v>707017</v>
       </c>
       <c r="R22" t="n">
-        <v>7426771</v>
+        <v>7426508</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -2830,12 +2830,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2861,13 +2861,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102291</t>
+          <t>https://artportalen.se/Sighting/136114167</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134102292</v>
+        <v>134102288</v>
       </c>
       <c r="B23" t="n">
         <v>79440</v>
@@ -2902,10 +2902,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>706891</v>
+        <v>706968</v>
       </c>
       <c r="R23" t="n">
-        <v>7426771</v>
+        <v>7426698</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -2963,13 +2963,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102292</t>
+          <t>https://artportalen.se/Sighting/134102288</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134102293</v>
+        <v>134102289</v>
       </c>
       <c r="B24" t="n">
         <v>79440</v>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>706890</v>
+        <v>706941</v>
       </c>
       <c r="R24" t="n">
-        <v>7426773</v>
+        <v>7426720</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -3065,13 +3065,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102293</t>
+          <t>https://artportalen.se/Sighting/134102289</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134102294</v>
+        <v>134102290</v>
       </c>
       <c r="B25" t="n">
         <v>79440</v>
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>706878</v>
+        <v>706918</v>
       </c>
       <c r="R25" t="n">
-        <v>7426778</v>
+        <v>7426756</v>
       </c>
       <c r="S25" t="n">
         <v>3</v>
@@ -3167,13 +3167,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102294</t>
+          <t>https://artportalen.se/Sighting/134102290</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134102295</v>
+        <v>134102291</v>
       </c>
       <c r="B26" t="n">
         <v>79440</v>
@@ -3208,10 +3208,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>706859</v>
+        <v>706899</v>
       </c>
       <c r="R26" t="n">
-        <v>7426782</v>
+        <v>7426771</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3269,13 +3269,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102295</t>
+          <t>https://artportalen.se/Sighting/134102291</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134102296</v>
+        <v>134102292</v>
       </c>
       <c r="B27" t="n">
         <v>79440</v>
@@ -3310,10 +3310,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>706851</v>
+        <v>706891</v>
       </c>
       <c r="R27" t="n">
-        <v>7426782</v>
+        <v>7426771</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3371,13 +3371,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102296</t>
+          <t>https://artportalen.se/Sighting/134102292</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134102297</v>
+        <v>134102293</v>
       </c>
       <c r="B28" t="n">
         <v>79440</v>
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>706834</v>
+        <v>706890</v>
       </c>
       <c r="R28" t="n">
-        <v>7426787</v>
+        <v>7426773</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -3473,13 +3473,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102297</t>
+          <t>https://artportalen.se/Sighting/134102293</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134102298</v>
+        <v>134102294</v>
       </c>
       <c r="B29" t="n">
         <v>79440</v>
@@ -3514,10 +3514,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>706810</v>
+        <v>706878</v>
       </c>
       <c r="R29" t="n">
-        <v>7426802</v>
+        <v>7426778</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3575,13 +3575,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102298</t>
+          <t>https://artportalen.se/Sighting/134102294</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134102299</v>
+        <v>134102295</v>
       </c>
       <c r="B30" t="n">
         <v>79440</v>
@@ -3616,10 +3616,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>706809</v>
+        <v>706859</v>
       </c>
       <c r="R30" t="n">
-        <v>7426819</v>
+        <v>7426782</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3677,13 +3677,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102299</t>
+          <t>https://artportalen.se/Sighting/134102295</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134102300</v>
+        <v>134102296</v>
       </c>
       <c r="B31" t="n">
         <v>79440</v>
@@ -3718,10 +3718,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>706796</v>
+        <v>706851</v>
       </c>
       <c r="R31" t="n">
-        <v>7426839</v>
+        <v>7426782</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -3779,13 +3779,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102300</t>
+          <t>https://artportalen.se/Sighting/134102296</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134102301</v>
+        <v>134102297</v>
       </c>
       <c r="B32" t="n">
         <v>79440</v>
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>706805</v>
+        <v>706834</v>
       </c>
       <c r="R32" t="n">
-        <v>7426845</v>
+        <v>7426787</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
@@ -3881,13 +3881,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102301</t>
+          <t>https://artportalen.se/Sighting/134102297</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134102302</v>
+        <v>134102298</v>
       </c>
       <c r="B33" t="n">
         <v>79440</v>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>706816</v>
+        <v>706810</v>
       </c>
       <c r="R33" t="n">
-        <v>7426823</v>
+        <v>7426802</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -3983,13 +3983,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102302</t>
+          <t>https://artportalen.se/Sighting/134102298</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134102303</v>
+        <v>134102299</v>
       </c>
       <c r="B34" t="n">
         <v>79440</v>
@@ -4024,10 +4024,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>706841</v>
+        <v>706809</v>
       </c>
       <c r="R34" t="n">
-        <v>7426814</v>
+        <v>7426819</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -4085,13 +4085,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102303</t>
+          <t>https://artportalen.se/Sighting/134102299</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134102304</v>
+        <v>134102300</v>
       </c>
       <c r="B35" t="n">
         <v>79440</v>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>706855</v>
+        <v>706796</v>
       </c>
       <c r="R35" t="n">
-        <v>7426811</v>
+        <v>7426839</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -4187,13 +4187,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102304</t>
+          <t>https://artportalen.se/Sighting/134102300</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134102305</v>
+        <v>134102301</v>
       </c>
       <c r="B36" t="n">
         <v>79440</v>
@@ -4228,10 +4228,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>706852</v>
+        <v>706805</v>
       </c>
       <c r="R36" t="n">
-        <v>7426799</v>
+        <v>7426845</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4289,13 +4289,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102305</t>
+          <t>https://artportalen.se/Sighting/134102301</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134102306</v>
+        <v>134102302</v>
       </c>
       <c r="B37" t="n">
         <v>79440</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>706863</v>
+        <v>706816</v>
       </c>
       <c r="R37" t="n">
-        <v>7426795</v>
+        <v>7426823</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4391,13 +4391,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102306</t>
+          <t>https://artportalen.se/Sighting/134102302</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134102307</v>
+        <v>134102303</v>
       </c>
       <c r="B38" t="n">
         <v>79440</v>
@@ -4432,10 +4432,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>706875</v>
+        <v>706841</v>
       </c>
       <c r="R38" t="n">
-        <v>7426805</v>
+        <v>7426814</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4493,13 +4493,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102307</t>
+          <t>https://artportalen.se/Sighting/134102303</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134102309</v>
+        <v>134102304</v>
       </c>
       <c r="B39" t="n">
         <v>79440</v>
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>706885</v>
+        <v>706855</v>
       </c>
       <c r="R39" t="n">
-        <v>7426802</v>
+        <v>7426811</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4595,13 +4595,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102309</t>
+          <t>https://artportalen.se/Sighting/134102304</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134102310</v>
+        <v>134102305</v>
       </c>
       <c r="B40" t="n">
         <v>79440</v>
@@ -4636,10 +4636,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>706887</v>
+        <v>706852</v>
       </c>
       <c r="R40" t="n">
-        <v>7426800</v>
+        <v>7426799</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -4697,13 +4697,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102310</t>
+          <t>https://artportalen.se/Sighting/134102305</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134102311</v>
+        <v>134102306</v>
       </c>
       <c r="B41" t="n">
         <v>79440</v>
@@ -4738,10 +4738,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>706893</v>
+        <v>706863</v>
       </c>
       <c r="R41" t="n">
-        <v>7426806</v>
+        <v>7426795</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
@@ -4799,13 +4799,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102311</t>
+          <t>https://artportalen.se/Sighting/134102306</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134102312</v>
+        <v>134102307</v>
       </c>
       <c r="B42" t="n">
         <v>79440</v>
@@ -4840,10 +4840,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>706909</v>
+        <v>706875</v>
       </c>
       <c r="R42" t="n">
-        <v>7426793</v>
+        <v>7426805</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -4901,13 +4901,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102312</t>
+          <t>https://artportalen.se/Sighting/134102307</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134102313</v>
+        <v>134102309</v>
       </c>
       <c r="B43" t="n">
         <v>79440</v>
@@ -4942,10 +4942,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>706912</v>
+        <v>706885</v>
       </c>
       <c r="R43" t="n">
-        <v>7426790</v>
+        <v>7426802</v>
       </c>
       <c r="S43" t="n">
         <v>3</v>
@@ -5003,13 +5003,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102313</t>
+          <t>https://artportalen.se/Sighting/134102309</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134102314</v>
+        <v>134102310</v>
       </c>
       <c r="B44" t="n">
         <v>79440</v>
@@ -5044,10 +5044,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>706925</v>
+        <v>706887</v>
       </c>
       <c r="R44" t="n">
-        <v>7426791</v>
+        <v>7426800</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -5105,13 +5105,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102314</t>
+          <t>https://artportalen.se/Sighting/134102310</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134102315</v>
+        <v>134102311</v>
       </c>
       <c r="B45" t="n">
         <v>79440</v>
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>706920</v>
+        <v>706893</v>
       </c>
       <c r="R45" t="n">
-        <v>7426784</v>
+        <v>7426806</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -5207,13 +5207,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102315</t>
+          <t>https://artportalen.se/Sighting/134102311</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134102316</v>
+        <v>134102312</v>
       </c>
       <c r="B46" t="n">
         <v>79440</v>
@@ -5248,7 +5248,7 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>706925</v>
+        <v>706909</v>
       </c>
       <c r="R46" t="n">
         <v>7426793</v>
@@ -5309,13 +5309,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102316</t>
+          <t>https://artportalen.se/Sighting/134102312</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134102317</v>
+        <v>134102313</v>
       </c>
       <c r="B47" t="n">
         <v>79440</v>
@@ -5350,10 +5350,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>706934</v>
+        <v>706912</v>
       </c>
       <c r="R47" t="n">
-        <v>7426777</v>
+        <v>7426790</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
@@ -5411,13 +5411,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102317</t>
+          <t>https://artportalen.se/Sighting/134102313</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134102318</v>
+        <v>134102314</v>
       </c>
       <c r="B48" t="n">
         <v>79440</v>
@@ -5452,10 +5452,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>706944</v>
+        <v>706925</v>
       </c>
       <c r="R48" t="n">
-        <v>7426769</v>
+        <v>7426791</v>
       </c>
       <c r="S48" t="n">
         <v>3</v>
@@ -5513,13 +5513,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102318</t>
+          <t>https://artportalen.se/Sighting/134102314</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134102319</v>
+        <v>134102315</v>
       </c>
       <c r="B49" t="n">
         <v>79440</v>
@@ -5554,10 +5554,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>706952</v>
+        <v>706920</v>
       </c>
       <c r="R49" t="n">
-        <v>7426764</v>
+        <v>7426784</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -5615,13 +5615,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102319</t>
+          <t>https://artportalen.se/Sighting/134102315</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134102320</v>
+        <v>134102316</v>
       </c>
       <c r="B50" t="n">
         <v>79440</v>
@@ -5656,10 +5656,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>706960</v>
+        <v>706925</v>
       </c>
       <c r="R50" t="n">
-        <v>7426760</v>
+        <v>7426793</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -5717,13 +5717,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102320</t>
+          <t>https://artportalen.se/Sighting/134102316</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134102321</v>
+        <v>134102317</v>
       </c>
       <c r="B51" t="n">
         <v>79440</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>706970</v>
+        <v>706934</v>
       </c>
       <c r="R51" t="n">
-        <v>7426748</v>
+        <v>7426777</v>
       </c>
       <c r="S51" t="n">
         <v>3</v>
@@ -5819,13 +5819,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102321</t>
+          <t>https://artportalen.se/Sighting/134102317</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134102322</v>
+        <v>134102318</v>
       </c>
       <c r="B52" t="n">
         <v>79440</v>
@@ -5860,10 +5860,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>706963</v>
+        <v>706944</v>
       </c>
       <c r="R52" t="n">
-        <v>7426740</v>
+        <v>7426769</v>
       </c>
       <c r="S52" t="n">
         <v>3</v>
@@ -5890,12 +5890,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5921,13 +5921,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102322</t>
+          <t>https://artportalen.se/Sighting/134102318</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134102323</v>
+        <v>134102319</v>
       </c>
       <c r="B53" t="n">
         <v>79440</v>
@@ -5962,10 +5962,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>706967</v>
+        <v>706952</v>
       </c>
       <c r="R53" t="n">
-        <v>7426729</v>
+        <v>7426764</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -5992,12 +5992,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6023,13 +6023,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102323</t>
+          <t>https://artportalen.se/Sighting/134102319</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134102324</v>
+        <v>134102320</v>
       </c>
       <c r="B54" t="n">
         <v>79440</v>
@@ -6064,10 +6064,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>706968</v>
+        <v>706960</v>
       </c>
       <c r="R54" t="n">
-        <v>7426683</v>
+        <v>7426760</v>
       </c>
       <c r="S54" t="n">
         <v>3</v>
@@ -6094,12 +6094,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6125,13 +6125,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102324</t>
+          <t>https://artportalen.se/Sighting/134102320</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134102325</v>
+        <v>134102321</v>
       </c>
       <c r="B55" t="n">
         <v>79440</v>
@@ -6166,10 +6166,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>706955</v>
+        <v>706970</v>
       </c>
       <c r="R55" t="n">
-        <v>7426674</v>
+        <v>7426748</v>
       </c>
       <c r="S55" t="n">
         <v>3</v>
@@ -6196,12 +6196,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6227,13 +6227,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102325</t>
+          <t>https://artportalen.se/Sighting/134102321</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134102326</v>
+        <v>134102322</v>
       </c>
       <c r="B56" t="n">
         <v>79440</v>
@@ -6268,10 +6268,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>706941</v>
+        <v>706963</v>
       </c>
       <c r="R56" t="n">
-        <v>7426672</v>
+        <v>7426740</v>
       </c>
       <c r="S56" t="n">
         <v>3</v>
@@ -6329,13 +6329,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102326</t>
+          <t>https://artportalen.se/Sighting/134102322</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134102327</v>
+        <v>134102323</v>
       </c>
       <c r="B57" t="n">
         <v>79440</v>
@@ -6370,10 +6370,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>706944</v>
+        <v>706967</v>
       </c>
       <c r="R57" t="n">
-        <v>7426692</v>
+        <v>7426729</v>
       </c>
       <c r="S57" t="n">
         <v>3</v>
@@ -6431,13 +6431,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102327</t>
+          <t>https://artportalen.se/Sighting/134102323</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134102328</v>
+        <v>134102324</v>
       </c>
       <c r="B58" t="n">
         <v>79440</v>
@@ -6472,10 +6472,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>706937</v>
+        <v>706968</v>
       </c>
       <c r="R58" t="n">
-        <v>7426690</v>
+        <v>7426683</v>
       </c>
       <c r="S58" t="n">
         <v>3</v>
@@ -6533,13 +6533,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102328</t>
+          <t>https://artportalen.se/Sighting/134102324</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134102394</v>
+        <v>134102325</v>
       </c>
       <c r="B59" t="n">
         <v>79440</v>
@@ -6574,10 +6574,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>706913</v>
+        <v>706955</v>
       </c>
       <c r="R59" t="n">
-        <v>7426627</v>
+        <v>7426674</v>
       </c>
       <c r="S59" t="n">
         <v>3</v>
@@ -6604,12 +6604,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6635,13 +6635,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102394</t>
+          <t>https://artportalen.se/Sighting/134102325</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134102395</v>
+        <v>134102326</v>
       </c>
       <c r="B60" t="n">
         <v>79440</v>
@@ -6676,10 +6676,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>706915</v>
+        <v>706941</v>
       </c>
       <c r="R60" t="n">
-        <v>7426639</v>
+        <v>7426672</v>
       </c>
       <c r="S60" t="n">
         <v>3</v>
@@ -6706,12 +6706,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6737,13 +6737,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102395</t>
+          <t>https://artportalen.se/Sighting/134102326</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134102396</v>
+        <v>134102327</v>
       </c>
       <c r="B61" t="n">
         <v>79440</v>
@@ -6778,10 +6778,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>706917</v>
+        <v>706944</v>
       </c>
       <c r="R61" t="n">
-        <v>7426646</v>
+        <v>7426692</v>
       </c>
       <c r="S61" t="n">
         <v>3</v>
@@ -6808,12 +6808,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6839,13 +6839,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102396</t>
+          <t>https://artportalen.se/Sighting/134102327</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134102397</v>
+        <v>134102328</v>
       </c>
       <c r="B62" t="n">
         <v>79440</v>
@@ -6880,10 +6880,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>706868</v>
+        <v>706937</v>
       </c>
       <c r="R62" t="n">
-        <v>7426681</v>
+        <v>7426690</v>
       </c>
       <c r="S62" t="n">
         <v>3</v>
@@ -6910,12 +6910,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6941,13 +6941,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102397</t>
+          <t>https://artportalen.se/Sighting/134102328</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>134272749</v>
+        <v>134102394</v>
       </c>
       <c r="B63" t="n">
         <v>79440</v>
@@ -6982,10 +6982,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>706238</v>
+        <v>706913</v>
       </c>
       <c r="R63" t="n">
-        <v>7426848</v>
+        <v>7426627</v>
       </c>
       <c r="S63" t="n">
         <v>3</v>
@@ -7012,12 +7012,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7043,38 +7043,38 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272749</t>
+          <t>https://artportalen.se/Sighting/134102394</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>134102332</v>
+        <v>134102395</v>
       </c>
       <c r="B64" t="n">
-        <v>79452</v>
+        <v>79440</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>864</v>
+        <v>637</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7084,10 +7084,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>706805</v>
+        <v>706915</v>
       </c>
       <c r="R64" t="n">
-        <v>7426821</v>
+        <v>7426639</v>
       </c>
       <c r="S64" t="n">
         <v>3</v>
@@ -7145,38 +7145,38 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102332</t>
+          <t>https://artportalen.se/Sighting/134102395</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>134102333</v>
+        <v>134102396</v>
       </c>
       <c r="B65" t="n">
-        <v>79452</v>
+        <v>79440</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>864</v>
+        <v>637</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>706797</v>
+        <v>706917</v>
       </c>
       <c r="R65" t="n">
-        <v>7426837</v>
+        <v>7426646</v>
       </c>
       <c r="S65" t="n">
         <v>3</v>
@@ -7247,38 +7247,38 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102333</t>
+          <t>https://artportalen.se/Sighting/134102396</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>134102334</v>
+        <v>134102397</v>
       </c>
       <c r="B66" t="n">
-        <v>79452</v>
+        <v>79440</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>864</v>
+        <v>637</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7288,10 +7288,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>706856</v>
+        <v>706868</v>
       </c>
       <c r="R66" t="n">
-        <v>7426791</v>
+        <v>7426681</v>
       </c>
       <c r="S66" t="n">
         <v>3</v>
@@ -7349,38 +7349,38 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102334</t>
+          <t>https://artportalen.se/Sighting/134102397</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>134272887</v>
+        <v>134272749</v>
       </c>
       <c r="B67" t="n">
-        <v>79452</v>
+        <v>79440</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>864</v>
+        <v>637</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7390,10 +7390,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>706763</v>
+        <v>706238</v>
       </c>
       <c r="R67" t="n">
-        <v>7426802</v>
+        <v>7426848</v>
       </c>
       <c r="S67" t="n">
         <v>3</v>
@@ -7451,38 +7451,38 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272887</t>
+          <t>https://artportalen.se/Sighting/134272749</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>134102335</v>
+        <v>136114162</v>
       </c>
       <c r="B68" t="n">
-        <v>83222</v>
+        <v>79512</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1312</v>
+        <v>639</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Grenlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Evernia mesomorpha</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>Nyl.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7492,10 +7492,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>706856</v>
+        <v>706836</v>
       </c>
       <c r="R68" t="n">
-        <v>7426794</v>
+        <v>7426791</v>
       </c>
       <c r="S68" t="n">
         <v>3</v>
@@ -7522,12 +7522,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7553,16 +7553,16 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102335</t>
+          <t>https://artportalen.se/Sighting/136114162</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134102336</v>
+        <v>134102332</v>
       </c>
       <c r="B69" t="n">
-        <v>83222</v>
+        <v>79452</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7570,21 +7570,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1312</v>
+        <v>864</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7594,10 +7594,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>706796</v>
+        <v>706805</v>
       </c>
       <c r="R69" t="n">
-        <v>7426839</v>
+        <v>7426821</v>
       </c>
       <c r="S69" t="n">
         <v>3</v>
@@ -7655,38 +7655,38 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102336</t>
+          <t>https://artportalen.se/Sighting/134102332</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134272881</v>
+        <v>134102333</v>
       </c>
       <c r="B70" t="n">
-        <v>101376</v>
+        <v>79452</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1365</v>
+        <v>864</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7696,10 +7696,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>706837</v>
+        <v>706797</v>
       </c>
       <c r="R70" t="n">
-        <v>7426798</v>
+        <v>7426837</v>
       </c>
       <c r="S70" t="n">
         <v>3</v>
@@ -7726,12 +7726,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7757,38 +7757,38 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272881</t>
+          <t>https://artportalen.se/Sighting/134102333</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>134272882</v>
+        <v>134102334</v>
       </c>
       <c r="B71" t="n">
-        <v>101376</v>
+        <v>79452</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1365</v>
+        <v>864</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7798,10 +7798,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>706944</v>
+        <v>706856</v>
       </c>
       <c r="R71" t="n">
-        <v>7426775</v>
+        <v>7426791</v>
       </c>
       <c r="S71" t="n">
         <v>3</v>
@@ -7828,12 +7828,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7859,38 +7859,38 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272882</t>
+          <t>https://artportalen.se/Sighting/134102334</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134272883</v>
+        <v>134272887</v>
       </c>
       <c r="B72" t="n">
-        <v>101376</v>
+        <v>79452</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1365</v>
+        <v>864</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7900,10 +7900,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>706961</v>
+        <v>706763</v>
       </c>
       <c r="R72" t="n">
-        <v>7426774</v>
+        <v>7426802</v>
       </c>
       <c r="S72" t="n">
         <v>3</v>
@@ -7961,16 +7961,16 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272883</t>
+          <t>https://artportalen.se/Sighting/134272887</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>90907437</v>
+        <v>134102335</v>
       </c>
       <c r="B73" t="n">
-        <v>92097</v>
+        <v>83222</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7978,37 +7978,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1588</v>
+        <v>1312</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Agas, Lu lm</t>
+          <t>Ågåsgielas, Lu lm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>706938</v>
+        <v>706856</v>
       </c>
       <c r="R73" t="n">
-        <v>7426555</v>
+        <v>7426794</v>
       </c>
       <c r="S73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8032,12 +8032,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2019-09-22</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2019-09-22</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8048,40 +8048,31 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AS73" t="inlineStr">
-        <is>
-          <t>Olle Finnström</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Charles Campbell</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Via Charles Campbell</t>
-        </is>
-      </c>
-      <c r="AY73" t="inlineStr">
-        <is>
-          <t>Statens Fastighetsverk - NVB - Greensway</t>
-        </is>
-      </c>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/90907437</t>
+          <t>https://artportalen.se/Sighting/134102335</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>90907438</v>
+        <v>134102336</v>
       </c>
       <c r="B74" t="n">
-        <v>93191</v>
+        <v>83222</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8089,37 +8080,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4362</v>
+        <v>1312</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Agas, Lu lm</t>
+          <t>Ågåsgielas, Lu lm</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>706953</v>
+        <v>706796</v>
       </c>
       <c r="R74" t="n">
-        <v>7426549</v>
+        <v>7426839</v>
       </c>
       <c r="S74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8143,12 +8134,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2019-09-22</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2019-09-22</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8159,62 +8150,53 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AS74" t="inlineStr">
-        <is>
-          <t>Olle Finnström</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Charles Campbell</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Via Charles Campbell</t>
-        </is>
-      </c>
-      <c r="AY74" t="inlineStr">
-        <is>
-          <t>Statens Fastighetsverk - NVB - Greensway</t>
-        </is>
-      </c>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/90907438</t>
+          <t>https://artportalen.se/Sighting/134102336</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133888840</v>
+        <v>134272881</v>
       </c>
       <c r="B75" t="n">
-        <v>93271</v>
+        <v>101376</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>1365</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8224,10 +8206,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>706935</v>
+        <v>706837</v>
       </c>
       <c r="R75" t="n">
-        <v>7426534</v>
+        <v>7426798</v>
       </c>
       <c r="S75" t="n">
         <v>3</v>
@@ -8254,12 +8236,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8285,38 +8267,38 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133888840</t>
+          <t>https://artportalen.se/Sighting/134272881</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134272753</v>
+        <v>134272882</v>
       </c>
       <c r="B76" t="n">
-        <v>79130</v>
+        <v>101376</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6446</v>
+        <v>1365</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8326,10 +8308,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>706836</v>
+        <v>706944</v>
       </c>
       <c r="R76" t="n">
-        <v>7426766</v>
+        <v>7426775</v>
       </c>
       <c r="S76" t="n">
         <v>3</v>
@@ -8387,38 +8369,38 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272753</t>
+          <t>https://artportalen.se/Sighting/134272882</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>134272884</v>
+        <v>134272883</v>
       </c>
       <c r="B77" t="n">
-        <v>79130</v>
+        <v>101376</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>1365</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8428,10 +8410,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>706477</v>
+        <v>706961</v>
       </c>
       <c r="R77" t="n">
-        <v>7426743</v>
+        <v>7426774</v>
       </c>
       <c r="S77" t="n">
         <v>3</v>
@@ -8489,38 +8471,38 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272884</t>
+          <t>https://artportalen.se/Sighting/134272883</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>134272885</v>
+        <v>136114161</v>
       </c>
       <c r="B78" t="n">
-        <v>79130</v>
+        <v>92243</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>1503</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8530,10 +8512,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>706844</v>
+        <v>706954</v>
       </c>
       <c r="R78" t="n">
-        <v>7426764</v>
+        <v>7426566</v>
       </c>
       <c r="S78" t="n">
         <v>3</v>
@@ -8560,12 +8542,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8591,16 +8573,16 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272885</t>
+          <t>https://artportalen.se/Sighting/136114161</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>134272886</v>
+        <v>90907437</v>
       </c>
       <c r="B79" t="n">
-        <v>79130</v>
+        <v>92097</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8608,37 +8590,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>1588</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Ågåsgielas, Lu lm</t>
+          <t>Agas, Lu lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>706845</v>
+        <v>706938</v>
       </c>
       <c r="R79" t="n">
-        <v>7426764</v>
+        <v>7426555</v>
       </c>
       <c r="S79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8662,12 +8644,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2019-09-22</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2019-09-22</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8678,31 +8660,40 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AS79" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Charles Campbell</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr"/>
+          <t>Via Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr">
+        <is>
+          <t>Statens Fastighetsverk - NVB - Greensway</t>
+        </is>
+      </c>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272886</t>
+          <t>https://artportalen.se/Sighting/90907437</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>134102284</v>
+        <v>136114157</v>
       </c>
       <c r="B80" t="n">
-        <v>57975</v>
+        <v>92117</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8710,21 +8701,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>2079</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8734,10 +8725,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>706890</v>
+        <v>707008</v>
       </c>
       <c r="R80" t="n">
-        <v>7426773</v>
+        <v>7426533</v>
       </c>
       <c r="S80" t="n">
         <v>3</v>
@@ -8764,12 +8755,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8795,16 +8786,16 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102284</t>
+          <t>https://artportalen.se/Sighting/136114157</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>134102285</v>
+        <v>136114153</v>
       </c>
       <c r="B81" t="n">
-        <v>57975</v>
+        <v>93387</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8812,21 +8803,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>3100</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8836,10 +8827,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>706809</v>
+        <v>707049</v>
       </c>
       <c r="R81" t="n">
-        <v>7426804</v>
+        <v>7426483</v>
       </c>
       <c r="S81" t="n">
         <v>3</v>
@@ -8866,12 +8857,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8897,16 +8888,16 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102285</t>
+          <t>https://artportalen.se/Sighting/136114153</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>134102286</v>
+        <v>136114158</v>
       </c>
       <c r="B82" t="n">
-        <v>57975</v>
+        <v>92192</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8914,21 +8905,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>3277</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8938,10 +8929,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>706976</v>
+        <v>706467</v>
       </c>
       <c r="R82" t="n">
-        <v>7426669</v>
+        <v>7426727</v>
       </c>
       <c r="S82" t="n">
         <v>3</v>
@@ -8968,12 +8959,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8999,38 +8990,38 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102286</t>
+          <t>https://artportalen.se/Sighting/136114158</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133888827</v>
+        <v>136114149</v>
       </c>
       <c r="B83" t="n">
-        <v>57162</v>
+        <v>87460</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100138</v>
+        <v>3690</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9040,10 +9031,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>706811</v>
+        <v>707005</v>
       </c>
       <c r="R83" t="n">
-        <v>7426646</v>
+        <v>7426526</v>
       </c>
       <c r="S83" t="n">
         <v>3</v>
@@ -9070,12 +9061,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9101,54 +9092,54 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133888827</t>
+          <t>https://artportalen.se/Sighting/136114149</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>134102287</v>
+        <v>90907438</v>
       </c>
       <c r="B84" t="n">
-        <v>57162</v>
+        <v>93191</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100138</v>
+        <v>4362</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Ågåsgielas, Lu lm</t>
+          <t>Agas, Lu lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>706951</v>
+        <v>706953</v>
       </c>
       <c r="R84" t="n">
-        <v>7426689</v>
+        <v>7426549</v>
       </c>
       <c r="S84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9172,17 +9163,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2019-09-22</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>2019-09-22</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9193,53 +9179,62 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AS84" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Charles Campbell</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr"/>
+          <t>Via Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr">
+        <is>
+          <t>Statens Fastighetsverk - NVB - Greensway</t>
+        </is>
+      </c>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102287</t>
+          <t>https://artportalen.se/Sighting/90907438</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>134272743</v>
+        <v>133888840</v>
       </c>
       <c r="B85" t="n">
-        <v>57162</v>
+        <v>93271</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9249,10 +9244,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>706576</v>
+        <v>706935</v>
       </c>
       <c r="R85" t="n">
-        <v>7426767</v>
+        <v>7426534</v>
       </c>
       <c r="S85" t="n">
         <v>3</v>
@@ -9279,17 +9274,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Otroligt mycket spillning på stenkulle</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9315,16 +9305,16 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272743</t>
+          <t>https://artportalen.se/Sighting/133888840</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>134272742</v>
+        <v>136114151</v>
       </c>
       <c r="B86" t="n">
-        <v>58839</v>
+        <v>89223</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9332,21 +9322,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>208249</v>
+        <v>4379</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9356,10 +9346,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>706447</v>
+        <v>706495</v>
       </c>
       <c r="R86" t="n">
-        <v>7426815</v>
+        <v>7426729</v>
       </c>
       <c r="S86" t="n">
         <v>3</v>
@@ -9386,12 +9376,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9417,38 +9407,38 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272742</t>
+          <t>https://artportalen.se/Sighting/136114151</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>134272878</v>
+        <v>136114145</v>
       </c>
       <c r="B87" t="n">
-        <v>58839</v>
+        <v>83430</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>208249</v>
+        <v>6440</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9458,10 +9448,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>706913</v>
+        <v>706856</v>
       </c>
       <c r="R87" t="n">
-        <v>7426789</v>
+        <v>7426784</v>
       </c>
       <c r="S87" t="n">
         <v>3</v>
@@ -9488,12 +9478,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9519,38 +9509,38 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272878</t>
+          <t>https://artportalen.se/Sighting/136114145</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>134272879</v>
+        <v>134272753</v>
       </c>
       <c r="B88" t="n">
-        <v>58839</v>
+        <v>79130</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>208249</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9560,10 +9550,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>706948</v>
+        <v>706836</v>
       </c>
       <c r="R88" t="n">
-        <v>7426772</v>
+        <v>7426766</v>
       </c>
       <c r="S88" t="n">
         <v>3</v>
@@ -9621,38 +9611,38 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272879</t>
+          <t>https://artportalen.se/Sighting/134272753</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>134272741</v>
+        <v>134272884</v>
       </c>
       <c r="B89" t="n">
-        <v>106309</v>
+        <v>79130</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221725</v>
+        <v>6446</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9662,10 +9652,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>706510</v>
+        <v>706477</v>
       </c>
       <c r="R89" t="n">
-        <v>7426625</v>
+        <v>7426743</v>
       </c>
       <c r="S89" t="n">
         <v>3</v>
@@ -9723,38 +9713,38 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272741</t>
+          <t>https://artportalen.se/Sighting/134272884</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>134272876</v>
+        <v>134272885</v>
       </c>
       <c r="B90" t="n">
-        <v>106309</v>
+        <v>79130</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>221725</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9764,10 +9754,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>706861</v>
+        <v>706844</v>
       </c>
       <c r="R90" t="n">
-        <v>7426790</v>
+        <v>7426764</v>
       </c>
       <c r="S90" t="n">
         <v>3</v>
@@ -9825,38 +9815,38 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272876</t>
+          <t>https://artportalen.se/Sighting/134272885</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133888828</v>
+        <v>134272886</v>
       </c>
       <c r="B91" t="n">
-        <v>104707</v>
+        <v>79130</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>222412</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9866,10 +9856,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>706508</v>
+        <v>706845</v>
       </c>
       <c r="R91" t="n">
-        <v>7426811</v>
+        <v>7426764</v>
       </c>
       <c r="S91" t="n">
         <v>3</v>
@@ -9896,12 +9886,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9927,16 +9917,16 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133888828</t>
+          <t>https://artportalen.se/Sighting/134272886</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>134272752</v>
+        <v>136114147</v>
       </c>
       <c r="B92" t="n">
-        <v>79131</v>
+        <v>80062</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9944,21 +9934,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9968,10 +9958,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>706597</v>
+        <v>706953</v>
       </c>
       <c r="R92" t="n">
-        <v>7426486</v>
+        <v>7426533</v>
       </c>
       <c r="S92" t="n">
         <v>3</v>
@@ -9998,12 +9988,12 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10029,16 +10019,16 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272752</t>
+          <t>https://artportalen.se/Sighting/136114147</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>134272877</v>
+        <v>134102284</v>
       </c>
       <c r="B93" t="n">
-        <v>79963</v>
+        <v>57975</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10046,21 +10036,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10070,10 +10060,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>706475</v>
+        <v>706890</v>
       </c>
       <c r="R93" t="n">
-        <v>7426738</v>
+        <v>7426773</v>
       </c>
       <c r="S93" t="n">
         <v>3</v>
@@ -10100,12 +10090,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10131,38 +10121,38 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272877</t>
+          <t>https://artportalen.se/Sighting/134102284</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>134272744</v>
+        <v>134102285</v>
       </c>
       <c r="B94" t="n">
-        <v>79899</v>
+        <v>57975</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>229830</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Späd brosklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Ramalina dilacerata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10172,10 +10162,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>706239</v>
+        <v>706809</v>
       </c>
       <c r="R94" t="n">
-        <v>7426846</v>
+        <v>7426804</v>
       </c>
       <c r="S94" t="n">
         <v>3</v>
@@ -10202,12 +10192,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10233,38 +10223,38 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272744</t>
+          <t>https://artportalen.se/Sighting/134102285</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>134272745</v>
+        <v>134102286</v>
       </c>
       <c r="B95" t="n">
-        <v>79899</v>
+        <v>57975</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>229830</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Späd brosklav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ramalina dilacerata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10274,10 +10264,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>706278</v>
+        <v>706976</v>
       </c>
       <c r="R95" t="n">
-        <v>7426914</v>
+        <v>7426669</v>
       </c>
       <c r="S95" t="n">
         <v>3</v>
@@ -10304,12 +10294,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10335,7 +10325,2159 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/134102286</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>136114150</v>
+      </c>
+      <c r="B96" t="n">
+        <v>57982</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>706541</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7426780</v>
+      </c>
+      <c r="S96" t="n">
+        <v>3</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136114150</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>133888827</v>
+      </c>
+      <c r="B97" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>706811</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7426646</v>
+      </c>
+      <c r="S97" t="n">
+        <v>3</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133888827</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>134102287</v>
+      </c>
+      <c r="B98" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>706951</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7426689</v>
+      </c>
+      <c r="S98" t="n">
+        <v>3</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134102287</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>134272743</v>
+      </c>
+      <c r="B99" t="n">
+        <v>57162</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>706576</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7426767</v>
+      </c>
+      <c r="S99" t="n">
+        <v>3</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Otroligt mycket spillning på stenkulle</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272743</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>136114155</v>
+      </c>
+      <c r="B100" t="n">
+        <v>5498</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>101410</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Reliktbock</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Nothorhina muricata</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Dalman, 1817)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>706537</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7426777</v>
+      </c>
+      <c r="S100" t="n">
+        <v>3</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136114155</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>136114152</v>
+      </c>
+      <c r="B101" t="n">
+        <v>58143</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>707003</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7426526</v>
+      </c>
+      <c r="S101" t="n">
+        <v>3</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136114152</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>134272742</v>
+      </c>
+      <c r="B102" t="n">
+        <v>58839</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>706447</v>
+      </c>
+      <c r="R102" t="n">
+        <v>7426815</v>
+      </c>
+      <c r="S102" t="n">
+        <v>3</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272742</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>134272878</v>
+      </c>
+      <c r="B103" t="n">
+        <v>58839</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>706913</v>
+      </c>
+      <c r="R103" t="n">
+        <v>7426789</v>
+      </c>
+      <c r="S103" t="n">
+        <v>3</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272878</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>134272879</v>
+      </c>
+      <c r="B104" t="n">
+        <v>58839</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>706948</v>
+      </c>
+      <c r="R104" t="n">
+        <v>7426772</v>
+      </c>
+      <c r="S104" t="n">
+        <v>3</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272879</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>136114159</v>
+      </c>
+      <c r="B105" t="n">
+        <v>108055</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>219933</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Kattfot</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Antennaria dioica</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>706490</v>
+      </c>
+      <c r="R105" t="n">
+        <v>7426729</v>
+      </c>
+      <c r="S105" t="n">
+        <v>3</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136114159</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>136114166</v>
+      </c>
+      <c r="B106" t="n">
+        <v>110263</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>220294</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Fjällskära</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Saussurea alpina</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(L.) DC.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>706470</v>
+      </c>
+      <c r="R106" t="n">
+        <v>7426725</v>
+      </c>
+      <c r="S106" t="n">
+        <v>3</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136114166</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>134272741</v>
+      </c>
+      <c r="B107" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>706510</v>
+      </c>
+      <c r="R107" t="n">
+        <v>7426625</v>
+      </c>
+      <c r="S107" t="n">
+        <v>3</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272741</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>134272876</v>
+      </c>
+      <c r="B108" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>706861</v>
+      </c>
+      <c r="R108" t="n">
+        <v>7426790</v>
+      </c>
+      <c r="S108" t="n">
+        <v>3</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272876</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>136114156</v>
+      </c>
+      <c r="B109" t="n">
+        <v>98161</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>706495</v>
+      </c>
+      <c r="R109" t="n">
+        <v>7426742</v>
+      </c>
+      <c r="S109" t="n">
+        <v>3</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136114156</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>133888828</v>
+      </c>
+      <c r="B110" t="n">
+        <v>104707</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>706508</v>
+      </c>
+      <c r="R110" t="n">
+        <v>7426811</v>
+      </c>
+      <c r="S110" t="n">
+        <v>3</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133888828</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>134272752</v>
+      </c>
+      <c r="B111" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>706597</v>
+      </c>
+      <c r="R111" t="n">
+        <v>7426486</v>
+      </c>
+      <c r="S111" t="n">
+        <v>3</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272752</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>134272877</v>
+      </c>
+      <c r="B112" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>706475</v>
+      </c>
+      <c r="R112" t="n">
+        <v>7426738</v>
+      </c>
+      <c r="S112" t="n">
+        <v>3</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272877</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>136114148</v>
+      </c>
+      <c r="B113" t="n">
+        <v>80033</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>706954</v>
+      </c>
+      <c r="R113" t="n">
+        <v>7426529</v>
+      </c>
+      <c r="S113" t="n">
+        <v>3</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136114148</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>134272744</v>
+      </c>
+      <c r="B114" t="n">
+        <v>79899</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>229830</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Späd brosklav</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Ramalina dilacerata</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>706239</v>
+      </c>
+      <c r="R114" t="n">
+        <v>7426846</v>
+      </c>
+      <c r="S114" t="n">
+        <v>3</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272744</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>134272745</v>
+      </c>
+      <c r="B115" t="n">
+        <v>79899</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>229830</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Späd brosklav</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Ramalina dilacerata</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>706278</v>
+      </c>
+      <c r="R115" t="n">
+        <v>7426914</v>
+      </c>
+      <c r="S115" t="n">
+        <v>3</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/134272745</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>136114154</v>
+      </c>
+      <c r="B116" t="n">
+        <v>79466</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>706991</v>
+      </c>
+      <c r="R116" t="n">
+        <v>7426530</v>
+      </c>
+      <c r="S116" t="n">
+        <v>3</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136114154</t>
         </is>
       </c>
     </row>
@@ -10435,6 +12577,27 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55525-2025 artfynd.xlsx
+++ b/artfynd/A 55525-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136114146</v>
       </c>
       <c r="B2" t="n">
-        <v>97530</v>
+        <v>97531</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136114163</v>
       </c>
       <c r="B3" t="n">
-        <v>92310</v>
+        <v>92311</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136114165</v>
       </c>
       <c r="B4" t="n">
-        <v>92310</v>
+        <v>92311</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>136114167</v>
       </c>
       <c r="B22" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>136114162</v>
       </c>
       <c r="B68" t="n">
-        <v>79512</v>
+        <v>79513</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>136114161</v>
       </c>
       <c r="B78" t="n">
-        <v>92243</v>
+        <v>92244</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         <v>136114157</v>
       </c>
       <c r="B80" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>136114153</v>
       </c>
       <c r="B81" t="n">
-        <v>93387</v>
+        <v>93388</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>136114158</v>
       </c>
       <c r="B82" t="n">
-        <v>92192</v>
+        <v>92193</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>136114149</v>
       </c>
       <c r="B83" t="n">
-        <v>87460</v>
+        <v>87461</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>136114151</v>
       </c>
       <c r="B86" t="n">
-        <v>89223</v>
+        <v>89224</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>136114145</v>
       </c>
       <c r="B87" t="n">
-        <v>83430</v>
+        <v>83431</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>136114147</v>
       </c>
       <c r="B92" t="n">
-        <v>80062</v>
+        <v>80063</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         <v>136114159</v>
       </c>
       <c r="B105" t="n">
-        <v>108055</v>
+        <v>108057</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>136114166</v>
       </c>
       <c r="B106" t="n">
-        <v>110263</v>
+        <v>110265</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>136114156</v>
       </c>
       <c r="B109" t="n">
-        <v>98161</v>
+        <v>98162</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>136114148</v>
       </c>
       <c r="B113" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12384,7 +12384,7 @@
         <v>136114154</v>
       </c>
       <c r="B116" t="n">
-        <v>79466</v>
+        <v>79467</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 55525-2025 artfynd.xlsx
+++ b/artfynd/A 55525-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136114146</v>
       </c>
       <c r="B2" t="n">
-        <v>97531</v>
+        <v>97532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136114163</v>
       </c>
       <c r="B3" t="n">
-        <v>92311</v>
+        <v>92312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136114165</v>
       </c>
       <c r="B4" t="n">
-        <v>92311</v>
+        <v>92312</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>136114161</v>
       </c>
       <c r="B78" t="n">
-        <v>92244</v>
+        <v>92245</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         <v>136114157</v>
       </c>
       <c r="B80" t="n">
-        <v>92118</v>
+        <v>92119</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>136114153</v>
       </c>
       <c r="B81" t="n">
-        <v>93388</v>
+        <v>93389</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>136114158</v>
       </c>
       <c r="B82" t="n">
-        <v>92193</v>
+        <v>92194</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>136114149</v>
       </c>
       <c r="B83" t="n">
-        <v>87461</v>
+        <v>87462</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>136114151</v>
       </c>
       <c r="B86" t="n">
-        <v>89224</v>
+        <v>89225</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         <v>136114159</v>
       </c>
       <c r="B105" t="n">
-        <v>108057</v>
+        <v>108058</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>136114166</v>
       </c>
       <c r="B106" t="n">
-        <v>110265</v>
+        <v>110266</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>136114156</v>
       </c>
       <c r="B109" t="n">
-        <v>98162</v>
+        <v>98163</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>

--- a/artfynd/A 55525-2025 artfynd.xlsx
+++ b/artfynd/A 55525-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136114146</v>
       </c>
       <c r="B2" t="n">
-        <v>97532</v>
+        <v>97533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136114163</v>
       </c>
       <c r="B3" t="n">
-        <v>92312</v>
+        <v>92313</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136114165</v>
       </c>
       <c r="B4" t="n">
-        <v>92312</v>
+        <v>92313</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>136114167</v>
       </c>
       <c r="B22" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>136114162</v>
       </c>
       <c r="B68" t="n">
-        <v>79513</v>
+        <v>79514</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>136114161</v>
       </c>
       <c r="B78" t="n">
-        <v>92245</v>
+        <v>92246</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         <v>136114157</v>
       </c>
       <c r="B80" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>136114153</v>
       </c>
       <c r="B81" t="n">
-        <v>93389</v>
+        <v>93390</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>136114158</v>
       </c>
       <c r="B82" t="n">
-        <v>92194</v>
+        <v>92195</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>136114149</v>
       </c>
       <c r="B83" t="n">
-        <v>87462</v>
+        <v>87463</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>136114151</v>
       </c>
       <c r="B86" t="n">
-        <v>89225</v>
+        <v>89226</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>136114145</v>
       </c>
       <c r="B87" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>136114147</v>
       </c>
       <c r="B92" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>136114150</v>
       </c>
       <c r="B96" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>136114152</v>
       </c>
       <c r="B101" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         <v>136114159</v>
       </c>
       <c r="B105" t="n">
-        <v>108058</v>
+        <v>108059</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>136114166</v>
       </c>
       <c r="B106" t="n">
-        <v>110266</v>
+        <v>110267</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>136114156</v>
       </c>
       <c r="B109" t="n">
-        <v>98163</v>
+        <v>98164</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>136114148</v>
       </c>
       <c r="B113" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12384,7 +12384,7 @@
         <v>136114154</v>
       </c>
       <c r="B116" t="n">
-        <v>79467</v>
+        <v>79468</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 55525-2025 artfynd.xlsx
+++ b/artfynd/A 55525-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136114146</v>
       </c>
       <c r="B2" t="n">
-        <v>97533</v>
+        <v>97539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136114163</v>
       </c>
       <c r="B3" t="n">
-        <v>92313</v>
+        <v>92319</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136114165</v>
       </c>
       <c r="B4" t="n">
-        <v>92313</v>
+        <v>92319</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2768,7 +2768,7 @@
         <v>136114167</v>
       </c>
       <c r="B22" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -7460,7 +7460,7 @@
         <v>136114162</v>
       </c>
       <c r="B68" t="n">
-        <v>79514</v>
+        <v>79518</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8480,7 +8480,7 @@
         <v>136114161</v>
       </c>
       <c r="B78" t="n">
-        <v>92246</v>
+        <v>92252</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8693,7 +8693,7 @@
         <v>136114157</v>
       </c>
       <c r="B80" t="n">
-        <v>92120</v>
+        <v>92126</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8795,7 +8795,7 @@
         <v>136114153</v>
       </c>
       <c r="B81" t="n">
-        <v>93390</v>
+        <v>93396</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8897,7 +8897,7 @@
         <v>136114158</v>
       </c>
       <c r="B82" t="n">
-        <v>92195</v>
+        <v>92201</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8999,7 +8999,7 @@
         <v>136114149</v>
       </c>
       <c r="B83" t="n">
-        <v>87463</v>
+        <v>87469</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9314,7 +9314,7 @@
         <v>136114151</v>
       </c>
       <c r="B86" t="n">
-        <v>89226</v>
+        <v>89232</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>136114145</v>
       </c>
       <c r="B87" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>136114147</v>
       </c>
       <c r="B92" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10334,7 +10334,7 @@
         <v>136114150</v>
       </c>
       <c r="B96" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>136114152</v>
       </c>
       <c r="B101" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         <v>136114159</v>
       </c>
       <c r="B105" t="n">
-        <v>108059</v>
+        <v>108065</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11364,7 +11364,7 @@
         <v>136114166</v>
       </c>
       <c r="B106" t="n">
-        <v>110267</v>
+        <v>110273</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11670,7 +11670,7 @@
         <v>136114156</v>
       </c>
       <c r="B109" t="n">
-        <v>98164</v>
+        <v>98170</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12078,7 +12078,7 @@
         <v>136114148</v>
       </c>
       <c r="B113" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12384,7 +12384,7 @@
         <v>136114154</v>
       </c>
       <c r="B116" t="n">
-        <v>79468</v>
+        <v>79472</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>

--- a/artfynd/A 55525-2025 artfynd.xlsx
+++ b/artfynd/A 55525-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ116"/>
+  <dimension ref="A1:AZ130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>136114146</v>
       </c>
       <c r="B2" t="n">
-        <v>97539</v>
+        <v>97540</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136114163</v>
       </c>
       <c r="B3" t="n">
-        <v>92319</v>
+        <v>92320</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136114165</v>
       </c>
       <c r="B4" t="n">
-        <v>92319</v>
+        <v>92320</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133888829</v>
+        <v>136331401</v>
       </c>
       <c r="B5" t="n">
-        <v>99084</v>
+        <v>92320</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>233</v>
+        <v>65</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>706484</v>
+        <v>706499</v>
       </c>
       <c r="R5" t="n">
-        <v>7426734</v>
+        <v>7426693</v>
       </c>
       <c r="S5" t="n">
         <v>3</v>
@@ -1051,17 +1051,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2 blommor</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1087,16 +1082,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133888829</t>
+          <t>https://artportalen.se/Sighting/136331401</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133888830</v>
+        <v>136331402</v>
       </c>
       <c r="B6" t="n">
-        <v>99084</v>
+        <v>92320</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1104,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>233</v>
+        <v>65</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>706475</v>
+        <v>706496</v>
       </c>
       <c r="R6" t="n">
-        <v>7426727</v>
+        <v>7426676</v>
       </c>
       <c r="S6" t="n">
         <v>3</v>
@@ -1158,17 +1153,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>5 blommor</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1194,16 +1184,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133888830</t>
+          <t>https://artportalen.se/Sighting/136331402</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133888831</v>
+        <v>136331403</v>
       </c>
       <c r="B7" t="n">
-        <v>99084</v>
+        <v>92320</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1211,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>233</v>
+        <v>65</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1235,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>706466</v>
+        <v>706468</v>
       </c>
       <c r="R7" t="n">
-        <v>7426731</v>
+        <v>7426685</v>
       </c>
       <c r="S7" t="n">
         <v>3</v>
@@ -1265,17 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>9 blommor</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1301,16 +1286,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133888831</t>
+          <t>https://artportalen.se/Sighting/136331403</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133888832</v>
+        <v>136331404</v>
       </c>
       <c r="B8" t="n">
-        <v>99084</v>
+        <v>92320</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1318,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>233</v>
+        <v>65</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>706457</v>
+        <v>706475</v>
       </c>
       <c r="R8" t="n">
-        <v>7426725</v>
+        <v>7426674</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1372,17 +1357,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>3 blommor</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1408,16 +1388,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133888832</t>
+          <t>https://artportalen.se/Sighting/136331404</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133888833</v>
+        <v>136331405</v>
       </c>
       <c r="B9" t="n">
-        <v>99084</v>
+        <v>92320</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1425,21 +1405,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>233</v>
+        <v>65</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1449,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>706441</v>
+        <v>706480</v>
       </c>
       <c r="R9" t="n">
-        <v>7426721</v>
+        <v>7426712</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
@@ -1479,12 +1459,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1510,16 +1490,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133888833</t>
+          <t>https://artportalen.se/Sighting/136331405</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133888834</v>
+        <v>136331406</v>
       </c>
       <c r="B10" t="n">
-        <v>99084</v>
+        <v>92320</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1527,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>233</v>
+        <v>65</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>706459</v>
+        <v>706682</v>
       </c>
       <c r="R10" t="n">
-        <v>7426728</v>
+        <v>7426646</v>
       </c>
       <c r="S10" t="n">
         <v>3</v>
@@ -1581,12 +1561,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1612,38 +1592,38 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133888834</t>
+          <t>https://artportalen.se/Sighting/136331406</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133888835</v>
+        <v>136331398</v>
       </c>
       <c r="B11" t="n">
-        <v>99084</v>
+        <v>92024</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>233</v>
+        <v>112</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>706462</v>
+        <v>706722</v>
       </c>
       <c r="R11" t="n">
-        <v>7426725</v>
+        <v>7426552</v>
       </c>
       <c r="S11" t="n">
         <v>3</v>
@@ -1683,17 +1663,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>5 blommor</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1719,38 +1694,38 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133888835</t>
+          <t>https://artportalen.se/Sighting/136331398</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133888836</v>
+        <v>136331399</v>
       </c>
       <c r="B12" t="n">
-        <v>99084</v>
+        <v>92024</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>233</v>
+        <v>112</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Norna</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calypso bulbosa</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Oakes</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>706505</v>
+        <v>706710</v>
       </c>
       <c r="R12" t="n">
-        <v>7426733</v>
+        <v>7426559</v>
       </c>
       <c r="S12" t="n">
         <v>3</v>
@@ -1790,12 +1765,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1821,13 +1796,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133888836</t>
+          <t>https://artportalen.se/Sighting/136331399</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133888837</v>
+        <v>133888829</v>
       </c>
       <c r="B13" t="n">
         <v>99084</v>
@@ -1862,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>706498</v>
+        <v>706484</v>
       </c>
       <c r="R13" t="n">
-        <v>7426729</v>
+        <v>7426734</v>
       </c>
       <c r="S13" t="n">
         <v>3</v>
@@ -1900,6 +1875,11 @@
           <t>2026-05-25</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>2 blommor</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1923,13 +1903,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133888837</t>
+          <t>https://artportalen.se/Sighting/133888829</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133888838</v>
+        <v>133888830</v>
       </c>
       <c r="B14" t="n">
         <v>99084</v>
@@ -1964,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>706493</v>
+        <v>706475</v>
       </c>
       <c r="R14" t="n">
-        <v>7426724</v>
+        <v>7426727</v>
       </c>
       <c r="S14" t="n">
         <v>3</v>
@@ -2002,6 +1982,11 @@
           <t>2026-05-25</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>5 blommor</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2025,13 +2010,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133888838</t>
+          <t>https://artportalen.se/Sighting/133888830</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133888839</v>
+        <v>133888831</v>
       </c>
       <c r="B15" t="n">
         <v>99084</v>
@@ -2066,7 +2051,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>706491</v>
+        <v>706466</v>
       </c>
       <c r="R15" t="n">
         <v>7426731</v>
@@ -2106,7 +2091,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Två blommor</t>
+          <t>9 blommor</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2132,13 +2117,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133888839</t>
+          <t>https://artportalen.se/Sighting/133888831</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134102329</v>
+        <v>133888832</v>
       </c>
       <c r="B16" t="n">
         <v>99084</v>
@@ -2173,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>706942</v>
+        <v>706457</v>
       </c>
       <c r="R16" t="n">
-        <v>7426762</v>
+        <v>7426725</v>
       </c>
       <c r="S16" t="n">
         <v>3</v>
@@ -2203,17 +2188,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>En blomma</t>
+          <t>3 blommor</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2239,13 +2224,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102329</t>
+          <t>https://artportalen.se/Sighting/133888832</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134102330</v>
+        <v>133888833</v>
       </c>
       <c r="B17" t="n">
         <v>99084</v>
@@ -2280,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>706920</v>
+        <v>706441</v>
       </c>
       <c r="R17" t="n">
-        <v>7426776</v>
+        <v>7426721</v>
       </c>
       <c r="S17" t="n">
         <v>3</v>
@@ -2310,12 +2295,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2341,13 +2326,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102330</t>
+          <t>https://artportalen.se/Sighting/133888833</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134272750</v>
+        <v>133888834</v>
       </c>
       <c r="B18" t="n">
         <v>99084</v>
@@ -2382,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>706247</v>
+        <v>706459</v>
       </c>
       <c r="R18" t="n">
-        <v>7426954</v>
+        <v>7426728</v>
       </c>
       <c r="S18" t="n">
         <v>3</v>
@@ -2412,17 +2397,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>4 blommor</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2448,13 +2428,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272750</t>
+          <t>https://artportalen.se/Sighting/133888834</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134272751</v>
+        <v>133888835</v>
       </c>
       <c r="B19" t="n">
         <v>99084</v>
@@ -2489,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>706204</v>
+        <v>706462</v>
       </c>
       <c r="R19" t="n">
-        <v>7426971</v>
+        <v>7426725</v>
       </c>
       <c r="S19" t="n">
         <v>3</v>
@@ -2519,17 +2499,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>1 blommande</t>
+          <t>5 blommor</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2555,38 +2535,38 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272751</t>
+          <t>https://artportalen.se/Sighting/133888835</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134272754</v>
+        <v>133888836</v>
       </c>
       <c r="B20" t="n">
-        <v>79039</v>
+        <v>99084</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>353</v>
+        <v>233</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2596,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>706491</v>
+        <v>706505</v>
       </c>
       <c r="R20" t="n">
-        <v>7426611</v>
+        <v>7426733</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
@@ -2626,12 +2606,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2657,38 +2637,38 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272754</t>
+          <t>https://artportalen.se/Sighting/133888836</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134272755</v>
+        <v>133888837</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>99084</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>353</v>
+        <v>233</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2698,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>706573</v>
+        <v>706498</v>
       </c>
       <c r="R21" t="n">
-        <v>7426540</v>
+        <v>7426729</v>
       </c>
       <c r="S21" t="n">
         <v>3</v>
@@ -2728,12 +2708,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2759,38 +2739,38 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272755</t>
+          <t>https://artportalen.se/Sighting/133888837</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136114167</v>
+        <v>133888838</v>
       </c>
       <c r="B22" t="n">
-        <v>79115</v>
+        <v>99084</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>233</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2800,10 +2780,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>707017</v>
+        <v>706493</v>
       </c>
       <c r="R22" t="n">
-        <v>7426508</v>
+        <v>7426724</v>
       </c>
       <c r="S22" t="n">
         <v>3</v>
@@ -2830,12 +2810,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2861,16 +2841,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136114167</t>
+          <t>https://artportalen.se/Sighting/133888838</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134102288</v>
+        <v>133888839</v>
       </c>
       <c r="B23" t="n">
-        <v>79440</v>
+        <v>99084</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2878,21 +2858,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>637</v>
+        <v>233</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2902,10 +2882,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>706968</v>
+        <v>706491</v>
       </c>
       <c r="R23" t="n">
-        <v>7426698</v>
+        <v>7426731</v>
       </c>
       <c r="S23" t="n">
         <v>3</v>
@@ -2932,12 +2912,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Två blommor</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2963,16 +2948,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102288</t>
+          <t>https://artportalen.se/Sighting/133888839</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134102289</v>
+        <v>134102329</v>
       </c>
       <c r="B24" t="n">
-        <v>79440</v>
+        <v>99084</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2980,21 +2965,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>637</v>
+        <v>233</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3004,10 +2989,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>706941</v>
+        <v>706942</v>
       </c>
       <c r="R24" t="n">
-        <v>7426720</v>
+        <v>7426762</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -3042,6 +3027,11 @@
           <t>2026-06-04</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>En blomma</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3065,16 +3055,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102289</t>
+          <t>https://artportalen.se/Sighting/134102329</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134102290</v>
+        <v>134102330</v>
       </c>
       <c r="B25" t="n">
-        <v>79440</v>
+        <v>99084</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3082,21 +3072,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>637</v>
+        <v>233</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3106,10 +3096,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>706918</v>
+        <v>706920</v>
       </c>
       <c r="R25" t="n">
-        <v>7426756</v>
+        <v>7426776</v>
       </c>
       <c r="S25" t="n">
         <v>3</v>
@@ -3167,16 +3157,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102290</t>
+          <t>https://artportalen.se/Sighting/134102330</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134102291</v>
+        <v>134272750</v>
       </c>
       <c r="B26" t="n">
-        <v>79440</v>
+        <v>99084</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3184,21 +3174,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>637</v>
+        <v>233</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3208,10 +3198,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>706899</v>
+        <v>706247</v>
       </c>
       <c r="R26" t="n">
-        <v>7426771</v>
+        <v>7426954</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3238,12 +3228,17 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>4 blommor</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3269,16 +3264,16 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102291</t>
+          <t>https://artportalen.se/Sighting/134272750</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134102292</v>
+        <v>134272751</v>
       </c>
       <c r="B27" t="n">
-        <v>79440</v>
+        <v>99084</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3286,21 +3281,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>637</v>
+        <v>233</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Norna</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Calypso bulbosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Oakes</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3310,10 +3305,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>706891</v>
+        <v>706204</v>
       </c>
       <c r="R27" t="n">
-        <v>7426771</v>
+        <v>7426971</v>
       </c>
       <c r="S27" t="n">
         <v>3</v>
@@ -3340,12 +3335,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>1 blommande</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3371,38 +3371,38 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102292</t>
+          <t>https://artportalen.se/Sighting/134272751</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134102293</v>
+        <v>134272754</v>
       </c>
       <c r="B28" t="n">
-        <v>79440</v>
+        <v>79039</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>637</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3412,10 +3412,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>706890</v>
+        <v>706491</v>
       </c>
       <c r="R28" t="n">
-        <v>7426773</v>
+        <v>7426611</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -3442,12 +3442,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3473,38 +3473,38 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102293</t>
+          <t>https://artportalen.se/Sighting/134272754</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134102294</v>
+        <v>134272755</v>
       </c>
       <c r="B29" t="n">
-        <v>79440</v>
+        <v>79039</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>637</v>
+        <v>353</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3514,10 +3514,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>706878</v>
+        <v>706573</v>
       </c>
       <c r="R29" t="n">
-        <v>7426778</v>
+        <v>7426540</v>
       </c>
       <c r="S29" t="n">
         <v>3</v>
@@ -3544,12 +3544,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3575,38 +3575,38 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102294</t>
+          <t>https://artportalen.se/Sighting/134272755</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134102295</v>
+        <v>136114167</v>
       </c>
       <c r="B30" t="n">
-        <v>79440</v>
+        <v>79116</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>637</v>
+        <v>353</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ringlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Evernia divaricata</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3616,10 +3616,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>706859</v>
+        <v>707017</v>
       </c>
       <c r="R30" t="n">
-        <v>7426782</v>
+        <v>7426508</v>
       </c>
       <c r="S30" t="n">
         <v>3</v>
@@ -3646,12 +3646,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3677,13 +3677,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102295</t>
+          <t>https://artportalen.se/Sighting/136114167</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134102296</v>
+        <v>134102288</v>
       </c>
       <c r="B31" t="n">
         <v>79440</v>
@@ -3718,10 +3718,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>706851</v>
+        <v>706968</v>
       </c>
       <c r="R31" t="n">
-        <v>7426782</v>
+        <v>7426698</v>
       </c>
       <c r="S31" t="n">
         <v>3</v>
@@ -3779,13 +3779,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102296</t>
+          <t>https://artportalen.se/Sighting/134102288</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134102297</v>
+        <v>134102289</v>
       </c>
       <c r="B32" t="n">
         <v>79440</v>
@@ -3820,10 +3820,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>706834</v>
+        <v>706941</v>
       </c>
       <c r="R32" t="n">
-        <v>7426787</v>
+        <v>7426720</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
@@ -3881,13 +3881,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102297</t>
+          <t>https://artportalen.se/Sighting/134102289</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134102298</v>
+        <v>134102290</v>
       </c>
       <c r="B33" t="n">
         <v>79440</v>
@@ -3922,10 +3922,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>706810</v>
+        <v>706918</v>
       </c>
       <c r="R33" t="n">
-        <v>7426802</v>
+        <v>7426756</v>
       </c>
       <c r="S33" t="n">
         <v>3</v>
@@ -3983,13 +3983,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102298</t>
+          <t>https://artportalen.se/Sighting/134102290</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134102299</v>
+        <v>134102291</v>
       </c>
       <c r="B34" t="n">
         <v>79440</v>
@@ -4024,10 +4024,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>706809</v>
+        <v>706899</v>
       </c>
       <c r="R34" t="n">
-        <v>7426819</v>
+        <v>7426771</v>
       </c>
       <c r="S34" t="n">
         <v>3</v>
@@ -4085,13 +4085,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102299</t>
+          <t>https://artportalen.se/Sighting/134102291</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134102300</v>
+        <v>134102292</v>
       </c>
       <c r="B35" t="n">
         <v>79440</v>
@@ -4126,10 +4126,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>706796</v>
+        <v>706891</v>
       </c>
       <c r="R35" t="n">
-        <v>7426839</v>
+        <v>7426771</v>
       </c>
       <c r="S35" t="n">
         <v>3</v>
@@ -4187,13 +4187,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102300</t>
+          <t>https://artportalen.se/Sighting/134102292</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134102301</v>
+        <v>134102293</v>
       </c>
       <c r="B36" t="n">
         <v>79440</v>
@@ -4228,10 +4228,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>706805</v>
+        <v>706890</v>
       </c>
       <c r="R36" t="n">
-        <v>7426845</v>
+        <v>7426773</v>
       </c>
       <c r="S36" t="n">
         <v>3</v>
@@ -4289,13 +4289,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102301</t>
+          <t>https://artportalen.se/Sighting/134102293</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134102302</v>
+        <v>134102294</v>
       </c>
       <c r="B37" t="n">
         <v>79440</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>706816</v>
+        <v>706878</v>
       </c>
       <c r="R37" t="n">
-        <v>7426823</v>
+        <v>7426778</v>
       </c>
       <c r="S37" t="n">
         <v>3</v>
@@ -4391,13 +4391,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102302</t>
+          <t>https://artportalen.se/Sighting/134102294</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134102303</v>
+        <v>134102295</v>
       </c>
       <c r="B38" t="n">
         <v>79440</v>
@@ -4432,10 +4432,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>706841</v>
+        <v>706859</v>
       </c>
       <c r="R38" t="n">
-        <v>7426814</v>
+        <v>7426782</v>
       </c>
       <c r="S38" t="n">
         <v>3</v>
@@ -4493,13 +4493,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102303</t>
+          <t>https://artportalen.se/Sighting/134102295</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134102304</v>
+        <v>134102296</v>
       </c>
       <c r="B39" t="n">
         <v>79440</v>
@@ -4534,10 +4534,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>706855</v>
+        <v>706851</v>
       </c>
       <c r="R39" t="n">
-        <v>7426811</v>
+        <v>7426782</v>
       </c>
       <c r="S39" t="n">
         <v>3</v>
@@ -4595,13 +4595,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102304</t>
+          <t>https://artportalen.se/Sighting/134102296</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134102305</v>
+        <v>134102297</v>
       </c>
       <c r="B40" t="n">
         <v>79440</v>
@@ -4636,10 +4636,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>706852</v>
+        <v>706834</v>
       </c>
       <c r="R40" t="n">
-        <v>7426799</v>
+        <v>7426787</v>
       </c>
       <c r="S40" t="n">
         <v>3</v>
@@ -4697,13 +4697,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102305</t>
+          <t>https://artportalen.se/Sighting/134102297</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134102306</v>
+        <v>134102298</v>
       </c>
       <c r="B41" t="n">
         <v>79440</v>
@@ -4738,10 +4738,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>706863</v>
+        <v>706810</v>
       </c>
       <c r="R41" t="n">
-        <v>7426795</v>
+        <v>7426802</v>
       </c>
       <c r="S41" t="n">
         <v>3</v>
@@ -4799,13 +4799,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102306</t>
+          <t>https://artportalen.se/Sighting/134102298</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134102307</v>
+        <v>134102299</v>
       </c>
       <c r="B42" t="n">
         <v>79440</v>
@@ -4840,10 +4840,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>706875</v>
+        <v>706809</v>
       </c>
       <c r="R42" t="n">
-        <v>7426805</v>
+        <v>7426819</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
@@ -4901,13 +4901,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102307</t>
+          <t>https://artportalen.se/Sighting/134102299</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134102309</v>
+        <v>134102300</v>
       </c>
       <c r="B43" t="n">
         <v>79440</v>
@@ -4942,10 +4942,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>706885</v>
+        <v>706796</v>
       </c>
       <c r="R43" t="n">
-        <v>7426802</v>
+        <v>7426839</v>
       </c>
       <c r="S43" t="n">
         <v>3</v>
@@ -5003,13 +5003,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102309</t>
+          <t>https://artportalen.se/Sighting/134102300</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134102310</v>
+        <v>134102301</v>
       </c>
       <c r="B44" t="n">
         <v>79440</v>
@@ -5044,10 +5044,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>706887</v>
+        <v>706805</v>
       </c>
       <c r="R44" t="n">
-        <v>7426800</v>
+        <v>7426845</v>
       </c>
       <c r="S44" t="n">
         <v>3</v>
@@ -5105,13 +5105,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102310</t>
+          <t>https://artportalen.se/Sighting/134102301</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134102311</v>
+        <v>134102302</v>
       </c>
       <c r="B45" t="n">
         <v>79440</v>
@@ -5146,10 +5146,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>706893</v>
+        <v>706816</v>
       </c>
       <c r="R45" t="n">
-        <v>7426806</v>
+        <v>7426823</v>
       </c>
       <c r="S45" t="n">
         <v>3</v>
@@ -5207,13 +5207,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102311</t>
+          <t>https://artportalen.se/Sighting/134102302</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134102312</v>
+        <v>134102303</v>
       </c>
       <c r="B46" t="n">
         <v>79440</v>
@@ -5248,10 +5248,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>706909</v>
+        <v>706841</v>
       </c>
       <c r="R46" t="n">
-        <v>7426793</v>
+        <v>7426814</v>
       </c>
       <c r="S46" t="n">
         <v>3</v>
@@ -5309,13 +5309,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102312</t>
+          <t>https://artportalen.se/Sighting/134102303</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134102313</v>
+        <v>134102304</v>
       </c>
       <c r="B47" t="n">
         <v>79440</v>
@@ -5350,10 +5350,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>706912</v>
+        <v>706855</v>
       </c>
       <c r="R47" t="n">
-        <v>7426790</v>
+        <v>7426811</v>
       </c>
       <c r="S47" t="n">
         <v>3</v>
@@ -5411,13 +5411,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102313</t>
+          <t>https://artportalen.se/Sighting/134102304</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134102314</v>
+        <v>134102305</v>
       </c>
       <c r="B48" t="n">
         <v>79440</v>
@@ -5452,10 +5452,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>706925</v>
+        <v>706852</v>
       </c>
       <c r="R48" t="n">
-        <v>7426791</v>
+        <v>7426799</v>
       </c>
       <c r="S48" t="n">
         <v>3</v>
@@ -5513,13 +5513,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102314</t>
+          <t>https://artportalen.se/Sighting/134102305</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134102315</v>
+        <v>134102306</v>
       </c>
       <c r="B49" t="n">
         <v>79440</v>
@@ -5554,10 +5554,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>706920</v>
+        <v>706863</v>
       </c>
       <c r="R49" t="n">
-        <v>7426784</v>
+        <v>7426795</v>
       </c>
       <c r="S49" t="n">
         <v>3</v>
@@ -5615,13 +5615,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102315</t>
+          <t>https://artportalen.se/Sighting/134102306</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134102316</v>
+        <v>134102307</v>
       </c>
       <c r="B50" t="n">
         <v>79440</v>
@@ -5656,10 +5656,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>706925</v>
+        <v>706875</v>
       </c>
       <c r="R50" t="n">
-        <v>7426793</v>
+        <v>7426805</v>
       </c>
       <c r="S50" t="n">
         <v>3</v>
@@ -5717,13 +5717,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102316</t>
+          <t>https://artportalen.se/Sighting/134102307</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134102317</v>
+        <v>134102309</v>
       </c>
       <c r="B51" t="n">
         <v>79440</v>
@@ -5758,10 +5758,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>706934</v>
+        <v>706885</v>
       </c>
       <c r="R51" t="n">
-        <v>7426777</v>
+        <v>7426802</v>
       </c>
       <c r="S51" t="n">
         <v>3</v>
@@ -5819,13 +5819,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102317</t>
+          <t>https://artportalen.se/Sighting/134102309</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134102318</v>
+        <v>134102310</v>
       </c>
       <c r="B52" t="n">
         <v>79440</v>
@@ -5860,10 +5860,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>706944</v>
+        <v>706887</v>
       </c>
       <c r="R52" t="n">
-        <v>7426769</v>
+        <v>7426800</v>
       </c>
       <c r="S52" t="n">
         <v>3</v>
@@ -5921,13 +5921,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102318</t>
+          <t>https://artportalen.se/Sighting/134102310</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134102319</v>
+        <v>134102311</v>
       </c>
       <c r="B53" t="n">
         <v>79440</v>
@@ -5962,10 +5962,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>706952</v>
+        <v>706893</v>
       </c>
       <c r="R53" t="n">
-        <v>7426764</v>
+        <v>7426806</v>
       </c>
       <c r="S53" t="n">
         <v>3</v>
@@ -6023,13 +6023,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102319</t>
+          <t>https://artportalen.se/Sighting/134102311</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134102320</v>
+        <v>134102312</v>
       </c>
       <c r="B54" t="n">
         <v>79440</v>
@@ -6064,10 +6064,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>706960</v>
+        <v>706909</v>
       </c>
       <c r="R54" t="n">
-        <v>7426760</v>
+        <v>7426793</v>
       </c>
       <c r="S54" t="n">
         <v>3</v>
@@ -6125,13 +6125,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102320</t>
+          <t>https://artportalen.se/Sighting/134102312</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134102321</v>
+        <v>134102313</v>
       </c>
       <c r="B55" t="n">
         <v>79440</v>
@@ -6166,10 +6166,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>706970</v>
+        <v>706912</v>
       </c>
       <c r="R55" t="n">
-        <v>7426748</v>
+        <v>7426790</v>
       </c>
       <c r="S55" t="n">
         <v>3</v>
@@ -6227,13 +6227,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102321</t>
+          <t>https://artportalen.se/Sighting/134102313</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134102322</v>
+        <v>134102314</v>
       </c>
       <c r="B56" t="n">
         <v>79440</v>
@@ -6268,10 +6268,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>706963</v>
+        <v>706925</v>
       </c>
       <c r="R56" t="n">
-        <v>7426740</v>
+        <v>7426791</v>
       </c>
       <c r="S56" t="n">
         <v>3</v>
@@ -6298,12 +6298,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6329,13 +6329,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102322</t>
+          <t>https://artportalen.se/Sighting/134102314</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134102323</v>
+        <v>134102315</v>
       </c>
       <c r="B57" t="n">
         <v>79440</v>
@@ -6370,10 +6370,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>706967</v>
+        <v>706920</v>
       </c>
       <c r="R57" t="n">
-        <v>7426729</v>
+        <v>7426784</v>
       </c>
       <c r="S57" t="n">
         <v>3</v>
@@ -6400,12 +6400,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6431,13 +6431,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102323</t>
+          <t>https://artportalen.se/Sighting/134102315</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134102324</v>
+        <v>134102316</v>
       </c>
       <c r="B58" t="n">
         <v>79440</v>
@@ -6472,10 +6472,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>706968</v>
+        <v>706925</v>
       </c>
       <c r="R58" t="n">
-        <v>7426683</v>
+        <v>7426793</v>
       </c>
       <c r="S58" t="n">
         <v>3</v>
@@ -6502,12 +6502,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6533,13 +6533,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102324</t>
+          <t>https://artportalen.se/Sighting/134102316</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134102325</v>
+        <v>134102317</v>
       </c>
       <c r="B59" t="n">
         <v>79440</v>
@@ -6574,10 +6574,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>706955</v>
+        <v>706934</v>
       </c>
       <c r="R59" t="n">
-        <v>7426674</v>
+        <v>7426777</v>
       </c>
       <c r="S59" t="n">
         <v>3</v>
@@ -6604,12 +6604,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6635,13 +6635,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102325</t>
+          <t>https://artportalen.se/Sighting/134102317</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134102326</v>
+        <v>134102318</v>
       </c>
       <c r="B60" t="n">
         <v>79440</v>
@@ -6676,10 +6676,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>706941</v>
+        <v>706944</v>
       </c>
       <c r="R60" t="n">
-        <v>7426672</v>
+        <v>7426769</v>
       </c>
       <c r="S60" t="n">
         <v>3</v>
@@ -6706,12 +6706,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6737,13 +6737,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102326</t>
+          <t>https://artportalen.se/Sighting/134102318</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>134102327</v>
+        <v>134102319</v>
       </c>
       <c r="B61" t="n">
         <v>79440</v>
@@ -6778,10 +6778,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>706944</v>
+        <v>706952</v>
       </c>
       <c r="R61" t="n">
-        <v>7426692</v>
+        <v>7426764</v>
       </c>
       <c r="S61" t="n">
         <v>3</v>
@@ -6808,12 +6808,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6839,13 +6839,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102327</t>
+          <t>https://artportalen.se/Sighting/134102319</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>134102328</v>
+        <v>134102320</v>
       </c>
       <c r="B62" t="n">
         <v>79440</v>
@@ -6880,10 +6880,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>706937</v>
+        <v>706960</v>
       </c>
       <c r="R62" t="n">
-        <v>7426690</v>
+        <v>7426760</v>
       </c>
       <c r="S62" t="n">
         <v>3</v>
@@ -6910,12 +6910,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6941,13 +6941,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102328</t>
+          <t>https://artportalen.se/Sighting/134102320</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>134102394</v>
+        <v>134102321</v>
       </c>
       <c r="B63" t="n">
         <v>79440</v>
@@ -6982,10 +6982,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>706913</v>
+        <v>706970</v>
       </c>
       <c r="R63" t="n">
-        <v>7426627</v>
+        <v>7426748</v>
       </c>
       <c r="S63" t="n">
         <v>3</v>
@@ -7043,13 +7043,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102394</t>
+          <t>https://artportalen.se/Sighting/134102321</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>134102395</v>
+        <v>134102322</v>
       </c>
       <c r="B64" t="n">
         <v>79440</v>
@@ -7084,10 +7084,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>706915</v>
+        <v>706963</v>
       </c>
       <c r="R64" t="n">
-        <v>7426639</v>
+        <v>7426740</v>
       </c>
       <c r="S64" t="n">
         <v>3</v>
@@ -7114,12 +7114,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7145,13 +7145,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102395</t>
+          <t>https://artportalen.se/Sighting/134102322</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>134102396</v>
+        <v>134102323</v>
       </c>
       <c r="B65" t="n">
         <v>79440</v>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>706917</v>
+        <v>706967</v>
       </c>
       <c r="R65" t="n">
-        <v>7426646</v>
+        <v>7426729</v>
       </c>
       <c r="S65" t="n">
         <v>3</v>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7247,13 +7247,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102396</t>
+          <t>https://artportalen.se/Sighting/134102323</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>134102397</v>
+        <v>134102324</v>
       </c>
       <c r="B66" t="n">
         <v>79440</v>
@@ -7288,10 +7288,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>706868</v>
+        <v>706968</v>
       </c>
       <c r="R66" t="n">
-        <v>7426681</v>
+        <v>7426683</v>
       </c>
       <c r="S66" t="n">
         <v>3</v>
@@ -7318,12 +7318,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7349,13 +7349,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102397</t>
+          <t>https://artportalen.se/Sighting/134102324</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>134272749</v>
+        <v>134102325</v>
       </c>
       <c r="B67" t="n">
         <v>79440</v>
@@ -7390,10 +7390,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>706238</v>
+        <v>706955</v>
       </c>
       <c r="R67" t="n">
-        <v>7426848</v>
+        <v>7426674</v>
       </c>
       <c r="S67" t="n">
         <v>3</v>
@@ -7420,12 +7420,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7451,16 +7451,16 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272749</t>
+          <t>https://artportalen.se/Sighting/134102325</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>136114162</v>
+        <v>134102326</v>
       </c>
       <c r="B68" t="n">
-        <v>79518</v>
+        <v>79440</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7468,21 +7468,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grenlav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Evernia mesomorpha</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Nyl.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7492,10 +7492,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>706836</v>
+        <v>706941</v>
       </c>
       <c r="R68" t="n">
-        <v>7426791</v>
+        <v>7426672</v>
       </c>
       <c r="S68" t="n">
         <v>3</v>
@@ -7522,12 +7522,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7553,38 +7553,38 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136114162</t>
+          <t>https://artportalen.se/Sighting/134102326</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134102332</v>
+        <v>134102327</v>
       </c>
       <c r="B69" t="n">
-        <v>79452</v>
+        <v>79440</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>864</v>
+        <v>637</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7594,10 +7594,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>706805</v>
+        <v>706944</v>
       </c>
       <c r="R69" t="n">
-        <v>7426821</v>
+        <v>7426692</v>
       </c>
       <c r="S69" t="n">
         <v>3</v>
@@ -7624,12 +7624,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7655,38 +7655,38 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102332</t>
+          <t>https://artportalen.se/Sighting/134102327</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134102333</v>
+        <v>134102328</v>
       </c>
       <c r="B70" t="n">
-        <v>79452</v>
+        <v>79440</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>864</v>
+        <v>637</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7696,10 +7696,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>706797</v>
+        <v>706937</v>
       </c>
       <c r="R70" t="n">
-        <v>7426837</v>
+        <v>7426690</v>
       </c>
       <c r="S70" t="n">
         <v>3</v>
@@ -7726,12 +7726,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7757,38 +7757,38 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102333</t>
+          <t>https://artportalen.se/Sighting/134102328</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>134102334</v>
+        <v>134102394</v>
       </c>
       <c r="B71" t="n">
-        <v>79452</v>
+        <v>79440</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>864</v>
+        <v>637</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7798,10 +7798,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>706856</v>
+        <v>706913</v>
       </c>
       <c r="R71" t="n">
-        <v>7426791</v>
+        <v>7426627</v>
       </c>
       <c r="S71" t="n">
         <v>3</v>
@@ -7859,38 +7859,38 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102334</t>
+          <t>https://artportalen.se/Sighting/134102394</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134272887</v>
+        <v>134102395</v>
       </c>
       <c r="B72" t="n">
-        <v>79452</v>
+        <v>79440</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>864</v>
+        <v>637</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7900,10 +7900,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>706763</v>
+        <v>706915</v>
       </c>
       <c r="R72" t="n">
-        <v>7426802</v>
+        <v>7426639</v>
       </c>
       <c r="S72" t="n">
         <v>3</v>
@@ -7930,12 +7930,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7961,38 +7961,38 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272887</t>
+          <t>https://artportalen.se/Sighting/134102395</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134102335</v>
+        <v>134102396</v>
       </c>
       <c r="B73" t="n">
-        <v>83222</v>
+        <v>79440</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1312</v>
+        <v>637</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8002,10 +8002,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>706856</v>
+        <v>706917</v>
       </c>
       <c r="R73" t="n">
-        <v>7426794</v>
+        <v>7426646</v>
       </c>
       <c r="S73" t="n">
         <v>3</v>
@@ -8063,38 +8063,38 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102335</t>
+          <t>https://artportalen.se/Sighting/134102396</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134102336</v>
+        <v>134102397</v>
       </c>
       <c r="B74" t="n">
-        <v>83222</v>
+        <v>79440</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1312</v>
+        <v>637</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8104,10 +8104,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>706796</v>
+        <v>706868</v>
       </c>
       <c r="R74" t="n">
-        <v>7426839</v>
+        <v>7426681</v>
       </c>
       <c r="S74" t="n">
         <v>3</v>
@@ -8165,38 +8165,38 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102336</t>
+          <t>https://artportalen.se/Sighting/134102397</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>134272881</v>
+        <v>134272749</v>
       </c>
       <c r="B75" t="n">
-        <v>101376</v>
+        <v>79440</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1365</v>
+        <v>637</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Ringlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Evernia divaricata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8206,10 +8206,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>706837</v>
+        <v>706238</v>
       </c>
       <c r="R75" t="n">
-        <v>7426798</v>
+        <v>7426848</v>
       </c>
       <c r="S75" t="n">
         <v>3</v>
@@ -8267,38 +8267,38 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272881</t>
+          <t>https://artportalen.se/Sighting/134272749</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134272882</v>
+        <v>136114162</v>
       </c>
       <c r="B76" t="n">
-        <v>101376</v>
+        <v>79519</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1365</v>
+        <v>639</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Grenlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Evernia mesomorpha</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>Nyl.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8308,10 +8308,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>706944</v>
+        <v>706836</v>
       </c>
       <c r="R76" t="n">
-        <v>7426775</v>
+        <v>7426791</v>
       </c>
       <c r="S76" t="n">
         <v>3</v>
@@ -8338,12 +8338,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8369,38 +8369,38 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272882</t>
+          <t>https://artportalen.se/Sighting/136114162</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>134272883</v>
+        <v>134102332</v>
       </c>
       <c r="B77" t="n">
-        <v>101376</v>
+        <v>79452</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1365</v>
+        <v>864</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lappranunkel</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Coptidium lapponicum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Tzvelev</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8410,10 +8410,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>706961</v>
+        <v>706805</v>
       </c>
       <c r="R77" t="n">
-        <v>7426774</v>
+        <v>7426821</v>
       </c>
       <c r="S77" t="n">
         <v>3</v>
@@ -8440,12 +8440,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8471,38 +8471,38 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272883</t>
+          <t>https://artportalen.se/Sighting/134102332</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>136114161</v>
+        <v>134102333</v>
       </c>
       <c r="B78" t="n">
-        <v>92252</v>
+        <v>79452</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>1503</v>
+        <v>864</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8512,10 +8512,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>706954</v>
+        <v>706797</v>
       </c>
       <c r="R78" t="n">
-        <v>7426566</v>
+        <v>7426837</v>
       </c>
       <c r="S78" t="n">
         <v>3</v>
@@ -8542,12 +8542,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8573,16 +8573,16 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136114161</t>
+          <t>https://artportalen.se/Sighting/134102333</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>90907437</v>
+        <v>134102334</v>
       </c>
       <c r="B79" t="n">
-        <v>92097</v>
+        <v>79452</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8590,37 +8590,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1588</v>
+        <v>864</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Agas, Lu lm</t>
+          <t>Ågåsgielas, Lu lm</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>706938</v>
+        <v>706856</v>
       </c>
       <c r="R79" t="n">
-        <v>7426555</v>
+        <v>7426791</v>
       </c>
       <c r="S79" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8644,12 +8644,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2019-09-22</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2019-09-22</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8660,40 +8660,31 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AS79" t="inlineStr">
-        <is>
-          <t>Olle Finnström</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Charles Campbell</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Via Charles Campbell</t>
-        </is>
-      </c>
-      <c r="AY79" t="inlineStr">
-        <is>
-          <t>Statens Fastighetsverk - NVB - Greensway</t>
-        </is>
-      </c>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/90907437</t>
+          <t>https://artportalen.se/Sighting/134102334</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>136114157</v>
+        <v>134272887</v>
       </c>
       <c r="B80" t="n">
-        <v>92126</v>
+        <v>79452</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8701,21 +8692,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2079</v>
+        <v>864</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8725,10 +8716,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>707008</v>
+        <v>706763</v>
       </c>
       <c r="R80" t="n">
-        <v>7426533</v>
+        <v>7426802</v>
       </c>
       <c r="S80" t="n">
         <v>3</v>
@@ -8755,12 +8746,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8786,16 +8777,16 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136114157</t>
+          <t>https://artportalen.se/Sighting/134272887</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>136114153</v>
+        <v>136331396</v>
       </c>
       <c r="B81" t="n">
-        <v>93396</v>
+        <v>92074</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8803,21 +8794,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>3100</v>
+        <v>1202</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8827,10 +8818,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>707049</v>
+        <v>706725</v>
       </c>
       <c r="R81" t="n">
-        <v>7426483</v>
+        <v>7426551</v>
       </c>
       <c r="S81" t="n">
         <v>3</v>
@@ -8857,12 +8848,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -8888,16 +8879,16 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136114153</t>
+          <t>https://artportalen.se/Sighting/136331396</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>136114158</v>
+        <v>134102335</v>
       </c>
       <c r="B82" t="n">
-        <v>92201</v>
+        <v>83222</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8905,21 +8896,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>3277</v>
+        <v>1312</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Luddfingersvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alloclavaria purpurea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8929,10 +8920,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>706467</v>
+        <v>706856</v>
       </c>
       <c r="R82" t="n">
-        <v>7426727</v>
+        <v>7426794</v>
       </c>
       <c r="S82" t="n">
         <v>3</v>
@@ -8959,12 +8950,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -8990,16 +8981,16 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136114158</t>
+          <t>https://artportalen.se/Sighting/134102335</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>136114149</v>
+        <v>134102336</v>
       </c>
       <c r="B83" t="n">
-        <v>87469</v>
+        <v>83222</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9007,21 +8998,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>3690</v>
+        <v>1312</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9031,10 +9022,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>707005</v>
+        <v>706796</v>
       </c>
       <c r="R83" t="n">
-        <v>7426526</v>
+        <v>7426839</v>
       </c>
       <c r="S83" t="n">
         <v>3</v>
@@ -9061,12 +9052,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9092,54 +9083,54 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136114149</t>
+          <t>https://artportalen.se/Sighting/134102336</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>90907438</v>
+        <v>134272881</v>
       </c>
       <c r="B84" t="n">
-        <v>93191</v>
+        <v>101376</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4362</v>
+        <v>1365</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Agas, Lu lm</t>
+          <t>Ågåsgielas, Lu lm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>706953</v>
+        <v>706837</v>
       </c>
       <c r="R84" t="n">
-        <v>7426549</v>
+        <v>7426798</v>
       </c>
       <c r="S84" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9163,12 +9154,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2019-09-22</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2019-09-22</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9179,62 +9170,53 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AS84" t="inlineStr">
-        <is>
-          <t>Olle Finnström</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Charles Campbell</t>
+          <t>Cecilia Lundin</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Via Charles Campbell</t>
-        </is>
-      </c>
-      <c r="AY84" t="inlineStr">
-        <is>
-          <t>Statens Fastighetsverk - NVB - Greensway</t>
-        </is>
-      </c>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/90907438</t>
+          <t>https://artportalen.se/Sighting/134272881</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133888840</v>
+        <v>134272882</v>
       </c>
       <c r="B85" t="n">
-        <v>93271</v>
+        <v>101376</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>1365</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9244,10 +9226,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>706935</v>
+        <v>706944</v>
       </c>
       <c r="R85" t="n">
-        <v>7426534</v>
+        <v>7426775</v>
       </c>
       <c r="S85" t="n">
         <v>3</v>
@@ -9274,12 +9256,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9305,16 +9287,16 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133888840</t>
+          <t>https://artportalen.se/Sighting/134272882</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>136114151</v>
+        <v>134272883</v>
       </c>
       <c r="B86" t="n">
-        <v>89232</v>
+        <v>101376</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9322,21 +9304,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4379</v>
+        <v>1365</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Toppvaxing</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hygrocybe conica</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schaeff.) P.Kumm.</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9346,10 +9328,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>706495</v>
+        <v>706961</v>
       </c>
       <c r="R86" t="n">
-        <v>7426729</v>
+        <v>7426774</v>
       </c>
       <c r="S86" t="n">
         <v>3</v>
@@ -9376,12 +9358,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9407,38 +9389,38 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136114151</t>
+          <t>https://artportalen.se/Sighting/134272883</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>136114145</v>
+        <v>136114161</v>
       </c>
       <c r="B87" t="n">
-        <v>83436</v>
+        <v>92253</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6440</v>
+        <v>1503</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9448,10 +9430,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>706856</v>
+        <v>706954</v>
       </c>
       <c r="R87" t="n">
-        <v>7426784</v>
+        <v>7426566</v>
       </c>
       <c r="S87" t="n">
         <v>3</v>
@@ -9509,16 +9491,16 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136114145</t>
+          <t>https://artportalen.se/Sighting/136114161</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>134272753</v>
+        <v>90907437</v>
       </c>
       <c r="B88" t="n">
-        <v>79130</v>
+        <v>92097</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9526,37 +9508,37 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>1588</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violmussling</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Trichaptum laricinum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Ryvarden</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Ågåsgielas, Lu lm</t>
+          <t>Agas, Lu lm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>706836</v>
+        <v>706938</v>
       </c>
       <c r="R88" t="n">
-        <v>7426766</v>
+        <v>7426555</v>
       </c>
       <c r="S88" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9580,12 +9562,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2019-09-22</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2019-09-22</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9596,31 +9578,40 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Charles Campbell</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
-        </is>
-      </c>
-      <c r="AY88" t="inlineStr"/>
+          <t>Via Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr">
+        <is>
+          <t>Statens Fastighetsverk - NVB - Greensway</t>
+        </is>
+      </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272753</t>
+          <t>https://artportalen.se/Sighting/90907437</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>134272884</v>
+        <v>136331394</v>
       </c>
       <c r="B89" t="n">
-        <v>79130</v>
+        <v>91083</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9628,21 +9619,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9652,10 +9643,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>706477</v>
+        <v>706474</v>
       </c>
       <c r="R89" t="n">
-        <v>7426743</v>
+        <v>7426674</v>
       </c>
       <c r="S89" t="n">
         <v>3</v>
@@ -9682,12 +9673,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9713,16 +9704,16 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272884</t>
+          <t>https://artportalen.se/Sighting/136331394</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>134272885</v>
+        <v>136331395</v>
       </c>
       <c r="B90" t="n">
-        <v>79130</v>
+        <v>91083</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9730,21 +9721,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9754,10 +9745,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>706844</v>
+        <v>706467</v>
       </c>
       <c r="R90" t="n">
-        <v>7426764</v>
+        <v>7426681</v>
       </c>
       <c r="S90" t="n">
         <v>3</v>
@@ -9784,12 +9775,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9815,16 +9806,16 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272885</t>
+          <t>https://artportalen.se/Sighting/136331395</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>134272886</v>
+        <v>136114157</v>
       </c>
       <c r="B91" t="n">
-        <v>79130</v>
+        <v>92127</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9832,21 +9823,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>2079</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9856,10 +9847,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>706845</v>
+        <v>707008</v>
       </c>
       <c r="R91" t="n">
-        <v>7426764</v>
+        <v>7426533</v>
       </c>
       <c r="S91" t="n">
         <v>3</v>
@@ -9886,12 +9877,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -9917,16 +9908,16 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272886</t>
+          <t>https://artportalen.se/Sighting/136114157</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>136114147</v>
+        <v>136114153</v>
       </c>
       <c r="B92" t="n">
-        <v>80068</v>
+        <v>93397</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9934,21 +9925,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6453</v>
+        <v>3100</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -9958,10 +9949,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>706953</v>
+        <v>707049</v>
       </c>
       <c r="R92" t="n">
-        <v>7426533</v>
+        <v>7426483</v>
       </c>
       <c r="S92" t="n">
         <v>3</v>
@@ -10019,16 +10010,16 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136114147</t>
+          <t>https://artportalen.se/Sighting/136114153</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>134102284</v>
+        <v>136114158</v>
       </c>
       <c r="B93" t="n">
-        <v>57975</v>
+        <v>92202</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10036,21 +10027,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>3277</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddfingersvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alloclavaria purpurea</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(O.F.Müll.) Dentinger &amp; D.J.McLaughlin</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10060,10 +10051,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>706890</v>
+        <v>706467</v>
       </c>
       <c r="R93" t="n">
-        <v>7426773</v>
+        <v>7426727</v>
       </c>
       <c r="S93" t="n">
         <v>3</v>
@@ -10090,12 +10081,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10121,16 +10112,16 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102284</t>
+          <t>https://artportalen.se/Sighting/136114158</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>134102285</v>
+        <v>136114149</v>
       </c>
       <c r="B94" t="n">
-        <v>57975</v>
+        <v>87470</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10138,21 +10129,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>3690</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10162,10 +10153,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>706809</v>
+        <v>707005</v>
       </c>
       <c r="R94" t="n">
-        <v>7426804</v>
+        <v>7426526</v>
       </c>
       <c r="S94" t="n">
         <v>3</v>
@@ -10192,12 +10183,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2026-06-04</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10223,16 +10214,16 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102285</t>
+          <t>https://artportalen.se/Sighting/136114149</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>134102286</v>
+        <v>90907438</v>
       </c>
       <c r="B95" t="n">
-        <v>57975</v>
+        <v>93191</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10240,37 +10231,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Ågåsgielas, Lu lm</t>
+          <t>Agas, Lu lm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>706976</v>
+        <v>706953</v>
       </c>
       <c r="R95" t="n">
-        <v>7426669</v>
+        <v>7426549</v>
       </c>
       <c r="S95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10294,12 +10285,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2019-09-22</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2019-09-22</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10310,31 +10301,40 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>Olle Finnström</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
+          <t>Charles Campbell</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Cecilia Lundin</t>
-        </is>
-      </c>
-      <c r="AY95" t="inlineStr"/>
+          <t>Via Charles Campbell</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>Statens Fastighetsverk - NVB - Greensway</t>
+        </is>
+      </c>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102286</t>
+          <t>https://artportalen.se/Sighting/90907438</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>136114150</v>
+        <v>133888840</v>
       </c>
       <c r="B96" t="n">
-        <v>57987</v>
+        <v>93271</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10342,21 +10342,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10366,10 +10366,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>706541</v>
+        <v>706935</v>
       </c>
       <c r="R96" t="n">
-        <v>7426780</v>
+        <v>7426534</v>
       </c>
       <c r="S96" t="n">
         <v>3</v>
@@ -10396,12 +10396,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10427,38 +10427,38 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136114150</t>
+          <t>https://artportalen.se/Sighting/133888840</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133888827</v>
+        <v>136331408</v>
       </c>
       <c r="B97" t="n">
-        <v>57162</v>
+        <v>93372</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10468,10 +10468,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>706811</v>
+        <v>706487</v>
       </c>
       <c r="R97" t="n">
-        <v>7426646</v>
+        <v>7426686</v>
       </c>
       <c r="S97" t="n">
         <v>3</v>
@@ -10498,12 +10498,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10529,16 +10529,16 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133888827</t>
+          <t>https://artportalen.se/Sighting/136331408</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>134102287</v>
+        <v>136114151</v>
       </c>
       <c r="B98" t="n">
-        <v>57162</v>
+        <v>89233</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10546,21 +10546,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100138</v>
+        <v>4379</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Toppvaxing</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hygrocybe conica</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schaeff.) P.Kumm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10570,10 +10570,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>706951</v>
+        <v>706495</v>
       </c>
       <c r="R98" t="n">
-        <v>7426689</v>
+        <v>7426729</v>
       </c>
       <c r="S98" t="n">
         <v>3</v>
@@ -10600,17 +10600,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10636,38 +10631,38 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134102287</t>
+          <t>https://artportalen.se/Sighting/136114151</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>134272743</v>
+        <v>136114145</v>
       </c>
       <c r="B99" t="n">
-        <v>57162</v>
+        <v>83437</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100138</v>
+        <v>6440</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10677,10 +10672,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>706576</v>
+        <v>706856</v>
       </c>
       <c r="R99" t="n">
-        <v>7426767</v>
+        <v>7426784</v>
       </c>
       <c r="S99" t="n">
         <v>3</v>
@@ -10707,17 +10702,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Otroligt mycket spillning på stenkulle</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -10743,16 +10733,16 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272743</t>
+          <t>https://artportalen.se/Sighting/136114145</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>136114155</v>
+        <v>134272753</v>
       </c>
       <c r="B100" t="n">
-        <v>5498</v>
+        <v>79130</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10760,21 +10750,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>101410</v>
+        <v>6446</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Reliktbock</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Nothorhina muricata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Dalman, 1817)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10784,10 +10774,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>706537</v>
+        <v>706836</v>
       </c>
       <c r="R100" t="n">
-        <v>7426777</v>
+        <v>7426766</v>
       </c>
       <c r="S100" t="n">
         <v>3</v>
@@ -10814,12 +10804,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10845,16 +10835,16 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136114155</t>
+          <t>https://artportalen.se/Sighting/134272753</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>136114152</v>
+        <v>134272884</v>
       </c>
       <c r="B101" t="n">
-        <v>58148</v>
+        <v>79130</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -10862,21 +10852,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10886,10 +10876,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>707003</v>
+        <v>706477</v>
       </c>
       <c r="R101" t="n">
-        <v>7426526</v>
+        <v>7426743</v>
       </c>
       <c r="S101" t="n">
         <v>3</v>
@@ -10916,12 +10906,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -10947,38 +10937,38 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136114152</t>
+          <t>https://artportalen.se/Sighting/134272884</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>134272742</v>
+        <v>134272885</v>
       </c>
       <c r="B102" t="n">
-        <v>58839</v>
+        <v>79130</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>208249</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10988,10 +10978,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>706447</v>
+        <v>706844</v>
       </c>
       <c r="R102" t="n">
-        <v>7426815</v>
+        <v>7426764</v>
       </c>
       <c r="S102" t="n">
         <v>3</v>
@@ -11049,38 +11039,38 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272742</t>
+          <t>https://artportalen.se/Sighting/134272885</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>134272878</v>
+        <v>134272886</v>
       </c>
       <c r="B103" t="n">
-        <v>58839</v>
+        <v>79130</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>208249</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11090,10 +11080,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>706913</v>
+        <v>706845</v>
       </c>
       <c r="R103" t="n">
-        <v>7426789</v>
+        <v>7426764</v>
       </c>
       <c r="S103" t="n">
         <v>3</v>
@@ -11151,38 +11141,38 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272878</t>
+          <t>https://artportalen.se/Sighting/134272886</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>134272879</v>
+        <v>136114147</v>
       </c>
       <c r="B104" t="n">
-        <v>58839</v>
+        <v>80069</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>208249</v>
+        <v>6453</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11192,10 +11182,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>706948</v>
+        <v>706953</v>
       </c>
       <c r="R104" t="n">
-        <v>7426772</v>
+        <v>7426533</v>
       </c>
       <c r="S104" t="n">
         <v>3</v>
@@ -11222,12 +11212,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11253,38 +11243,38 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272879</t>
+          <t>https://artportalen.se/Sighting/136114147</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>136114159</v>
+        <v>134102284</v>
       </c>
       <c r="B105" t="n">
-        <v>108065</v>
+        <v>57975</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>219933</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Kattfot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Antennaria dioica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Gaertn.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11294,10 +11284,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>706490</v>
+        <v>706890</v>
       </c>
       <c r="R105" t="n">
-        <v>7426729</v>
+        <v>7426773</v>
       </c>
       <c r="S105" t="n">
         <v>3</v>
@@ -11324,12 +11314,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11355,38 +11345,38 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136114159</t>
+          <t>https://artportalen.se/Sighting/134102284</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>136114166</v>
+        <v>134102285</v>
       </c>
       <c r="B106" t="n">
-        <v>110273</v>
+        <v>57975</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220294</v>
+        <v>100109</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Fjällskära</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Saussurea alpina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11396,10 +11386,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>706470</v>
+        <v>706809</v>
       </c>
       <c r="R106" t="n">
-        <v>7426725</v>
+        <v>7426804</v>
       </c>
       <c r="S106" t="n">
         <v>3</v>
@@ -11426,12 +11416,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-04</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11457,38 +11447,38 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136114166</t>
+          <t>https://artportalen.se/Sighting/134102285</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>134272741</v>
+        <v>134102286</v>
       </c>
       <c r="B107" t="n">
-        <v>106309</v>
+        <v>57975</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11498,10 +11488,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>706510</v>
+        <v>706976</v>
       </c>
       <c r="R107" t="n">
-        <v>7426625</v>
+        <v>7426669</v>
       </c>
       <c r="S107" t="n">
         <v>3</v>
@@ -11528,12 +11518,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11559,38 +11549,38 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272741</t>
+          <t>https://artportalen.se/Sighting/134102286</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>134272876</v>
+        <v>136114150</v>
       </c>
       <c r="B108" t="n">
-        <v>106309</v>
+        <v>57988</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>221725</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11600,10 +11590,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>706861</v>
+        <v>706541</v>
       </c>
       <c r="R108" t="n">
-        <v>7426790</v>
+        <v>7426780</v>
       </c>
       <c r="S108" t="n">
         <v>3</v>
@@ -11630,12 +11620,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11661,38 +11651,38 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272876</t>
+          <t>https://artportalen.se/Sighting/136114150</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>136114156</v>
+        <v>136331397</v>
       </c>
       <c r="B109" t="n">
-        <v>98170</v>
+        <v>57988</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11702,10 +11692,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>706495</v>
+        <v>706811</v>
       </c>
       <c r="R109" t="n">
-        <v>7426742</v>
+        <v>7426642</v>
       </c>
       <c r="S109" t="n">
         <v>3</v>
@@ -11732,12 +11722,17 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -11763,16 +11758,16 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136114156</t>
+          <t>https://artportalen.se/Sighting/136331397</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>133888828</v>
+        <v>133888827</v>
       </c>
       <c r="B110" t="n">
-        <v>104707</v>
+        <v>57162</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11780,21 +11775,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>222412</v>
+        <v>100138</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11804,10 +11799,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>706508</v>
+        <v>706811</v>
       </c>
       <c r="R110" t="n">
-        <v>7426811</v>
+        <v>7426646</v>
       </c>
       <c r="S110" t="n">
         <v>3</v>
@@ -11865,38 +11860,38 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133888828</t>
+          <t>https://artportalen.se/Sighting/133888827</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>134272752</v>
+        <v>134102287</v>
       </c>
       <c r="B111" t="n">
-        <v>79131</v>
+        <v>57162</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11906,10 +11901,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>706597</v>
+        <v>706951</v>
       </c>
       <c r="R111" t="n">
-        <v>7426486</v>
+        <v>7426689</v>
       </c>
       <c r="S111" t="n">
         <v>3</v>
@@ -11936,12 +11931,17 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -11967,38 +11967,38 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272752</t>
+          <t>https://artportalen.se/Sighting/134102287</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>134272877</v>
+        <v>134272743</v>
       </c>
       <c r="B112" t="n">
-        <v>79963</v>
+        <v>57162</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12008,10 +12008,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>706475</v>
+        <v>706576</v>
       </c>
       <c r="R112" t="n">
-        <v>7426738</v>
+        <v>7426767</v>
       </c>
       <c r="S112" t="n">
         <v>3</v>
@@ -12046,6 +12046,11 @@
           <t>2026-06-09</t>
         </is>
       </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Otroligt mycket spillning på stenkulle</t>
+        </is>
+      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
@@ -12069,16 +12074,16 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272877</t>
+          <t>https://artportalen.se/Sighting/134272743</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>136114148</v>
+        <v>136114155</v>
       </c>
       <c r="B113" t="n">
-        <v>80039</v>
+        <v>5498</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12086,21 +12091,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>229821</v>
+        <v>101410</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Reliktbock</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Nothorhina muricata</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Dalman, 1817)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12110,10 +12115,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>706954</v>
+        <v>706537</v>
       </c>
       <c r="R113" t="n">
-        <v>7426529</v>
+        <v>7426777</v>
       </c>
       <c r="S113" t="n">
         <v>3</v>
@@ -12171,38 +12176,38 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136114148</t>
+          <t>https://artportalen.se/Sighting/136114155</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>134272744</v>
+        <v>136114152</v>
       </c>
       <c r="B114" t="n">
-        <v>79899</v>
+        <v>58149</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>229830</v>
+        <v>103021</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Späd brosklav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Ramalina dilacerata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12212,10 +12217,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>706239</v>
+        <v>707003</v>
       </c>
       <c r="R114" t="n">
-        <v>7426846</v>
+        <v>7426526</v>
       </c>
       <c r="S114" t="n">
         <v>3</v>
@@ -12242,12 +12247,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12273,38 +12278,38 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272744</t>
+          <t>https://artportalen.se/Sighting/136114152</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>134272745</v>
+        <v>134272742</v>
       </c>
       <c r="B115" t="n">
-        <v>79899</v>
+        <v>58839</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>229830</v>
+        <v>208249</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Späd brosklav</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Ramalina dilacerata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12314,10 +12319,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>706278</v>
+        <v>706447</v>
       </c>
       <c r="R115" t="n">
-        <v>7426914</v>
+        <v>7426815</v>
       </c>
       <c r="S115" t="n">
         <v>3</v>
@@ -12375,38 +12380,38 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134272745</t>
+          <t>https://artportalen.se/Sighting/134272742</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>136114154</v>
+        <v>134272878</v>
       </c>
       <c r="B116" t="n">
-        <v>79472</v>
+        <v>58839</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>260591</v>
+        <v>208249</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12416,10 +12421,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>706991</v>
+        <v>706913</v>
       </c>
       <c r="R116" t="n">
-        <v>7426530</v>
+        <v>7426789</v>
       </c>
       <c r="S116" t="n">
         <v>3</v>
@@ -12446,12 +12451,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12477,7 +12482,1440 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/134272878</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>134272879</v>
+      </c>
+      <c r="B117" t="n">
+        <v>58839</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>706948</v>
+      </c>
+      <c r="R117" t="n">
+        <v>7426772</v>
+      </c>
+      <c r="S117" t="n">
+        <v>3</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272879</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>136114159</v>
+      </c>
+      <c r="B118" t="n">
+        <v>108066</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>219933</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Kattfot</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Antennaria dioica</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>706490</v>
+      </c>
+      <c r="R118" t="n">
+        <v>7426729</v>
+      </c>
+      <c r="S118" t="n">
+        <v>3</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136114159</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>136114166</v>
+      </c>
+      <c r="B119" t="n">
+        <v>110274</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>220294</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Fjällskära</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Saussurea alpina</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>(L.) DC.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>706470</v>
+      </c>
+      <c r="R119" t="n">
+        <v>7426725</v>
+      </c>
+      <c r="S119" t="n">
+        <v>3</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136114166</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>134272741</v>
+      </c>
+      <c r="B120" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>706510</v>
+      </c>
+      <c r="R120" t="n">
+        <v>7426625</v>
+      </c>
+      <c r="S120" t="n">
+        <v>3</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272741</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>134272876</v>
+      </c>
+      <c r="B121" t="n">
+        <v>106309</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>706861</v>
+      </c>
+      <c r="R121" t="n">
+        <v>7426790</v>
+      </c>
+      <c r="S121" t="n">
+        <v>3</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272876</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>136114156</v>
+      </c>
+      <c r="B122" t="n">
+        <v>98171</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>706495</v>
+      </c>
+      <c r="R122" t="n">
+        <v>7426742</v>
+      </c>
+      <c r="S122" t="n">
+        <v>3</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136114156</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>133888828</v>
+      </c>
+      <c r="B123" t="n">
+        <v>104707</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>706508</v>
+      </c>
+      <c r="R123" t="n">
+        <v>7426811</v>
+      </c>
+      <c r="S123" t="n">
+        <v>3</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133888828</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>134272752</v>
+      </c>
+      <c r="B124" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>706597</v>
+      </c>
+      <c r="R124" t="n">
+        <v>7426486</v>
+      </c>
+      <c r="S124" t="n">
+        <v>3</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272752</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>134272877</v>
+      </c>
+      <c r="B125" t="n">
+        <v>79963</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>706475</v>
+      </c>
+      <c r="R125" t="n">
+        <v>7426738</v>
+      </c>
+      <c r="S125" t="n">
+        <v>3</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX125" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272877</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>136114148</v>
+      </c>
+      <c r="B126" t="n">
+        <v>80040</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>706954</v>
+      </c>
+      <c r="R126" t="n">
+        <v>7426529</v>
+      </c>
+      <c r="S126" t="n">
+        <v>3</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136114148</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>134272744</v>
+      </c>
+      <c r="B127" t="n">
+        <v>79899</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>229830</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Späd brosklav</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Ramalina dilacerata</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>706239</v>
+      </c>
+      <c r="R127" t="n">
+        <v>7426846</v>
+      </c>
+      <c r="S127" t="n">
+        <v>3</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272744</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>134272745</v>
+      </c>
+      <c r="B128" t="n">
+        <v>79899</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>229830</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Späd brosklav</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Ramalina dilacerata</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>706278</v>
+      </c>
+      <c r="R128" t="n">
+        <v>7426914</v>
+      </c>
+      <c r="S128" t="n">
+        <v>3</v>
+      </c>
+      <c r="T128" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U128" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="AD128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="inlineStr"/>
+      <c r="AW128" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX128" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134272745</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>136114154</v>
+      </c>
+      <c r="B129" t="n">
+        <v>79473</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>706991</v>
+      </c>
+      <c r="R129" t="n">
+        <v>7426530</v>
+      </c>
+      <c r="S129" t="n">
+        <v>3</v>
+      </c>
+      <c r="T129" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U129" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="AD129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="inlineStr"/>
+      <c r="AW129" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX129" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136114154</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>136331400</v>
+      </c>
+      <c r="B130" t="n">
+        <v>92322</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>CR</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>6008693</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Kritporing</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Antrodia crassa</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>Ågåsgielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>706476</v>
+      </c>
+      <c r="R130" t="n">
+        <v>7426673</v>
+      </c>
+      <c r="S130" t="n">
+        <v>3</v>
+      </c>
+      <c r="T130" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U130" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Gammal frukkropp</t>
+        </is>
+      </c>
+      <c r="AD130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG130" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT130" t="inlineStr"/>
+      <c r="AW130" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AX130" t="inlineStr">
+        <is>
+          <t>Cecilia Lundin</t>
+        </is>
+      </c>
+      <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136331400</t>
         </is>
       </c>
     </row>
@@ -12598,6 +14036,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55525-2025 artfynd.xlsx
+++ b/artfynd/A 55525-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136114146</v>
       </c>
       <c r="B2" t="n">
-        <v>97540</v>
+        <v>97551</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136114163</v>
       </c>
       <c r="B3" t="n">
-        <v>92320</v>
+        <v>92326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136114165</v>
       </c>
       <c r="B4" t="n">
-        <v>92320</v>
+        <v>92326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136331401</v>
       </c>
       <c r="B5" t="n">
-        <v>92320</v>
+        <v>92326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136331402</v>
       </c>
       <c r="B6" t="n">
-        <v>92320</v>
+        <v>92326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136331403</v>
       </c>
       <c r="B7" t="n">
-        <v>92320</v>
+        <v>92326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136331404</v>
       </c>
       <c r="B8" t="n">
-        <v>92320</v>
+        <v>92326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136331405</v>
       </c>
       <c r="B9" t="n">
-        <v>92320</v>
+        <v>92326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136331406</v>
       </c>
       <c r="B10" t="n">
-        <v>92320</v>
+        <v>92326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136331398</v>
       </c>
       <c r="B11" t="n">
-        <v>92024</v>
+        <v>92030</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136331399</v>
       </c>
       <c r="B12" t="n">
-        <v>92024</v>
+        <v>92030</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>136114167</v>
       </c>
       <c r="B30" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>136114162</v>
       </c>
       <c r="B76" t="n">
-        <v>79519</v>
+        <v>79523</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>136331396</v>
       </c>
       <c r="B81" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>136114161</v>
       </c>
       <c r="B87" t="n">
-        <v>92253</v>
+        <v>92259</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>136331394</v>
       </c>
       <c r="B89" t="n">
-        <v>91083</v>
+        <v>91089</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>136331395</v>
       </c>
       <c r="B90" t="n">
-        <v>91083</v>
+        <v>91089</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>136114157</v>
       </c>
       <c r="B91" t="n">
-        <v>92127</v>
+        <v>92133</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>136114153</v>
       </c>
       <c r="B92" t="n">
-        <v>93397</v>
+        <v>93403</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>136114158</v>
       </c>
       <c r="B93" t="n">
-        <v>92202</v>
+        <v>92208</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>136114149</v>
       </c>
       <c r="B94" t="n">
-        <v>87470</v>
+        <v>87476</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>136331408</v>
       </c>
       <c r="B97" t="n">
-        <v>93372</v>
+        <v>93378</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>136114151</v>
       </c>
       <c r="B98" t="n">
-        <v>89233</v>
+        <v>89239</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>136114145</v>
       </c>
       <c r="B99" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>136114147</v>
       </c>
       <c r="B104" t="n">
-        <v>80069</v>
+        <v>80073</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>136114159</v>
       </c>
       <c r="B118" t="n">
-        <v>108066</v>
+        <v>108077</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>136114166</v>
       </c>
       <c r="B119" t="n">
-        <v>110274</v>
+        <v>110285</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         <v>136114156</v>
       </c>
       <c r="B122" t="n">
-        <v>98171</v>
+        <v>98182</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>136114148</v>
       </c>
       <c r="B126" t="n">
-        <v>80040</v>
+        <v>80044</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
         <v>136114154</v>
       </c>
       <c r="B129" t="n">
-        <v>79473</v>
+        <v>79477</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>136331400</v>
       </c>
       <c r="B130" t="n">
-        <v>92322</v>
+        <v>92328</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/A 55525-2025 artfynd.xlsx
+++ b/artfynd/A 55525-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136114146</v>
       </c>
       <c r="B2" t="n">
-        <v>97551</v>
+        <v>97564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136114163</v>
       </c>
       <c r="B3" t="n">
-        <v>92326</v>
+        <v>92333</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136114165</v>
       </c>
       <c r="B4" t="n">
-        <v>92326</v>
+        <v>92333</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136331401</v>
       </c>
       <c r="B5" t="n">
-        <v>92326</v>
+        <v>92333</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136331402</v>
       </c>
       <c r="B6" t="n">
-        <v>92326</v>
+        <v>92333</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136331403</v>
       </c>
       <c r="B7" t="n">
-        <v>92326</v>
+        <v>92333</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136331404</v>
       </c>
       <c r="B8" t="n">
-        <v>92326</v>
+        <v>92333</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136331405</v>
       </c>
       <c r="B9" t="n">
-        <v>92326</v>
+        <v>92333</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136331406</v>
       </c>
       <c r="B10" t="n">
-        <v>92326</v>
+        <v>92333</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136331398</v>
       </c>
       <c r="B11" t="n">
-        <v>92030</v>
+        <v>92037</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136331399</v>
       </c>
       <c r="B12" t="n">
-        <v>92030</v>
+        <v>92037</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>136114167</v>
       </c>
       <c r="B30" t="n">
-        <v>79120</v>
+        <v>79126</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>136114162</v>
       </c>
       <c r="B76" t="n">
-        <v>79523</v>
+        <v>79529</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>136331396</v>
       </c>
       <c r="B81" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>136114161</v>
       </c>
       <c r="B87" t="n">
-        <v>92259</v>
+        <v>92266</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>136331394</v>
       </c>
       <c r="B89" t="n">
-        <v>91089</v>
+        <v>91096</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>136331395</v>
       </c>
       <c r="B90" t="n">
-        <v>91089</v>
+        <v>91096</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>136114157</v>
       </c>
       <c r="B91" t="n">
-        <v>92133</v>
+        <v>92140</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>136114153</v>
       </c>
       <c r="B92" t="n">
-        <v>93403</v>
+        <v>93410</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>136114158</v>
       </c>
       <c r="B93" t="n">
-        <v>92208</v>
+        <v>92215</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>136114149</v>
       </c>
       <c r="B94" t="n">
-        <v>87476</v>
+        <v>87483</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>136331408</v>
       </c>
       <c r="B97" t="n">
-        <v>93378</v>
+        <v>93385</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>136114151</v>
       </c>
       <c r="B98" t="n">
-        <v>89239</v>
+        <v>89246</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>136114145</v>
       </c>
       <c r="B99" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>136114147</v>
       </c>
       <c r="B104" t="n">
-        <v>80073</v>
+        <v>80079</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>136114150</v>
       </c>
       <c r="B108" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11660,7 +11660,7 @@
         <v>136331397</v>
       </c>
       <c r="B109" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
         <v>136114152</v>
       </c>
       <c r="B114" t="n">
-        <v>58149</v>
+        <v>58154</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>136114159</v>
       </c>
       <c r="B118" t="n">
-        <v>108077</v>
+        <v>108090</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>136114166</v>
       </c>
       <c r="B119" t="n">
-        <v>110285</v>
+        <v>110298</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         <v>136114156</v>
       </c>
       <c r="B122" t="n">
-        <v>98182</v>
+        <v>98195</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>136114148</v>
       </c>
       <c r="B126" t="n">
-        <v>80044</v>
+        <v>80050</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
         <v>136114154</v>
       </c>
       <c r="B129" t="n">
-        <v>79477</v>
+        <v>79483</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>136331400</v>
       </c>
       <c r="B130" t="n">
-        <v>92328</v>
+        <v>92335</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/A 55525-2025 artfynd.xlsx
+++ b/artfynd/A 55525-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136114146</v>
       </c>
       <c r="B2" t="n">
-        <v>97564</v>
+        <v>97565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136114163</v>
       </c>
       <c r="B3" t="n">
-        <v>92333</v>
+        <v>92334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136114165</v>
       </c>
       <c r="B4" t="n">
-        <v>92333</v>
+        <v>92334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136331401</v>
       </c>
       <c r="B5" t="n">
-        <v>92333</v>
+        <v>92334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136331402</v>
       </c>
       <c r="B6" t="n">
-        <v>92333</v>
+        <v>92334</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136331403</v>
       </c>
       <c r="B7" t="n">
-        <v>92333</v>
+        <v>92334</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136331404</v>
       </c>
       <c r="B8" t="n">
-        <v>92333</v>
+        <v>92334</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136331405</v>
       </c>
       <c r="B9" t="n">
-        <v>92333</v>
+        <v>92334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136331406</v>
       </c>
       <c r="B10" t="n">
-        <v>92333</v>
+        <v>92334</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136331398</v>
       </c>
       <c r="B11" t="n">
-        <v>92037</v>
+        <v>92038</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136331399</v>
       </c>
       <c r="B12" t="n">
-        <v>92037</v>
+        <v>92038</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>136331396</v>
       </c>
       <c r="B81" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>136114161</v>
       </c>
       <c r="B87" t="n">
-        <v>92266</v>
+        <v>92267</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>136331394</v>
       </c>
       <c r="B89" t="n">
-        <v>91096</v>
+        <v>91097</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>136331395</v>
       </c>
       <c r="B90" t="n">
-        <v>91096</v>
+        <v>91097</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>136114157</v>
       </c>
       <c r="B91" t="n">
-        <v>92140</v>
+        <v>92141</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>136114153</v>
       </c>
       <c r="B92" t="n">
-        <v>93410</v>
+        <v>93411</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>136114158</v>
       </c>
       <c r="B93" t="n">
-        <v>92215</v>
+        <v>92216</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>136331408</v>
       </c>
       <c r="B97" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>136114151</v>
       </c>
       <c r="B98" t="n">
-        <v>89246</v>
+        <v>89247</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>136114159</v>
       </c>
       <c r="B118" t="n">
-        <v>108090</v>
+        <v>108091</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>136114166</v>
       </c>
       <c r="B119" t="n">
-        <v>110298</v>
+        <v>110299</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         <v>136114156</v>
       </c>
       <c r="B122" t="n">
-        <v>98195</v>
+        <v>98196</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>136331400</v>
       </c>
       <c r="B130" t="n">
-        <v>92335</v>
+        <v>92336</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/A 55525-2025 artfynd.xlsx
+++ b/artfynd/A 55525-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136114146</v>
       </c>
       <c r="B2" t="n">
-        <v>97565</v>
+        <v>97578</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136114163</v>
       </c>
       <c r="B3" t="n">
-        <v>92334</v>
+        <v>92347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136114165</v>
       </c>
       <c r="B4" t="n">
-        <v>92334</v>
+        <v>92347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136331401</v>
       </c>
       <c r="B5" t="n">
-        <v>92334</v>
+        <v>92347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136331402</v>
       </c>
       <c r="B6" t="n">
-        <v>92334</v>
+        <v>92347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136331403</v>
       </c>
       <c r="B7" t="n">
-        <v>92334</v>
+        <v>92347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136331404</v>
       </c>
       <c r="B8" t="n">
-        <v>92334</v>
+        <v>92347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136331405</v>
       </c>
       <c r="B9" t="n">
-        <v>92334</v>
+        <v>92347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136331406</v>
       </c>
       <c r="B10" t="n">
-        <v>92334</v>
+        <v>92347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136331398</v>
       </c>
       <c r="B11" t="n">
-        <v>92038</v>
+        <v>92051</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136331399</v>
       </c>
       <c r="B12" t="n">
-        <v>92038</v>
+        <v>92051</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>136114167</v>
       </c>
       <c r="B30" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>136114162</v>
       </c>
       <c r="B76" t="n">
-        <v>79529</v>
+        <v>79542</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>136331396</v>
       </c>
       <c r="B81" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>136114161</v>
       </c>
       <c r="B87" t="n">
-        <v>92267</v>
+        <v>92280</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>136331394</v>
       </c>
       <c r="B89" t="n">
-        <v>91097</v>
+        <v>91110</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>136331395</v>
       </c>
       <c r="B90" t="n">
-        <v>91097</v>
+        <v>91110</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>136114157</v>
       </c>
       <c r="B91" t="n">
-        <v>92141</v>
+        <v>92154</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>136114153</v>
       </c>
       <c r="B92" t="n">
-        <v>93411</v>
+        <v>93424</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>136114158</v>
       </c>
       <c r="B93" t="n">
-        <v>92216</v>
+        <v>92229</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>136114149</v>
       </c>
       <c r="B94" t="n">
-        <v>87483</v>
+        <v>87496</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>136331408</v>
       </c>
       <c r="B97" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>136114151</v>
       </c>
       <c r="B98" t="n">
-        <v>89247</v>
+        <v>89260</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>136114145</v>
       </c>
       <c r="B99" t="n">
-        <v>83447</v>
+        <v>83460</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>136114147</v>
       </c>
       <c r="B104" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>136114150</v>
       </c>
       <c r="B108" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11660,7 +11660,7 @@
         <v>136331397</v>
       </c>
       <c r="B109" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
         <v>136114152</v>
       </c>
       <c r="B114" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>136114159</v>
       </c>
       <c r="B118" t="n">
-        <v>108091</v>
+        <v>108104</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>136114166</v>
       </c>
       <c r="B119" t="n">
-        <v>110299</v>
+        <v>110312</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         <v>136114156</v>
       </c>
       <c r="B122" t="n">
-        <v>98196</v>
+        <v>98209</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>136114148</v>
       </c>
       <c r="B126" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
         <v>136114154</v>
       </c>
       <c r="B129" t="n">
-        <v>79483</v>
+        <v>79496</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>136331400</v>
       </c>
       <c r="B130" t="n">
-        <v>92336</v>
+        <v>92349</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>

--- a/artfynd/A 55525-2025 artfynd.xlsx
+++ b/artfynd/A 55525-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136114146</v>
       </c>
       <c r="B2" t="n">
-        <v>97578</v>
+        <v>97579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136114163</v>
       </c>
       <c r="B3" t="n">
-        <v>92347</v>
+        <v>92348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136114165</v>
       </c>
       <c r="B4" t="n">
-        <v>92347</v>
+        <v>92348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>136331401</v>
       </c>
       <c r="B5" t="n">
-        <v>92347</v>
+        <v>92348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>136331402</v>
       </c>
       <c r="B6" t="n">
-        <v>92347</v>
+        <v>92348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>136331403</v>
       </c>
       <c r="B7" t="n">
-        <v>92347</v>
+        <v>92348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1295,7 +1295,7 @@
         <v>136331404</v>
       </c>
       <c r="B8" t="n">
-        <v>92347</v>
+        <v>92348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
         <v>136331405</v>
       </c>
       <c r="B9" t="n">
-        <v>92347</v>
+        <v>92348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>136331406</v>
       </c>
       <c r="B10" t="n">
-        <v>92347</v>
+        <v>92348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>136331398</v>
       </c>
       <c r="B11" t="n">
-        <v>92051</v>
+        <v>92052</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         <v>136331399</v>
       </c>
       <c r="B12" t="n">
-        <v>92051</v>
+        <v>92052</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>136114167</v>
       </c>
       <c r="B30" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>136114162</v>
       </c>
       <c r="B76" t="n">
-        <v>79542</v>
+        <v>79543</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8786,7 +8786,7 @@
         <v>136331396</v>
       </c>
       <c r="B81" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>136114161</v>
       </c>
       <c r="B87" t="n">
-        <v>92280</v>
+        <v>92281</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9611,7 +9611,7 @@
         <v>136331394</v>
       </c>
       <c r="B89" t="n">
-        <v>91110</v>
+        <v>91111</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9713,7 +9713,7 @@
         <v>136331395</v>
       </c>
       <c r="B90" t="n">
-        <v>91110</v>
+        <v>91111</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>136114157</v>
       </c>
       <c r="B91" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>136114153</v>
       </c>
       <c r="B92" t="n">
-        <v>93424</v>
+        <v>93425</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>136114158</v>
       </c>
       <c r="B93" t="n">
-        <v>92229</v>
+        <v>92230</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10121,7 +10121,7 @@
         <v>136114149</v>
       </c>
       <c r="B94" t="n">
-        <v>87496</v>
+        <v>87497</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>136331408</v>
       </c>
       <c r="B97" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10538,7 +10538,7 @@
         <v>136114151</v>
       </c>
       <c r="B98" t="n">
-        <v>89260</v>
+        <v>89261</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10640,7 +10640,7 @@
         <v>136114145</v>
       </c>
       <c r="B99" t="n">
-        <v>83460</v>
+        <v>83461</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11150,7 +11150,7 @@
         <v>136114147</v>
       </c>
       <c r="B104" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>136114159</v>
       </c>
       <c r="B118" t="n">
-        <v>108104</v>
+        <v>108105</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>136114166</v>
       </c>
       <c r="B119" t="n">
-        <v>110312</v>
+        <v>110313</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         <v>136114156</v>
       </c>
       <c r="B122" t="n">
-        <v>98209</v>
+        <v>98210</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -13409,7 +13409,7 @@
         <v>136114148</v>
       </c>
       <c r="B126" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
         <v>136114154</v>
       </c>
       <c r="B129" t="n">
-        <v>79496</v>
+        <v>79497</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>136331400</v>
       </c>
       <c r="B130" t="n">
-        <v>92349</v>
+        <v>92350</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
